--- a/0001_ROBOS/CAPTAÇÃO/FORMS GERAL/Forms_Cru.xlsx
+++ b/0001_ROBOS/CAPTAÇÃO/FORMS GERAL/Forms_Cru.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DI174"/>
+  <dimension ref="A1:DI219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30338,6 +30338,7649 @@
         </is>
       </c>
     </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>537</v>
+      </c>
+      <c r="B175" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C175" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>AMÉRICAS</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
+      <c r="O175" t="inlineStr"/>
+      <c r="P175" t="inlineStr"/>
+      <c r="Q175" t="inlineStr"/>
+      <c r="R175" t="inlineStr"/>
+      <c r="S175" t="inlineStr"/>
+      <c r="T175" t="inlineStr"/>
+      <c r="U175" t="inlineStr"/>
+      <c r="V175" t="inlineStr"/>
+      <c r="W175" t="n">
+        <v>96512019</v>
+      </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>THAIS SANTOS DOS ANJOS</t>
+        </is>
+      </c>
+      <c r="Y175" t="n">
+        <v>11149358750</v>
+      </c>
+      <c r="Z175" s="1" t="n">
+        <v>30824</v>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="AD175" t="n">
+        <v>500</v>
+      </c>
+      <c r="AE175" t="n">
+        <v>21976535327</v>
+      </c>
+      <c r="AF175" t="inlineStr">
+        <is>
+          <t>Emagrecimento</t>
+        </is>
+      </c>
+      <c r="AG175" t="inlineStr"/>
+      <c r="AH175" t="inlineStr"/>
+      <c r="AI175" t="inlineStr"/>
+      <c r="AJ175" t="inlineStr"/>
+      <c r="AK175" t="inlineStr"/>
+      <c r="AL175" t="inlineStr"/>
+      <c r="AM175" t="inlineStr"/>
+      <c r="AN175" t="inlineStr"/>
+      <c r="AO175" t="inlineStr"/>
+      <c r="AP175" t="inlineStr"/>
+      <c r="AQ175" t="inlineStr"/>
+      <c r="AR175" t="inlineStr"/>
+      <c r="AS175" t="inlineStr"/>
+      <c r="AT175" t="inlineStr"/>
+      <c r="AU175" t="inlineStr"/>
+      <c r="AV175" t="inlineStr"/>
+      <c r="AW175" t="inlineStr"/>
+      <c r="AX175" t="inlineStr"/>
+      <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr"/>
+      <c r="BA175" t="inlineStr"/>
+      <c r="BB175" t="inlineStr"/>
+      <c r="BC175" t="inlineStr"/>
+      <c r="BD175" t="inlineStr"/>
+      <c r="BE175" t="inlineStr"/>
+      <c r="BF175" t="inlineStr"/>
+      <c r="BG175" t="inlineStr"/>
+      <c r="BH175" t="inlineStr"/>
+      <c r="BI175" t="inlineStr"/>
+      <c r="BJ175" t="inlineStr"/>
+      <c r="BK175" t="inlineStr"/>
+      <c r="BL175" t="inlineStr"/>
+      <c r="BM175" t="inlineStr"/>
+      <c r="BN175" t="inlineStr"/>
+      <c r="BO175" t="inlineStr"/>
+      <c r="BP175" t="inlineStr"/>
+      <c r="BQ175" t="inlineStr"/>
+      <c r="BR175" t="inlineStr"/>
+      <c r="BS175" t="inlineStr"/>
+      <c r="BT175" t="inlineStr"/>
+      <c r="BU175" t="inlineStr"/>
+      <c r="BV175" t="inlineStr"/>
+      <c r="BW175" t="inlineStr"/>
+      <c r="BX175" t="inlineStr"/>
+      <c r="BY175" t="inlineStr"/>
+      <c r="BZ175" t="inlineStr"/>
+      <c r="CA175" t="inlineStr"/>
+      <c r="CB175" t="inlineStr"/>
+      <c r="CC175" t="inlineStr"/>
+      <c r="CD175" t="inlineStr"/>
+      <c r="CE175" t="inlineStr"/>
+      <c r="CF175" t="inlineStr"/>
+      <c r="CG175" t="inlineStr"/>
+      <c r="CH175" t="inlineStr"/>
+      <c r="CI175" t="inlineStr"/>
+      <c r="CJ175" t="inlineStr"/>
+      <c r="CK175" t="inlineStr"/>
+      <c r="CL175" t="inlineStr"/>
+      <c r="CM175" t="inlineStr"/>
+      <c r="CN175" t="inlineStr"/>
+      <c r="CO175" t="inlineStr"/>
+      <c r="CP175" t="inlineStr"/>
+      <c r="CQ175" t="inlineStr"/>
+      <c r="CR175" t="inlineStr"/>
+      <c r="CS175" t="inlineStr"/>
+      <c r="CT175" t="inlineStr"/>
+      <c r="CU175" t="inlineStr"/>
+      <c r="CV175" t="inlineStr"/>
+      <c r="CW175" t="inlineStr"/>
+      <c r="CX175" t="inlineStr"/>
+      <c r="CY175" t="inlineStr"/>
+      <c r="CZ175" t="inlineStr"/>
+      <c r="DA175" t="inlineStr"/>
+      <c r="DB175" t="inlineStr"/>
+      <c r="DC175" t="inlineStr"/>
+      <c r="DD175" t="inlineStr"/>
+      <c r="DE175" t="inlineStr"/>
+      <c r="DF175" t="inlineStr"/>
+      <c r="DG175" t="inlineStr"/>
+      <c r="DH175" t="inlineStr"/>
+      <c r="DI175" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>538</v>
+      </c>
+      <c r="B176" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C176" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>AMÉRICAS</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
+      <c r="O176" t="inlineStr"/>
+      <c r="P176" t="inlineStr"/>
+      <c r="Q176" t="inlineStr"/>
+      <c r="R176" t="inlineStr"/>
+      <c r="S176" t="inlineStr"/>
+      <c r="T176" t="inlineStr"/>
+      <c r="U176" t="inlineStr"/>
+      <c r="V176" t="inlineStr"/>
+      <c r="W176" t="n">
+        <v>83744354</v>
+      </c>
+      <c r="X176" t="inlineStr">
+        <is>
+          <t>ANDRESSA DE MORAES GONÇALVES</t>
+        </is>
+      </c>
+      <c r="Y176" t="n">
+        <v>13448759716</v>
+      </c>
+      <c r="Z176" s="1" t="n">
+        <v>32159</v>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>Rio de janeiro</t>
+        </is>
+      </c>
+      <c r="AD176" t="n">
+        <v>400</v>
+      </c>
+      <c r="AE176" t="n">
+        <v>21973179293</v>
+      </c>
+      <c r="AF176" t="inlineStr">
+        <is>
+          <t>Emagrecimento</t>
+        </is>
+      </c>
+      <c r="AG176" t="inlineStr"/>
+      <c r="AH176" t="inlineStr"/>
+      <c r="AI176" t="inlineStr"/>
+      <c r="AJ176" t="inlineStr"/>
+      <c r="AK176" t="inlineStr"/>
+      <c r="AL176" t="inlineStr"/>
+      <c r="AM176" t="inlineStr"/>
+      <c r="AN176" t="inlineStr"/>
+      <c r="AO176" t="inlineStr"/>
+      <c r="AP176" t="inlineStr"/>
+      <c r="AQ176" t="inlineStr"/>
+      <c r="AR176" t="inlineStr"/>
+      <c r="AS176" t="inlineStr"/>
+      <c r="AT176" t="inlineStr"/>
+      <c r="AU176" t="inlineStr"/>
+      <c r="AV176" t="inlineStr"/>
+      <c r="AW176" t="inlineStr"/>
+      <c r="AX176" t="inlineStr"/>
+      <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr"/>
+      <c r="BA176" t="inlineStr"/>
+      <c r="BB176" t="inlineStr"/>
+      <c r="BC176" t="inlineStr"/>
+      <c r="BD176" t="inlineStr"/>
+      <c r="BE176" t="inlineStr"/>
+      <c r="BF176" t="inlineStr"/>
+      <c r="BG176" t="inlineStr"/>
+      <c r="BH176" t="inlineStr"/>
+      <c r="BI176" t="inlineStr"/>
+      <c r="BJ176" t="inlineStr"/>
+      <c r="BK176" t="inlineStr"/>
+      <c r="BL176" t="inlineStr"/>
+      <c r="BM176" t="inlineStr"/>
+      <c r="BN176" t="inlineStr"/>
+      <c r="BO176" t="inlineStr"/>
+      <c r="BP176" t="inlineStr"/>
+      <c r="BQ176" t="inlineStr"/>
+      <c r="BR176" t="inlineStr"/>
+      <c r="BS176" t="inlineStr"/>
+      <c r="BT176" t="inlineStr"/>
+      <c r="BU176" t="inlineStr"/>
+      <c r="BV176" t="inlineStr"/>
+      <c r="BW176" t="inlineStr"/>
+      <c r="BX176" t="inlineStr"/>
+      <c r="BY176" t="inlineStr"/>
+      <c r="BZ176" t="inlineStr"/>
+      <c r="CA176" t="inlineStr"/>
+      <c r="CB176" t="inlineStr"/>
+      <c r="CC176" t="inlineStr"/>
+      <c r="CD176" t="inlineStr"/>
+      <c r="CE176" t="inlineStr"/>
+      <c r="CF176" t="inlineStr"/>
+      <c r="CG176" t="inlineStr"/>
+      <c r="CH176" t="inlineStr"/>
+      <c r="CI176" t="inlineStr"/>
+      <c r="CJ176" t="inlineStr"/>
+      <c r="CK176" t="inlineStr"/>
+      <c r="CL176" t="inlineStr"/>
+      <c r="CM176" t="inlineStr"/>
+      <c r="CN176" t="inlineStr"/>
+      <c r="CO176" t="inlineStr"/>
+      <c r="CP176" t="inlineStr"/>
+      <c r="CQ176" t="inlineStr"/>
+      <c r="CR176" t="inlineStr"/>
+      <c r="CS176" t="inlineStr"/>
+      <c r="CT176" t="inlineStr"/>
+      <c r="CU176" t="inlineStr"/>
+      <c r="CV176" t="inlineStr"/>
+      <c r="CW176" t="inlineStr"/>
+      <c r="CX176" t="inlineStr"/>
+      <c r="CY176" t="inlineStr"/>
+      <c r="CZ176" t="inlineStr"/>
+      <c r="DA176" t="inlineStr"/>
+      <c r="DB176" t="inlineStr"/>
+      <c r="DC176" t="inlineStr"/>
+      <c r="DD176" t="inlineStr"/>
+      <c r="DE176" t="inlineStr"/>
+      <c r="DF176" t="inlineStr"/>
+      <c r="DG176" t="inlineStr"/>
+      <c r="DH176" t="inlineStr"/>
+      <c r="DI176" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>539</v>
+      </c>
+      <c r="B177" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C177" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>AMÉRICAS</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
+      <c r="O177" t="inlineStr"/>
+      <c r="P177" t="inlineStr"/>
+      <c r="Q177" t="inlineStr"/>
+      <c r="R177" t="inlineStr"/>
+      <c r="S177" t="inlineStr"/>
+      <c r="T177" t="inlineStr"/>
+      <c r="U177" t="inlineStr"/>
+      <c r="V177" t="inlineStr"/>
+      <c r="W177" t="n">
+        <v>93964396</v>
+      </c>
+      <c r="X177" t="inlineStr">
+        <is>
+          <t>VICTOR HUGO CURI CARNEIRO</t>
+        </is>
+      </c>
+      <c r="Y177" t="n">
+        <v>16611905707</v>
+      </c>
+      <c r="Z177" s="1" t="n">
+        <v>34427</v>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="AD177" t="n">
+        <v>600</v>
+      </c>
+      <c r="AE177" t="n">
+        <v>21987618579</v>
+      </c>
+      <c r="AF177" t="inlineStr">
+        <is>
+          <t>Emagrecimento</t>
+        </is>
+      </c>
+      <c r="AG177" t="inlineStr"/>
+      <c r="AH177" t="inlineStr"/>
+      <c r="AI177" t="inlineStr"/>
+      <c r="AJ177" t="inlineStr"/>
+      <c r="AK177" t="inlineStr"/>
+      <c r="AL177" t="inlineStr"/>
+      <c r="AM177" t="inlineStr"/>
+      <c r="AN177" t="inlineStr"/>
+      <c r="AO177" t="inlineStr"/>
+      <c r="AP177" t="inlineStr"/>
+      <c r="AQ177" t="inlineStr"/>
+      <c r="AR177" t="inlineStr"/>
+      <c r="AS177" t="inlineStr"/>
+      <c r="AT177" t="inlineStr"/>
+      <c r="AU177" t="inlineStr"/>
+      <c r="AV177" t="inlineStr"/>
+      <c r="AW177" t="inlineStr"/>
+      <c r="AX177" t="inlineStr"/>
+      <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr"/>
+      <c r="BA177" t="inlineStr"/>
+      <c r="BB177" t="inlineStr"/>
+      <c r="BC177" t="inlineStr"/>
+      <c r="BD177" t="inlineStr"/>
+      <c r="BE177" t="inlineStr"/>
+      <c r="BF177" t="inlineStr"/>
+      <c r="BG177" t="inlineStr"/>
+      <c r="BH177" t="inlineStr"/>
+      <c r="BI177" t="inlineStr"/>
+      <c r="BJ177" t="inlineStr"/>
+      <c r="BK177" t="inlineStr"/>
+      <c r="BL177" t="inlineStr"/>
+      <c r="BM177" t="inlineStr"/>
+      <c r="BN177" t="inlineStr"/>
+      <c r="BO177" t="inlineStr"/>
+      <c r="BP177" t="inlineStr"/>
+      <c r="BQ177" t="inlineStr"/>
+      <c r="BR177" t="inlineStr"/>
+      <c r="BS177" t="inlineStr"/>
+      <c r="BT177" t="inlineStr"/>
+      <c r="BU177" t="inlineStr"/>
+      <c r="BV177" t="inlineStr"/>
+      <c r="BW177" t="inlineStr"/>
+      <c r="BX177" t="inlineStr"/>
+      <c r="BY177" t="inlineStr"/>
+      <c r="BZ177" t="inlineStr"/>
+      <c r="CA177" t="inlineStr"/>
+      <c r="CB177" t="inlineStr"/>
+      <c r="CC177" t="inlineStr"/>
+      <c r="CD177" t="inlineStr"/>
+      <c r="CE177" t="inlineStr"/>
+      <c r="CF177" t="inlineStr"/>
+      <c r="CG177" t="inlineStr"/>
+      <c r="CH177" t="inlineStr"/>
+      <c r="CI177" t="inlineStr"/>
+      <c r="CJ177" t="inlineStr"/>
+      <c r="CK177" t="inlineStr"/>
+      <c r="CL177" t="inlineStr"/>
+      <c r="CM177" t="inlineStr"/>
+      <c r="CN177" t="inlineStr"/>
+      <c r="CO177" t="inlineStr"/>
+      <c r="CP177" t="inlineStr"/>
+      <c r="CQ177" t="inlineStr"/>
+      <c r="CR177" t="inlineStr"/>
+      <c r="CS177" t="inlineStr"/>
+      <c r="CT177" t="inlineStr"/>
+      <c r="CU177" t="inlineStr"/>
+      <c r="CV177" t="inlineStr"/>
+      <c r="CW177" t="inlineStr"/>
+      <c r="CX177" t="inlineStr"/>
+      <c r="CY177" t="inlineStr"/>
+      <c r="CZ177" t="inlineStr"/>
+      <c r="DA177" t="inlineStr"/>
+      <c r="DB177" t="inlineStr"/>
+      <c r="DC177" t="inlineStr"/>
+      <c r="DD177" t="inlineStr"/>
+      <c r="DE177" t="inlineStr"/>
+      <c r="DF177" t="inlineStr"/>
+      <c r="DG177" t="inlineStr"/>
+      <c r="DH177" t="inlineStr"/>
+      <c r="DI177" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>540</v>
+      </c>
+      <c r="B178" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C178" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>AMÉRICAS</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
+      <c r="O178" t="inlineStr"/>
+      <c r="P178" t="inlineStr"/>
+      <c r="Q178" t="inlineStr"/>
+      <c r="R178" t="inlineStr"/>
+      <c r="S178" t="inlineStr"/>
+      <c r="T178" t="inlineStr"/>
+      <c r="U178" t="inlineStr"/>
+      <c r="V178" t="inlineStr"/>
+      <c r="W178" t="n">
+        <v>93899663</v>
+      </c>
+      <c r="X178" t="inlineStr">
+        <is>
+          <t>ANNA BEATRIZ BORGES DOS SANTOS FERREIRA</t>
+        </is>
+      </c>
+      <c r="Y178" t="n">
+        <v>21203269757</v>
+      </c>
+      <c r="Z178" s="1" t="n">
+        <v>37901</v>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="AD178" t="n">
+        <v>450</v>
+      </c>
+      <c r="AE178" t="n">
+        <v>21968899982</v>
+      </c>
+      <c r="AF178" t="inlineStr">
+        <is>
+          <t>Emagrecimento</t>
+        </is>
+      </c>
+      <c r="AG178" t="inlineStr"/>
+      <c r="AH178" t="inlineStr"/>
+      <c r="AI178" t="inlineStr"/>
+      <c r="AJ178" t="inlineStr"/>
+      <c r="AK178" t="inlineStr"/>
+      <c r="AL178" t="inlineStr"/>
+      <c r="AM178" t="inlineStr"/>
+      <c r="AN178" t="inlineStr"/>
+      <c r="AO178" t="inlineStr"/>
+      <c r="AP178" t="inlineStr"/>
+      <c r="AQ178" t="inlineStr"/>
+      <c r="AR178" t="inlineStr"/>
+      <c r="AS178" t="inlineStr"/>
+      <c r="AT178" t="inlineStr"/>
+      <c r="AU178" t="inlineStr"/>
+      <c r="AV178" t="inlineStr"/>
+      <c r="AW178" t="inlineStr"/>
+      <c r="AX178" t="inlineStr"/>
+      <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr"/>
+      <c r="BA178" t="inlineStr"/>
+      <c r="BB178" t="inlineStr"/>
+      <c r="BC178" t="inlineStr"/>
+      <c r="BD178" t="inlineStr"/>
+      <c r="BE178" t="inlineStr"/>
+      <c r="BF178" t="inlineStr"/>
+      <c r="BG178" t="inlineStr"/>
+      <c r="BH178" t="inlineStr"/>
+      <c r="BI178" t="inlineStr"/>
+      <c r="BJ178" t="inlineStr"/>
+      <c r="BK178" t="inlineStr"/>
+      <c r="BL178" t="inlineStr"/>
+      <c r="BM178" t="inlineStr"/>
+      <c r="BN178" t="inlineStr"/>
+      <c r="BO178" t="inlineStr"/>
+      <c r="BP178" t="inlineStr"/>
+      <c r="BQ178" t="inlineStr"/>
+      <c r="BR178" t="inlineStr"/>
+      <c r="BS178" t="inlineStr"/>
+      <c r="BT178" t="inlineStr"/>
+      <c r="BU178" t="inlineStr"/>
+      <c r="BV178" t="inlineStr"/>
+      <c r="BW178" t="inlineStr"/>
+      <c r="BX178" t="inlineStr"/>
+      <c r="BY178" t="inlineStr"/>
+      <c r="BZ178" t="inlineStr"/>
+      <c r="CA178" t="inlineStr"/>
+      <c r="CB178" t="inlineStr"/>
+      <c r="CC178" t="inlineStr"/>
+      <c r="CD178" t="inlineStr"/>
+      <c r="CE178" t="inlineStr"/>
+      <c r="CF178" t="inlineStr"/>
+      <c r="CG178" t="inlineStr"/>
+      <c r="CH178" t="inlineStr"/>
+      <c r="CI178" t="inlineStr"/>
+      <c r="CJ178" t="inlineStr"/>
+      <c r="CK178" t="inlineStr"/>
+      <c r="CL178" t="inlineStr"/>
+      <c r="CM178" t="inlineStr"/>
+      <c r="CN178" t="inlineStr"/>
+      <c r="CO178" t="inlineStr"/>
+      <c r="CP178" t="inlineStr"/>
+      <c r="CQ178" t="inlineStr"/>
+      <c r="CR178" t="inlineStr"/>
+      <c r="CS178" t="inlineStr"/>
+      <c r="CT178" t="inlineStr"/>
+      <c r="CU178" t="inlineStr"/>
+      <c r="CV178" t="inlineStr"/>
+      <c r="CW178" t="inlineStr"/>
+      <c r="CX178" t="inlineStr"/>
+      <c r="CY178" t="inlineStr"/>
+      <c r="CZ178" t="inlineStr"/>
+      <c r="DA178" t="inlineStr"/>
+      <c r="DB178" t="inlineStr"/>
+      <c r="DC178" t="inlineStr"/>
+      <c r="DD178" t="inlineStr"/>
+      <c r="DE178" t="inlineStr"/>
+      <c r="DF178" t="inlineStr"/>
+      <c r="DG178" t="inlineStr"/>
+      <c r="DH178" t="inlineStr"/>
+      <c r="DI178" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>541</v>
+      </c>
+      <c r="B179" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C179" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>AMÉRICAS</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
+      <c r="O179" t="inlineStr"/>
+      <c r="P179" t="inlineStr"/>
+      <c r="Q179" t="inlineStr"/>
+      <c r="R179" t="inlineStr"/>
+      <c r="S179" t="inlineStr"/>
+      <c r="T179" t="inlineStr"/>
+      <c r="U179" t="inlineStr"/>
+      <c r="V179" t="inlineStr"/>
+      <c r="W179" t="n">
+        <v>971951705</v>
+      </c>
+      <c r="X179" t="inlineStr">
+        <is>
+          <t>INGRID CRISTINE LIMA BOREL</t>
+        </is>
+      </c>
+      <c r="Y179" t="n">
+        <v>7227816796</v>
+      </c>
+      <c r="Z179" s="1" t="n">
+        <v>26634</v>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="AD179" t="n">
+        <v>400</v>
+      </c>
+      <c r="AE179" t="n">
+        <v>21998657128</v>
+      </c>
+      <c r="AF179" t="inlineStr">
+        <is>
+          <t>Emagrecimento</t>
+        </is>
+      </c>
+      <c r="AG179" t="inlineStr"/>
+      <c r="AH179" t="inlineStr"/>
+      <c r="AI179" t="inlineStr"/>
+      <c r="AJ179" t="inlineStr"/>
+      <c r="AK179" t="inlineStr"/>
+      <c r="AL179" t="inlineStr"/>
+      <c r="AM179" t="inlineStr"/>
+      <c r="AN179" t="inlineStr"/>
+      <c r="AO179" t="inlineStr"/>
+      <c r="AP179" t="inlineStr"/>
+      <c r="AQ179" t="inlineStr"/>
+      <c r="AR179" t="inlineStr"/>
+      <c r="AS179" t="inlineStr"/>
+      <c r="AT179" t="inlineStr"/>
+      <c r="AU179" t="inlineStr"/>
+      <c r="AV179" t="inlineStr"/>
+      <c r="AW179" t="inlineStr"/>
+      <c r="AX179" t="inlineStr"/>
+      <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr"/>
+      <c r="BA179" t="inlineStr"/>
+      <c r="BB179" t="inlineStr"/>
+      <c r="BC179" t="inlineStr"/>
+      <c r="BD179" t="inlineStr"/>
+      <c r="BE179" t="inlineStr"/>
+      <c r="BF179" t="inlineStr"/>
+      <c r="BG179" t="inlineStr"/>
+      <c r="BH179" t="inlineStr"/>
+      <c r="BI179" t="inlineStr"/>
+      <c r="BJ179" t="inlineStr"/>
+      <c r="BK179" t="inlineStr"/>
+      <c r="BL179" t="inlineStr"/>
+      <c r="BM179" t="inlineStr"/>
+      <c r="BN179" t="inlineStr"/>
+      <c r="BO179" t="inlineStr"/>
+      <c r="BP179" t="inlineStr"/>
+      <c r="BQ179" t="inlineStr"/>
+      <c r="BR179" t="inlineStr"/>
+      <c r="BS179" t="inlineStr"/>
+      <c r="BT179" t="inlineStr"/>
+      <c r="BU179" t="inlineStr"/>
+      <c r="BV179" t="inlineStr"/>
+      <c r="BW179" t="inlineStr"/>
+      <c r="BX179" t="inlineStr"/>
+      <c r="BY179" t="inlineStr"/>
+      <c r="BZ179" t="inlineStr"/>
+      <c r="CA179" t="inlineStr"/>
+      <c r="CB179" t="inlineStr"/>
+      <c r="CC179" t="inlineStr"/>
+      <c r="CD179" t="inlineStr"/>
+      <c r="CE179" t="inlineStr"/>
+      <c r="CF179" t="inlineStr"/>
+      <c r="CG179" t="inlineStr"/>
+      <c r="CH179" t="inlineStr"/>
+      <c r="CI179" t="inlineStr"/>
+      <c r="CJ179" t="inlineStr"/>
+      <c r="CK179" t="inlineStr"/>
+      <c r="CL179" t="inlineStr"/>
+      <c r="CM179" t="inlineStr"/>
+      <c r="CN179" t="inlineStr"/>
+      <c r="CO179" t="inlineStr"/>
+      <c r="CP179" t="inlineStr"/>
+      <c r="CQ179" t="inlineStr"/>
+      <c r="CR179" t="inlineStr"/>
+      <c r="CS179" t="inlineStr"/>
+      <c r="CT179" t="inlineStr"/>
+      <c r="CU179" t="inlineStr"/>
+      <c r="CV179" t="inlineStr"/>
+      <c r="CW179" t="inlineStr"/>
+      <c r="CX179" t="inlineStr"/>
+      <c r="CY179" t="inlineStr"/>
+      <c r="CZ179" t="inlineStr"/>
+      <c r="DA179" t="inlineStr"/>
+      <c r="DB179" t="inlineStr"/>
+      <c r="DC179" t="inlineStr"/>
+      <c r="DD179" t="inlineStr"/>
+      <c r="DE179" t="inlineStr"/>
+      <c r="DF179" t="inlineStr"/>
+      <c r="DG179" t="inlineStr"/>
+      <c r="DH179" t="inlineStr"/>
+      <c r="DI179" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>542</v>
+      </c>
+      <c r="B180" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C180" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>DESOSPITALIZAÇÃO AMIL - TIME ERIC</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
+      <c r="O180" t="inlineStr"/>
+      <c r="P180" t="inlineStr"/>
+      <c r="Q180" t="inlineStr"/>
+      <c r="R180" t="inlineStr"/>
+      <c r="S180" t="inlineStr"/>
+      <c r="T180" t="inlineStr"/>
+      <c r="U180" t="inlineStr"/>
+      <c r="V180" t="inlineStr"/>
+      <c r="W180" t="inlineStr"/>
+      <c r="X180" t="inlineStr"/>
+      <c r="Y180" t="inlineStr"/>
+      <c r="Z180" t="inlineStr"/>
+      <c r="AA180" t="inlineStr"/>
+      <c r="AB180" t="inlineStr"/>
+      <c r="AC180" t="inlineStr"/>
+      <c r="AD180" t="inlineStr"/>
+      <c r="AE180" t="inlineStr"/>
+      <c r="AF180" t="inlineStr"/>
+      <c r="AG180" t="inlineStr"/>
+      <c r="AH180" t="inlineStr"/>
+      <c r="AI180" t="inlineStr"/>
+      <c r="AJ180" t="inlineStr"/>
+      <c r="AK180" t="n">
+        <v>89903957</v>
+      </c>
+      <c r="AL180" t="inlineStr">
+        <is>
+          <t>BEATRIZ DE OLIVEIRA PINTO DA SILVA</t>
+        </is>
+      </c>
+      <c r="AM180" t="inlineStr">
+        <is>
+          <t>161.534.177-36</t>
+        </is>
+      </c>
+      <c r="AN180" s="1" t="n">
+        <v>39692</v>
+      </c>
+      <c r="AO180" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="AP180" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="AQ180" t="inlineStr">
+        <is>
+          <t>DUQUE DE CAXIAS</t>
+        </is>
+      </c>
+      <c r="AR180" t="inlineStr">
+        <is>
+          <t>AMIL COLABORADOR QC NAC COPART PJ ADM</t>
+        </is>
+      </c>
+      <c r="AS180" t="inlineStr">
+        <is>
+          <t>21-970559020</t>
+        </is>
+      </c>
+      <c r="AT180" t="inlineStr">
+        <is>
+          <t>Saúde Mental</t>
+        </is>
+      </c>
+      <c r="AU180" t="inlineStr">
+        <is>
+          <t>Busca preventiva por bem-estar</t>
+        </is>
+      </c>
+      <c r="AV180" t="inlineStr"/>
+      <c r="AW180" t="inlineStr"/>
+      <c r="AX180" t="inlineStr"/>
+      <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr"/>
+      <c r="BA180" t="inlineStr"/>
+      <c r="BB180" t="inlineStr"/>
+      <c r="BC180" t="inlineStr"/>
+      <c r="BD180" t="inlineStr"/>
+      <c r="BE180" t="inlineStr"/>
+      <c r="BF180" t="inlineStr"/>
+      <c r="BG180" t="inlineStr"/>
+      <c r="BH180" t="inlineStr"/>
+      <c r="BI180" t="inlineStr"/>
+      <c r="BJ180" t="inlineStr"/>
+      <c r="BK180" t="inlineStr"/>
+      <c r="BL180" t="inlineStr"/>
+      <c r="BM180" t="inlineStr"/>
+      <c r="BN180" t="inlineStr"/>
+      <c r="BO180" t="inlineStr"/>
+      <c r="BP180" t="inlineStr"/>
+      <c r="BQ180" t="inlineStr"/>
+      <c r="BR180" t="inlineStr"/>
+      <c r="BS180" t="inlineStr"/>
+      <c r="BT180" t="inlineStr"/>
+      <c r="BU180" t="inlineStr"/>
+      <c r="BV180" t="inlineStr"/>
+      <c r="BW180" t="inlineStr"/>
+      <c r="BX180" t="inlineStr"/>
+      <c r="BY180" t="inlineStr"/>
+      <c r="BZ180" t="inlineStr"/>
+      <c r="CA180" t="inlineStr"/>
+      <c r="CB180" t="inlineStr"/>
+      <c r="CC180" t="inlineStr"/>
+      <c r="CD180" t="inlineStr"/>
+      <c r="CE180" t="inlineStr"/>
+      <c r="CF180" t="inlineStr"/>
+      <c r="CG180" t="inlineStr"/>
+      <c r="CH180" t="inlineStr"/>
+      <c r="CI180" t="inlineStr"/>
+      <c r="CJ180" t="inlineStr"/>
+      <c r="CK180" t="inlineStr"/>
+      <c r="CL180" t="inlineStr"/>
+      <c r="CM180" t="inlineStr"/>
+      <c r="CN180" t="inlineStr"/>
+      <c r="CO180" t="inlineStr"/>
+      <c r="CP180" t="inlineStr"/>
+      <c r="CQ180" t="inlineStr"/>
+      <c r="CR180" t="inlineStr"/>
+      <c r="CS180" t="inlineStr"/>
+      <c r="CT180" t="inlineStr"/>
+      <c r="CU180" t="inlineStr"/>
+      <c r="CV180" t="inlineStr"/>
+      <c r="CW180" t="inlineStr"/>
+      <c r="CX180" t="inlineStr"/>
+      <c r="CY180" t="inlineStr"/>
+      <c r="CZ180" t="inlineStr"/>
+      <c r="DA180" t="inlineStr"/>
+      <c r="DB180" t="inlineStr"/>
+      <c r="DC180" t="inlineStr"/>
+      <c r="DD180" t="inlineStr"/>
+      <c r="DE180" t="inlineStr"/>
+      <c r="DF180" t="inlineStr"/>
+      <c r="DG180" t="inlineStr"/>
+      <c r="DH180" t="inlineStr"/>
+      <c r="DI180" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>543</v>
+      </c>
+      <c r="B181" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C181" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>AMÉRICAS</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr"/>
+      <c r="P181" t="inlineStr"/>
+      <c r="Q181" t="inlineStr"/>
+      <c r="R181" t="inlineStr"/>
+      <c r="S181" t="inlineStr"/>
+      <c r="T181" t="inlineStr"/>
+      <c r="U181" t="inlineStr"/>
+      <c r="V181" t="inlineStr"/>
+      <c r="W181" t="n">
+        <v>93745317</v>
+      </c>
+      <c r="X181" t="inlineStr">
+        <is>
+          <t>NICOLLE ANTUNES PEREIRA KOCH</t>
+        </is>
+      </c>
+      <c r="Y181" t="n">
+        <v>18929964729</v>
+      </c>
+      <c r="Z181" s="1" t="n">
+        <v>36394</v>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="AD181" t="n">
+        <v>450</v>
+      </c>
+      <c r="AE181" t="n">
+        <v>21981160720</v>
+      </c>
+      <c r="AF181" t="inlineStr">
+        <is>
+          <t>Emagrecimento</t>
+        </is>
+      </c>
+      <c r="AG181" t="inlineStr"/>
+      <c r="AH181" t="inlineStr"/>
+      <c r="AI181" t="inlineStr"/>
+      <c r="AJ181" t="inlineStr"/>
+      <c r="AK181" t="inlineStr"/>
+      <c r="AL181" t="inlineStr"/>
+      <c r="AM181" t="inlineStr"/>
+      <c r="AN181" t="inlineStr"/>
+      <c r="AO181" t="inlineStr"/>
+      <c r="AP181" t="inlineStr"/>
+      <c r="AQ181" t="inlineStr"/>
+      <c r="AR181" t="inlineStr"/>
+      <c r="AS181" t="inlineStr"/>
+      <c r="AT181" t="inlineStr"/>
+      <c r="AU181" t="inlineStr"/>
+      <c r="AV181" t="inlineStr"/>
+      <c r="AW181" t="inlineStr"/>
+      <c r="AX181" t="inlineStr"/>
+      <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr"/>
+      <c r="BA181" t="inlineStr"/>
+      <c r="BB181" t="inlineStr"/>
+      <c r="BC181" t="inlineStr"/>
+      <c r="BD181" t="inlineStr"/>
+      <c r="BE181" t="inlineStr"/>
+      <c r="BF181" t="inlineStr"/>
+      <c r="BG181" t="inlineStr"/>
+      <c r="BH181" t="inlineStr"/>
+      <c r="BI181" t="inlineStr"/>
+      <c r="BJ181" t="inlineStr"/>
+      <c r="BK181" t="inlineStr"/>
+      <c r="BL181" t="inlineStr"/>
+      <c r="BM181" t="inlineStr"/>
+      <c r="BN181" t="inlineStr"/>
+      <c r="BO181" t="inlineStr"/>
+      <c r="BP181" t="inlineStr"/>
+      <c r="BQ181" t="inlineStr"/>
+      <c r="BR181" t="inlineStr"/>
+      <c r="BS181" t="inlineStr"/>
+      <c r="BT181" t="inlineStr"/>
+      <c r="BU181" t="inlineStr"/>
+      <c r="BV181" t="inlineStr"/>
+      <c r="BW181" t="inlineStr"/>
+      <c r="BX181" t="inlineStr"/>
+      <c r="BY181" t="inlineStr"/>
+      <c r="BZ181" t="inlineStr"/>
+      <c r="CA181" t="inlineStr"/>
+      <c r="CB181" t="inlineStr"/>
+      <c r="CC181" t="inlineStr"/>
+      <c r="CD181" t="inlineStr"/>
+      <c r="CE181" t="inlineStr"/>
+      <c r="CF181" t="inlineStr"/>
+      <c r="CG181" t="inlineStr"/>
+      <c r="CH181" t="inlineStr"/>
+      <c r="CI181" t="inlineStr"/>
+      <c r="CJ181" t="inlineStr"/>
+      <c r="CK181" t="inlineStr"/>
+      <c r="CL181" t="inlineStr"/>
+      <c r="CM181" t="inlineStr"/>
+      <c r="CN181" t="inlineStr"/>
+      <c r="CO181" t="inlineStr"/>
+      <c r="CP181" t="inlineStr"/>
+      <c r="CQ181" t="inlineStr"/>
+      <c r="CR181" t="inlineStr"/>
+      <c r="CS181" t="inlineStr"/>
+      <c r="CT181" t="inlineStr"/>
+      <c r="CU181" t="inlineStr"/>
+      <c r="CV181" t="inlineStr"/>
+      <c r="CW181" t="inlineStr"/>
+      <c r="CX181" t="inlineStr"/>
+      <c r="CY181" t="inlineStr"/>
+      <c r="CZ181" t="inlineStr"/>
+      <c r="DA181" t="inlineStr"/>
+      <c r="DB181" t="inlineStr"/>
+      <c r="DC181" t="inlineStr"/>
+      <c r="DD181" t="inlineStr"/>
+      <c r="DE181" t="inlineStr"/>
+      <c r="DF181" t="inlineStr"/>
+      <c r="DG181" t="inlineStr"/>
+      <c r="DH181" t="inlineStr"/>
+      <c r="DI181" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>544</v>
+      </c>
+      <c r="B182" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C182" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>DESOSPITALIZAÇÃO AMIL - TIME ERIC</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
+      <c r="O182" t="inlineStr"/>
+      <c r="P182" t="inlineStr"/>
+      <c r="Q182" t="inlineStr"/>
+      <c r="R182" t="inlineStr"/>
+      <c r="S182" t="inlineStr"/>
+      <c r="T182" t="inlineStr"/>
+      <c r="U182" t="inlineStr"/>
+      <c r="V182" t="inlineStr"/>
+      <c r="W182" t="inlineStr"/>
+      <c r="X182" t="inlineStr"/>
+      <c r="Y182" t="inlineStr"/>
+      <c r="Z182" t="inlineStr"/>
+      <c r="AA182" t="inlineStr"/>
+      <c r="AB182" t="inlineStr"/>
+      <c r="AC182" t="inlineStr"/>
+      <c r="AD182" t="inlineStr"/>
+      <c r="AE182" t="inlineStr"/>
+      <c r="AF182" t="inlineStr"/>
+      <c r="AG182" t="inlineStr"/>
+      <c r="AH182" t="inlineStr"/>
+      <c r="AI182" t="inlineStr"/>
+      <c r="AJ182" t="inlineStr"/>
+      <c r="AK182" t="n">
+        <v>89903956</v>
+      </c>
+      <c r="AL182" t="inlineStr">
+        <is>
+          <t>EDVANE MEIRELES DE OLIVEIRA PINTO DA SILVA</t>
+        </is>
+      </c>
+      <c r="AM182" t="inlineStr">
+        <is>
+          <t>126.024.197-10</t>
+        </is>
+      </c>
+      <c r="AN182" s="1" t="n">
+        <v>32500</v>
+      </c>
+      <c r="AO182" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="AP182" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="AQ182" t="inlineStr">
+        <is>
+          <t>DUQUE DE CAXIAS</t>
+        </is>
+      </c>
+      <c r="AR182" t="inlineStr">
+        <is>
+          <t>AMIL COLABORADOR QC NAC COPART PJ ADM</t>
+        </is>
+      </c>
+      <c r="AS182" t="inlineStr">
+        <is>
+          <t>21-970559020</t>
+        </is>
+      </c>
+      <c r="AT182" t="inlineStr">
+        <is>
+          <t>Saúde Mental</t>
+        </is>
+      </c>
+      <c r="AU182" t="inlineStr">
+        <is>
+          <t>Busca preventiva por bem-estar</t>
+        </is>
+      </c>
+      <c r="AV182" t="inlineStr"/>
+      <c r="AW182" t="inlineStr"/>
+      <c r="AX182" t="inlineStr"/>
+      <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr"/>
+      <c r="BA182" t="inlineStr"/>
+      <c r="BB182" t="inlineStr"/>
+      <c r="BC182" t="inlineStr"/>
+      <c r="BD182" t="inlineStr"/>
+      <c r="BE182" t="inlineStr"/>
+      <c r="BF182" t="inlineStr"/>
+      <c r="BG182" t="inlineStr"/>
+      <c r="BH182" t="inlineStr"/>
+      <c r="BI182" t="inlineStr"/>
+      <c r="BJ182" t="inlineStr"/>
+      <c r="BK182" t="inlineStr"/>
+      <c r="BL182" t="inlineStr"/>
+      <c r="BM182" t="inlineStr"/>
+      <c r="BN182" t="inlineStr"/>
+      <c r="BO182" t="inlineStr"/>
+      <c r="BP182" t="inlineStr"/>
+      <c r="BQ182" t="inlineStr"/>
+      <c r="BR182" t="inlineStr"/>
+      <c r="BS182" t="inlineStr"/>
+      <c r="BT182" t="inlineStr"/>
+      <c r="BU182" t="inlineStr"/>
+      <c r="BV182" t="inlineStr"/>
+      <c r="BW182" t="inlineStr"/>
+      <c r="BX182" t="inlineStr"/>
+      <c r="BY182" t="inlineStr"/>
+      <c r="BZ182" t="inlineStr"/>
+      <c r="CA182" t="inlineStr"/>
+      <c r="CB182" t="inlineStr"/>
+      <c r="CC182" t="inlineStr"/>
+      <c r="CD182" t="inlineStr"/>
+      <c r="CE182" t="inlineStr"/>
+      <c r="CF182" t="inlineStr"/>
+      <c r="CG182" t="inlineStr"/>
+      <c r="CH182" t="inlineStr"/>
+      <c r="CI182" t="inlineStr"/>
+      <c r="CJ182" t="inlineStr"/>
+      <c r="CK182" t="inlineStr"/>
+      <c r="CL182" t="inlineStr"/>
+      <c r="CM182" t="inlineStr"/>
+      <c r="CN182" t="inlineStr"/>
+      <c r="CO182" t="inlineStr"/>
+      <c r="CP182" t="inlineStr"/>
+      <c r="CQ182" t="inlineStr"/>
+      <c r="CR182" t="inlineStr"/>
+      <c r="CS182" t="inlineStr"/>
+      <c r="CT182" t="inlineStr"/>
+      <c r="CU182" t="inlineStr"/>
+      <c r="CV182" t="inlineStr"/>
+      <c r="CW182" t="inlineStr"/>
+      <c r="CX182" t="inlineStr"/>
+      <c r="CY182" t="inlineStr"/>
+      <c r="CZ182" t="inlineStr"/>
+      <c r="DA182" t="inlineStr"/>
+      <c r="DB182" t="inlineStr"/>
+      <c r="DC182" t="inlineStr"/>
+      <c r="DD182" t="inlineStr"/>
+      <c r="DE182" t="inlineStr"/>
+      <c r="DF182" t="inlineStr"/>
+      <c r="DG182" t="inlineStr"/>
+      <c r="DH182" t="inlineStr"/>
+      <c r="DI182" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>545</v>
+      </c>
+      <c r="B183" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C183" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>AMÉRICAS</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr"/>
+      <c r="P183" t="inlineStr"/>
+      <c r="Q183" t="inlineStr"/>
+      <c r="R183" t="inlineStr"/>
+      <c r="S183" t="inlineStr"/>
+      <c r="T183" t="inlineStr"/>
+      <c r="U183" t="inlineStr"/>
+      <c r="V183" t="inlineStr"/>
+      <c r="W183" t="n">
+        <v>976967480</v>
+      </c>
+      <c r="X183" t="inlineStr">
+        <is>
+          <t>VICTORIA DA SILVA RIBEIRO</t>
+        </is>
+      </c>
+      <c r="Y183" t="n">
+        <v>16208427770</v>
+      </c>
+      <c r="Z183" s="1" t="n">
+        <v>35782</v>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="AD183" t="n">
+        <v>400</v>
+      </c>
+      <c r="AE183" t="n">
+        <v>21999078188</v>
+      </c>
+      <c r="AF183" t="inlineStr">
+        <is>
+          <t>Emagrecimento</t>
+        </is>
+      </c>
+      <c r="AG183" t="inlineStr"/>
+      <c r="AH183" t="inlineStr"/>
+      <c r="AI183" t="inlineStr"/>
+      <c r="AJ183" t="inlineStr"/>
+      <c r="AK183" t="inlineStr"/>
+      <c r="AL183" t="inlineStr"/>
+      <c r="AM183" t="inlineStr"/>
+      <c r="AN183" t="inlineStr"/>
+      <c r="AO183" t="inlineStr"/>
+      <c r="AP183" t="inlineStr"/>
+      <c r="AQ183" t="inlineStr"/>
+      <c r="AR183" t="inlineStr"/>
+      <c r="AS183" t="inlineStr"/>
+      <c r="AT183" t="inlineStr"/>
+      <c r="AU183" t="inlineStr"/>
+      <c r="AV183" t="inlineStr"/>
+      <c r="AW183" t="inlineStr"/>
+      <c r="AX183" t="inlineStr"/>
+      <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr"/>
+      <c r="BA183" t="inlineStr"/>
+      <c r="BB183" t="inlineStr"/>
+      <c r="BC183" t="inlineStr"/>
+      <c r="BD183" t="inlineStr"/>
+      <c r="BE183" t="inlineStr"/>
+      <c r="BF183" t="inlineStr"/>
+      <c r="BG183" t="inlineStr"/>
+      <c r="BH183" t="inlineStr"/>
+      <c r="BI183" t="inlineStr"/>
+      <c r="BJ183" t="inlineStr"/>
+      <c r="BK183" t="inlineStr"/>
+      <c r="BL183" t="inlineStr"/>
+      <c r="BM183" t="inlineStr"/>
+      <c r="BN183" t="inlineStr"/>
+      <c r="BO183" t="inlineStr"/>
+      <c r="BP183" t="inlineStr"/>
+      <c r="BQ183" t="inlineStr"/>
+      <c r="BR183" t="inlineStr"/>
+      <c r="BS183" t="inlineStr"/>
+      <c r="BT183" t="inlineStr"/>
+      <c r="BU183" t="inlineStr"/>
+      <c r="BV183" t="inlineStr"/>
+      <c r="BW183" t="inlineStr"/>
+      <c r="BX183" t="inlineStr"/>
+      <c r="BY183" t="inlineStr"/>
+      <c r="BZ183" t="inlineStr"/>
+      <c r="CA183" t="inlineStr"/>
+      <c r="CB183" t="inlineStr"/>
+      <c r="CC183" t="inlineStr"/>
+      <c r="CD183" t="inlineStr"/>
+      <c r="CE183" t="inlineStr"/>
+      <c r="CF183" t="inlineStr"/>
+      <c r="CG183" t="inlineStr"/>
+      <c r="CH183" t="inlineStr"/>
+      <c r="CI183" t="inlineStr"/>
+      <c r="CJ183" t="inlineStr"/>
+      <c r="CK183" t="inlineStr"/>
+      <c r="CL183" t="inlineStr"/>
+      <c r="CM183" t="inlineStr"/>
+      <c r="CN183" t="inlineStr"/>
+      <c r="CO183" t="inlineStr"/>
+      <c r="CP183" t="inlineStr"/>
+      <c r="CQ183" t="inlineStr"/>
+      <c r="CR183" t="inlineStr"/>
+      <c r="CS183" t="inlineStr"/>
+      <c r="CT183" t="inlineStr"/>
+      <c r="CU183" t="inlineStr"/>
+      <c r="CV183" t="inlineStr"/>
+      <c r="CW183" t="inlineStr"/>
+      <c r="CX183" t="inlineStr"/>
+      <c r="CY183" t="inlineStr"/>
+      <c r="CZ183" t="inlineStr"/>
+      <c r="DA183" t="inlineStr"/>
+      <c r="DB183" t="inlineStr"/>
+      <c r="DC183" t="inlineStr"/>
+      <c r="DD183" t="inlineStr"/>
+      <c r="DE183" t="inlineStr"/>
+      <c r="DF183" t="inlineStr"/>
+      <c r="DG183" t="inlineStr"/>
+      <c r="DH183" t="inlineStr"/>
+      <c r="DI183" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>546</v>
+      </c>
+      <c r="B184" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C184" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>AMÉRICAS</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr"/>
+      <c r="P184" t="inlineStr"/>
+      <c r="Q184" t="inlineStr"/>
+      <c r="R184" t="inlineStr"/>
+      <c r="S184" t="inlineStr"/>
+      <c r="T184" t="inlineStr"/>
+      <c r="U184" t="inlineStr"/>
+      <c r="V184" t="inlineStr"/>
+      <c r="W184" t="n">
+        <v>93942644</v>
+      </c>
+      <c r="X184" t="inlineStr">
+        <is>
+          <t>HUGO VIEIRA DE SA</t>
+        </is>
+      </c>
+      <c r="Y184" t="n">
+        <v>19289293705</v>
+      </c>
+      <c r="Z184" s="1" t="n">
+        <v>37005</v>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="AD184" t="n">
+        <v>450</v>
+      </c>
+      <c r="AE184" t="n">
+        <v>21965122393</v>
+      </c>
+      <c r="AF184" t="inlineStr">
+        <is>
+          <t>Emagrecimento</t>
+        </is>
+      </c>
+      <c r="AG184" t="inlineStr"/>
+      <c r="AH184" t="inlineStr"/>
+      <c r="AI184" t="inlineStr"/>
+      <c r="AJ184" t="inlineStr"/>
+      <c r="AK184" t="inlineStr"/>
+      <c r="AL184" t="inlineStr"/>
+      <c r="AM184" t="inlineStr"/>
+      <c r="AN184" t="inlineStr"/>
+      <c r="AO184" t="inlineStr"/>
+      <c r="AP184" t="inlineStr"/>
+      <c r="AQ184" t="inlineStr"/>
+      <c r="AR184" t="inlineStr"/>
+      <c r="AS184" t="inlineStr"/>
+      <c r="AT184" t="inlineStr"/>
+      <c r="AU184" t="inlineStr"/>
+      <c r="AV184" t="inlineStr"/>
+      <c r="AW184" t="inlineStr"/>
+      <c r="AX184" t="inlineStr"/>
+      <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr"/>
+      <c r="BA184" t="inlineStr"/>
+      <c r="BB184" t="inlineStr"/>
+      <c r="BC184" t="inlineStr"/>
+      <c r="BD184" t="inlineStr"/>
+      <c r="BE184" t="inlineStr"/>
+      <c r="BF184" t="inlineStr"/>
+      <c r="BG184" t="inlineStr"/>
+      <c r="BH184" t="inlineStr"/>
+      <c r="BI184" t="inlineStr"/>
+      <c r="BJ184" t="inlineStr"/>
+      <c r="BK184" t="inlineStr"/>
+      <c r="BL184" t="inlineStr"/>
+      <c r="BM184" t="inlineStr"/>
+      <c r="BN184" t="inlineStr"/>
+      <c r="BO184" t="inlineStr"/>
+      <c r="BP184" t="inlineStr"/>
+      <c r="BQ184" t="inlineStr"/>
+      <c r="BR184" t="inlineStr"/>
+      <c r="BS184" t="inlineStr"/>
+      <c r="BT184" t="inlineStr"/>
+      <c r="BU184" t="inlineStr"/>
+      <c r="BV184" t="inlineStr"/>
+      <c r="BW184" t="inlineStr"/>
+      <c r="BX184" t="inlineStr"/>
+      <c r="BY184" t="inlineStr"/>
+      <c r="BZ184" t="inlineStr"/>
+      <c r="CA184" t="inlineStr"/>
+      <c r="CB184" t="inlineStr"/>
+      <c r="CC184" t="inlineStr"/>
+      <c r="CD184" t="inlineStr"/>
+      <c r="CE184" t="inlineStr"/>
+      <c r="CF184" t="inlineStr"/>
+      <c r="CG184" t="inlineStr"/>
+      <c r="CH184" t="inlineStr"/>
+      <c r="CI184" t="inlineStr"/>
+      <c r="CJ184" t="inlineStr"/>
+      <c r="CK184" t="inlineStr"/>
+      <c r="CL184" t="inlineStr"/>
+      <c r="CM184" t="inlineStr"/>
+      <c r="CN184" t="inlineStr"/>
+      <c r="CO184" t="inlineStr"/>
+      <c r="CP184" t="inlineStr"/>
+      <c r="CQ184" t="inlineStr"/>
+      <c r="CR184" t="inlineStr"/>
+      <c r="CS184" t="inlineStr"/>
+      <c r="CT184" t="inlineStr"/>
+      <c r="CU184" t="inlineStr"/>
+      <c r="CV184" t="inlineStr"/>
+      <c r="CW184" t="inlineStr"/>
+      <c r="CX184" t="inlineStr"/>
+      <c r="CY184" t="inlineStr"/>
+      <c r="CZ184" t="inlineStr"/>
+      <c r="DA184" t="inlineStr"/>
+      <c r="DB184" t="inlineStr"/>
+      <c r="DC184" t="inlineStr"/>
+      <c r="DD184" t="inlineStr"/>
+      <c r="DE184" t="inlineStr"/>
+      <c r="DF184" t="inlineStr"/>
+      <c r="DG184" t="inlineStr"/>
+      <c r="DH184" t="inlineStr"/>
+      <c r="DI184" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>547</v>
+      </c>
+      <c r="B185" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C185" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>AMÉRICAS</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
+      <c r="O185" t="inlineStr"/>
+      <c r="P185" t="inlineStr"/>
+      <c r="Q185" t="inlineStr"/>
+      <c r="R185" t="inlineStr"/>
+      <c r="S185" t="inlineStr"/>
+      <c r="T185" t="inlineStr"/>
+      <c r="U185" t="inlineStr"/>
+      <c r="V185" t="inlineStr"/>
+      <c r="W185" t="n">
+        <v>96259247</v>
+      </c>
+      <c r="X185" t="inlineStr">
+        <is>
+          <t>PAULO SERGIO DOS SANTOS CRUZ</t>
+        </is>
+      </c>
+      <c r="Y185" t="n">
+        <v>3548403719</v>
+      </c>
+      <c r="Z185" s="1" t="n">
+        <v>27177</v>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="AD185" t="n">
+        <v>450</v>
+      </c>
+      <c r="AE185" t="n">
+        <v>21970460243</v>
+      </c>
+      <c r="AF185" t="inlineStr">
+        <is>
+          <t>Emagrecimento</t>
+        </is>
+      </c>
+      <c r="AG185" t="inlineStr"/>
+      <c r="AH185" t="inlineStr"/>
+      <c r="AI185" t="inlineStr"/>
+      <c r="AJ185" t="inlineStr"/>
+      <c r="AK185" t="inlineStr"/>
+      <c r="AL185" t="inlineStr"/>
+      <c r="AM185" t="inlineStr"/>
+      <c r="AN185" t="inlineStr"/>
+      <c r="AO185" t="inlineStr"/>
+      <c r="AP185" t="inlineStr"/>
+      <c r="AQ185" t="inlineStr"/>
+      <c r="AR185" t="inlineStr"/>
+      <c r="AS185" t="inlineStr"/>
+      <c r="AT185" t="inlineStr"/>
+      <c r="AU185" t="inlineStr"/>
+      <c r="AV185" t="inlineStr"/>
+      <c r="AW185" t="inlineStr"/>
+      <c r="AX185" t="inlineStr"/>
+      <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr"/>
+      <c r="BA185" t="inlineStr"/>
+      <c r="BB185" t="inlineStr"/>
+      <c r="BC185" t="inlineStr"/>
+      <c r="BD185" t="inlineStr"/>
+      <c r="BE185" t="inlineStr"/>
+      <c r="BF185" t="inlineStr"/>
+      <c r="BG185" t="inlineStr"/>
+      <c r="BH185" t="inlineStr"/>
+      <c r="BI185" t="inlineStr"/>
+      <c r="BJ185" t="inlineStr"/>
+      <c r="BK185" t="inlineStr"/>
+      <c r="BL185" t="inlineStr"/>
+      <c r="BM185" t="inlineStr"/>
+      <c r="BN185" t="inlineStr"/>
+      <c r="BO185" t="inlineStr"/>
+      <c r="BP185" t="inlineStr"/>
+      <c r="BQ185" t="inlineStr"/>
+      <c r="BR185" t="inlineStr"/>
+      <c r="BS185" t="inlineStr"/>
+      <c r="BT185" t="inlineStr"/>
+      <c r="BU185" t="inlineStr"/>
+      <c r="BV185" t="inlineStr"/>
+      <c r="BW185" t="inlineStr"/>
+      <c r="BX185" t="inlineStr"/>
+      <c r="BY185" t="inlineStr"/>
+      <c r="BZ185" t="inlineStr"/>
+      <c r="CA185" t="inlineStr"/>
+      <c r="CB185" t="inlineStr"/>
+      <c r="CC185" t="inlineStr"/>
+      <c r="CD185" t="inlineStr"/>
+      <c r="CE185" t="inlineStr"/>
+      <c r="CF185" t="inlineStr"/>
+      <c r="CG185" t="inlineStr"/>
+      <c r="CH185" t="inlineStr"/>
+      <c r="CI185" t="inlineStr"/>
+      <c r="CJ185" t="inlineStr"/>
+      <c r="CK185" t="inlineStr"/>
+      <c r="CL185" t="inlineStr"/>
+      <c r="CM185" t="inlineStr"/>
+      <c r="CN185" t="inlineStr"/>
+      <c r="CO185" t="inlineStr"/>
+      <c r="CP185" t="inlineStr"/>
+      <c r="CQ185" t="inlineStr"/>
+      <c r="CR185" t="inlineStr"/>
+      <c r="CS185" t="inlineStr"/>
+      <c r="CT185" t="inlineStr"/>
+      <c r="CU185" t="inlineStr"/>
+      <c r="CV185" t="inlineStr"/>
+      <c r="CW185" t="inlineStr"/>
+      <c r="CX185" t="inlineStr"/>
+      <c r="CY185" t="inlineStr"/>
+      <c r="CZ185" t="inlineStr"/>
+      <c r="DA185" t="inlineStr"/>
+      <c r="DB185" t="inlineStr"/>
+      <c r="DC185" t="inlineStr"/>
+      <c r="DD185" t="inlineStr"/>
+      <c r="DE185" t="inlineStr"/>
+      <c r="DF185" t="inlineStr"/>
+      <c r="DG185" t="inlineStr"/>
+      <c r="DH185" t="inlineStr"/>
+      <c r="DI185" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>548</v>
+      </c>
+      <c r="B186" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C186" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>DESOSPITALIZAÇÃO AMIL - TIME ERIC</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
+      <c r="O186" t="inlineStr"/>
+      <c r="P186" t="inlineStr"/>
+      <c r="Q186" t="inlineStr"/>
+      <c r="R186" t="inlineStr"/>
+      <c r="S186" t="inlineStr"/>
+      <c r="T186" t="inlineStr"/>
+      <c r="U186" t="inlineStr"/>
+      <c r="V186" t="inlineStr"/>
+      <c r="W186" t="inlineStr"/>
+      <c r="X186" t="inlineStr"/>
+      <c r="Y186" t="inlineStr"/>
+      <c r="Z186" t="inlineStr"/>
+      <c r="AA186" t="inlineStr"/>
+      <c r="AB186" t="inlineStr"/>
+      <c r="AC186" t="inlineStr"/>
+      <c r="AD186" t="inlineStr"/>
+      <c r="AE186" t="inlineStr"/>
+      <c r="AF186" t="inlineStr"/>
+      <c r="AG186" t="inlineStr"/>
+      <c r="AH186" t="inlineStr"/>
+      <c r="AI186" t="inlineStr"/>
+      <c r="AJ186" t="inlineStr"/>
+      <c r="AK186" t="n">
+        <v>123024285</v>
+      </c>
+      <c r="AL186" t="inlineStr">
+        <is>
+          <t>NILO GONCALVES CARDOSO</t>
+        </is>
+      </c>
+      <c r="AM186" t="inlineStr">
+        <is>
+          <t>089.247.838-15</t>
+        </is>
+      </c>
+      <c r="AN186" s="1" t="n">
+        <v>16706</v>
+      </c>
+      <c r="AO186" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="AP186" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="AQ186" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="AR186" t="inlineStr">
+        <is>
+          <t>MEDICUS 22 - FAM.C.PARTO</t>
+        </is>
+      </c>
+      <c r="AS186" t="n">
+        <v>11997588019</v>
+      </c>
+      <c r="AT186" t="inlineStr">
+        <is>
+          <t>Bem Cuidado</t>
+        </is>
+      </c>
+      <c r="AU186" t="inlineStr"/>
+      <c r="AV186" t="inlineStr"/>
+      <c r="AW186" t="inlineStr"/>
+      <c r="AX186" t="inlineStr"/>
+      <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr"/>
+      <c r="BA186" t="inlineStr"/>
+      <c r="BB186" t="inlineStr"/>
+      <c r="BC186" t="inlineStr"/>
+      <c r="BD186" t="inlineStr"/>
+      <c r="BE186" t="inlineStr"/>
+      <c r="BF186" t="inlineStr"/>
+      <c r="BG186" t="inlineStr"/>
+      <c r="BH186" t="inlineStr"/>
+      <c r="BI186" t="inlineStr"/>
+      <c r="BJ186" t="inlineStr"/>
+      <c r="BK186" t="inlineStr"/>
+      <c r="BL186" t="inlineStr"/>
+      <c r="BM186" t="inlineStr"/>
+      <c r="BN186" t="inlineStr"/>
+      <c r="BO186" t="inlineStr"/>
+      <c r="BP186" t="inlineStr"/>
+      <c r="BQ186" t="inlineStr"/>
+      <c r="BR186" t="inlineStr"/>
+      <c r="BS186" t="inlineStr"/>
+      <c r="BT186" t="inlineStr"/>
+      <c r="BU186" t="inlineStr"/>
+      <c r="BV186" t="inlineStr"/>
+      <c r="BW186" t="inlineStr"/>
+      <c r="BX186" t="inlineStr"/>
+      <c r="BY186" t="inlineStr"/>
+      <c r="BZ186" t="inlineStr"/>
+      <c r="CA186" t="inlineStr"/>
+      <c r="CB186" t="inlineStr"/>
+      <c r="CC186" t="inlineStr"/>
+      <c r="CD186" t="inlineStr"/>
+      <c r="CE186" t="inlineStr"/>
+      <c r="CF186" t="inlineStr"/>
+      <c r="CG186" t="inlineStr"/>
+      <c r="CH186" t="inlineStr"/>
+      <c r="CI186" t="inlineStr"/>
+      <c r="CJ186" t="inlineStr"/>
+      <c r="CK186" t="inlineStr"/>
+      <c r="CL186" t="inlineStr"/>
+      <c r="CM186" t="inlineStr"/>
+      <c r="CN186" t="inlineStr"/>
+      <c r="CO186" t="inlineStr"/>
+      <c r="CP186" t="inlineStr"/>
+      <c r="CQ186" t="inlineStr"/>
+      <c r="CR186" t="inlineStr"/>
+      <c r="CS186" t="inlineStr"/>
+      <c r="CT186" t="inlineStr"/>
+      <c r="CU186" t="inlineStr"/>
+      <c r="CV186" t="inlineStr"/>
+      <c r="CW186" t="inlineStr"/>
+      <c r="CX186" t="inlineStr"/>
+      <c r="CY186" t="inlineStr"/>
+      <c r="CZ186" t="inlineStr"/>
+      <c r="DA186" t="inlineStr"/>
+      <c r="DB186" t="inlineStr"/>
+      <c r="DC186" t="inlineStr"/>
+      <c r="DD186" t="inlineStr"/>
+      <c r="DE186" t="inlineStr"/>
+      <c r="DF186" t="inlineStr"/>
+      <c r="DG186" t="inlineStr"/>
+      <c r="DH186" t="inlineStr"/>
+      <c r="DI186" t="inlineStr">
+        <is>
+          <t>DESCARTADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>549</v>
+      </c>
+      <c r="B187" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C187" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>AMÉRICAS</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
+      <c r="O187" t="inlineStr"/>
+      <c r="P187" t="inlineStr"/>
+      <c r="Q187" t="inlineStr"/>
+      <c r="R187" t="inlineStr"/>
+      <c r="S187" t="inlineStr"/>
+      <c r="T187" t="inlineStr"/>
+      <c r="U187" t="inlineStr"/>
+      <c r="V187" t="inlineStr"/>
+      <c r="W187" t="n">
+        <v>94347803</v>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>Laura Alejandra Castillo Contreras</t>
+        </is>
+      </c>
+      <c r="Y187" t="n">
+        <v>94347803</v>
+      </c>
+      <c r="Z187" s="1" t="n">
+        <v>36015</v>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="AD187" t="n">
+        <v>450</v>
+      </c>
+      <c r="AE187" t="n">
+        <v>21992849987</v>
+      </c>
+      <c r="AF187" t="inlineStr">
+        <is>
+          <t>Emagrecimento</t>
+        </is>
+      </c>
+      <c r="AG187" t="inlineStr"/>
+      <c r="AH187" t="inlineStr"/>
+      <c r="AI187" t="inlineStr"/>
+      <c r="AJ187" t="inlineStr"/>
+      <c r="AK187" t="inlineStr"/>
+      <c r="AL187" t="inlineStr"/>
+      <c r="AM187" t="inlineStr"/>
+      <c r="AN187" t="inlineStr"/>
+      <c r="AO187" t="inlineStr"/>
+      <c r="AP187" t="inlineStr"/>
+      <c r="AQ187" t="inlineStr"/>
+      <c r="AR187" t="inlineStr"/>
+      <c r="AS187" t="inlineStr"/>
+      <c r="AT187" t="inlineStr"/>
+      <c r="AU187" t="inlineStr"/>
+      <c r="AV187" t="inlineStr"/>
+      <c r="AW187" t="inlineStr"/>
+      <c r="AX187" t="inlineStr"/>
+      <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr"/>
+      <c r="BA187" t="inlineStr"/>
+      <c r="BB187" t="inlineStr"/>
+      <c r="BC187" t="inlineStr"/>
+      <c r="BD187" t="inlineStr"/>
+      <c r="BE187" t="inlineStr"/>
+      <c r="BF187" t="inlineStr"/>
+      <c r="BG187" t="inlineStr"/>
+      <c r="BH187" t="inlineStr"/>
+      <c r="BI187" t="inlineStr"/>
+      <c r="BJ187" t="inlineStr"/>
+      <c r="BK187" t="inlineStr"/>
+      <c r="BL187" t="inlineStr"/>
+      <c r="BM187" t="inlineStr"/>
+      <c r="BN187" t="inlineStr"/>
+      <c r="BO187" t="inlineStr"/>
+      <c r="BP187" t="inlineStr"/>
+      <c r="BQ187" t="inlineStr"/>
+      <c r="BR187" t="inlineStr"/>
+      <c r="BS187" t="inlineStr"/>
+      <c r="BT187" t="inlineStr"/>
+      <c r="BU187" t="inlineStr"/>
+      <c r="BV187" t="inlineStr"/>
+      <c r="BW187" t="inlineStr"/>
+      <c r="BX187" t="inlineStr"/>
+      <c r="BY187" t="inlineStr"/>
+      <c r="BZ187" t="inlineStr"/>
+      <c r="CA187" t="inlineStr"/>
+      <c r="CB187" t="inlineStr"/>
+      <c r="CC187" t="inlineStr"/>
+      <c r="CD187" t="inlineStr"/>
+      <c r="CE187" t="inlineStr"/>
+      <c r="CF187" t="inlineStr"/>
+      <c r="CG187" t="inlineStr"/>
+      <c r="CH187" t="inlineStr"/>
+      <c r="CI187" t="inlineStr"/>
+      <c r="CJ187" t="inlineStr"/>
+      <c r="CK187" t="inlineStr"/>
+      <c r="CL187" t="inlineStr"/>
+      <c r="CM187" t="inlineStr"/>
+      <c r="CN187" t="inlineStr"/>
+      <c r="CO187" t="inlineStr"/>
+      <c r="CP187" t="inlineStr"/>
+      <c r="CQ187" t="inlineStr"/>
+      <c r="CR187" t="inlineStr"/>
+      <c r="CS187" t="inlineStr"/>
+      <c r="CT187" t="inlineStr"/>
+      <c r="CU187" t="inlineStr"/>
+      <c r="CV187" t="inlineStr"/>
+      <c r="CW187" t="inlineStr"/>
+      <c r="CX187" t="inlineStr"/>
+      <c r="CY187" t="inlineStr"/>
+      <c r="CZ187" t="inlineStr"/>
+      <c r="DA187" t="inlineStr"/>
+      <c r="DB187" t="inlineStr"/>
+      <c r="DC187" t="inlineStr"/>
+      <c r="DD187" t="inlineStr"/>
+      <c r="DE187" t="inlineStr"/>
+      <c r="DF187" t="inlineStr"/>
+      <c r="DG187" t="inlineStr"/>
+      <c r="DH187" t="inlineStr"/>
+      <c r="DI187" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>550</v>
+      </c>
+      <c r="B188" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C188" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>DESOSPITALIZAÇÃO AMIL - TIME ERIC</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
+      <c r="O188" t="inlineStr"/>
+      <c r="P188" t="inlineStr"/>
+      <c r="Q188" t="inlineStr"/>
+      <c r="R188" t="inlineStr"/>
+      <c r="S188" t="inlineStr"/>
+      <c r="T188" t="inlineStr"/>
+      <c r="U188" t="inlineStr"/>
+      <c r="V188" t="inlineStr"/>
+      <c r="W188" t="inlineStr"/>
+      <c r="X188" t="inlineStr"/>
+      <c r="Y188" t="inlineStr"/>
+      <c r="Z188" t="inlineStr"/>
+      <c r="AA188" t="inlineStr"/>
+      <c r="AB188" t="inlineStr"/>
+      <c r="AC188" t="inlineStr"/>
+      <c r="AD188" t="inlineStr"/>
+      <c r="AE188" t="inlineStr"/>
+      <c r="AF188" t="inlineStr"/>
+      <c r="AG188" t="inlineStr"/>
+      <c r="AH188" t="inlineStr"/>
+      <c r="AI188" t="inlineStr"/>
+      <c r="AJ188" t="inlineStr"/>
+      <c r="AK188" t="n">
+        <v>89129664</v>
+      </c>
+      <c r="AL188" t="inlineStr">
+        <is>
+          <t>GENOVEVA DOS SANTOS DA SILVA</t>
+        </is>
+      </c>
+      <c r="AM188" t="inlineStr">
+        <is>
+          <t>152.844.728-02</t>
+        </is>
+      </c>
+      <c r="AN188" s="1" t="n">
+        <v>25884</v>
+      </c>
+      <c r="AO188" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="AP188" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="AQ188" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="AR188" t="inlineStr">
+        <is>
+          <t>AMIL FÁCIL S60 QC SP MAIS GM COPART PJ</t>
+        </is>
+      </c>
+      <c r="AS188" t="n">
+        <v>11982911730</v>
+      </c>
+      <c r="AT188" t="inlineStr">
+        <is>
+          <t>Viva Bem</t>
+        </is>
+      </c>
+      <c r="AU188" t="inlineStr"/>
+      <c r="AV188" t="inlineStr"/>
+      <c r="AW188" t="inlineStr"/>
+      <c r="AX188" t="inlineStr"/>
+      <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr"/>
+      <c r="BA188" t="inlineStr"/>
+      <c r="BB188" t="inlineStr"/>
+      <c r="BC188" t="inlineStr"/>
+      <c r="BD188" t="inlineStr"/>
+      <c r="BE188" t="inlineStr"/>
+      <c r="BF188" t="inlineStr"/>
+      <c r="BG188" t="inlineStr"/>
+      <c r="BH188" t="inlineStr"/>
+      <c r="BI188" t="inlineStr"/>
+      <c r="BJ188" t="inlineStr"/>
+      <c r="BK188" t="inlineStr"/>
+      <c r="BL188" t="inlineStr"/>
+      <c r="BM188" t="inlineStr"/>
+      <c r="BN188" t="inlineStr"/>
+      <c r="BO188" t="inlineStr"/>
+      <c r="BP188" t="inlineStr"/>
+      <c r="BQ188" t="inlineStr"/>
+      <c r="BR188" t="inlineStr"/>
+      <c r="BS188" t="inlineStr"/>
+      <c r="BT188" t="inlineStr"/>
+      <c r="BU188" t="inlineStr"/>
+      <c r="BV188" t="inlineStr"/>
+      <c r="BW188" t="inlineStr"/>
+      <c r="BX188" t="inlineStr"/>
+      <c r="BY188" t="inlineStr"/>
+      <c r="BZ188" t="inlineStr"/>
+      <c r="CA188" t="inlineStr"/>
+      <c r="CB188" t="inlineStr"/>
+      <c r="CC188" t="inlineStr"/>
+      <c r="CD188" t="inlineStr"/>
+      <c r="CE188" t="inlineStr"/>
+      <c r="CF188" t="inlineStr"/>
+      <c r="CG188" t="inlineStr"/>
+      <c r="CH188" t="inlineStr"/>
+      <c r="CI188" t="inlineStr"/>
+      <c r="CJ188" t="inlineStr"/>
+      <c r="CK188" t="inlineStr"/>
+      <c r="CL188" t="inlineStr"/>
+      <c r="CM188" t="inlineStr"/>
+      <c r="CN188" t="inlineStr"/>
+      <c r="CO188" t="inlineStr"/>
+      <c r="CP188" t="inlineStr"/>
+      <c r="CQ188" t="inlineStr"/>
+      <c r="CR188" t="inlineStr"/>
+      <c r="CS188" t="inlineStr"/>
+      <c r="CT188" t="inlineStr"/>
+      <c r="CU188" t="inlineStr"/>
+      <c r="CV188" t="inlineStr"/>
+      <c r="CW188" t="inlineStr"/>
+      <c r="CX188" t="inlineStr"/>
+      <c r="CY188" t="inlineStr"/>
+      <c r="CZ188" t="inlineStr"/>
+      <c r="DA188" t="inlineStr"/>
+      <c r="DB188" t="inlineStr"/>
+      <c r="DC188" t="inlineStr"/>
+      <c r="DD188" t="inlineStr"/>
+      <c r="DE188" t="inlineStr"/>
+      <c r="DF188" t="inlineStr"/>
+      <c r="DG188" t="inlineStr"/>
+      <c r="DH188" t="inlineStr"/>
+      <c r="DI188" t="inlineStr">
+        <is>
+          <t>DESCARTADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>551</v>
+      </c>
+      <c r="B189" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C189" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>DESOSPITALIZAÇÃO AMIL - TIME ERIC</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
+      <c r="O189" t="inlineStr"/>
+      <c r="P189" t="inlineStr"/>
+      <c r="Q189" t="inlineStr"/>
+      <c r="R189" t="inlineStr"/>
+      <c r="S189" t="inlineStr"/>
+      <c r="T189" t="inlineStr"/>
+      <c r="U189" t="inlineStr"/>
+      <c r="V189" t="inlineStr"/>
+      <c r="W189" t="inlineStr"/>
+      <c r="X189" t="inlineStr"/>
+      <c r="Y189" t="inlineStr"/>
+      <c r="Z189" t="inlineStr"/>
+      <c r="AA189" t="inlineStr"/>
+      <c r="AB189" t="inlineStr"/>
+      <c r="AC189" t="inlineStr"/>
+      <c r="AD189" t="inlineStr"/>
+      <c r="AE189" t="inlineStr"/>
+      <c r="AF189" t="inlineStr"/>
+      <c r="AG189" t="inlineStr"/>
+      <c r="AH189" t="inlineStr"/>
+      <c r="AI189" t="inlineStr"/>
+      <c r="AJ189" t="inlineStr"/>
+      <c r="AK189" t="n">
+        <v>451594312</v>
+      </c>
+      <c r="AL189" t="inlineStr">
+        <is>
+          <t>JOSEFA MARIA DE ANDRADE</t>
+        </is>
+      </c>
+      <c r="AM189" t="n">
+        <v>451594312</v>
+      </c>
+      <c r="AN189" s="1" t="n">
+        <v>13820</v>
+      </c>
+      <c r="AO189" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="AP189" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="AQ189" t="inlineStr">
+        <is>
+          <t>sp</t>
+        </is>
+      </c>
+      <c r="AR189" t="inlineStr">
+        <is>
+          <t>MEDIAL STANDARD PLUS</t>
+        </is>
+      </c>
+      <c r="AS189" t="n">
+        <v>11984097653</v>
+      </c>
+      <c r="AT189" t="inlineStr">
+        <is>
+          <t>Bem Cuidado</t>
+        </is>
+      </c>
+      <c r="AU189" t="inlineStr"/>
+      <c r="AV189" t="inlineStr"/>
+      <c r="AW189" t="inlineStr"/>
+      <c r="AX189" t="inlineStr"/>
+      <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr"/>
+      <c r="BA189" t="inlineStr"/>
+      <c r="BB189" t="inlineStr"/>
+      <c r="BC189" t="inlineStr"/>
+      <c r="BD189" t="inlineStr"/>
+      <c r="BE189" t="inlineStr"/>
+      <c r="BF189" t="inlineStr"/>
+      <c r="BG189" t="inlineStr"/>
+      <c r="BH189" t="inlineStr"/>
+      <c r="BI189" t="inlineStr"/>
+      <c r="BJ189" t="inlineStr"/>
+      <c r="BK189" t="inlineStr"/>
+      <c r="BL189" t="inlineStr"/>
+      <c r="BM189" t="inlineStr"/>
+      <c r="BN189" t="inlineStr"/>
+      <c r="BO189" t="inlineStr"/>
+      <c r="BP189" t="inlineStr"/>
+      <c r="BQ189" t="inlineStr"/>
+      <c r="BR189" t="inlineStr"/>
+      <c r="BS189" t="inlineStr"/>
+      <c r="BT189" t="inlineStr"/>
+      <c r="BU189" t="inlineStr"/>
+      <c r="BV189" t="inlineStr"/>
+      <c r="BW189" t="inlineStr"/>
+      <c r="BX189" t="inlineStr"/>
+      <c r="BY189" t="inlineStr"/>
+      <c r="BZ189" t="inlineStr"/>
+      <c r="CA189" t="inlineStr"/>
+      <c r="CB189" t="inlineStr"/>
+      <c r="CC189" t="inlineStr"/>
+      <c r="CD189" t="inlineStr"/>
+      <c r="CE189" t="inlineStr"/>
+      <c r="CF189" t="inlineStr"/>
+      <c r="CG189" t="inlineStr"/>
+      <c r="CH189" t="inlineStr"/>
+      <c r="CI189" t="inlineStr"/>
+      <c r="CJ189" t="inlineStr"/>
+      <c r="CK189" t="inlineStr"/>
+      <c r="CL189" t="inlineStr"/>
+      <c r="CM189" t="inlineStr"/>
+      <c r="CN189" t="inlineStr"/>
+      <c r="CO189" t="inlineStr"/>
+      <c r="CP189" t="inlineStr"/>
+      <c r="CQ189" t="inlineStr"/>
+      <c r="CR189" t="inlineStr"/>
+      <c r="CS189" t="inlineStr"/>
+      <c r="CT189" t="inlineStr"/>
+      <c r="CU189" t="inlineStr"/>
+      <c r="CV189" t="inlineStr"/>
+      <c r="CW189" t="inlineStr"/>
+      <c r="CX189" t="inlineStr"/>
+      <c r="CY189" t="inlineStr"/>
+      <c r="CZ189" t="inlineStr"/>
+      <c r="DA189" t="inlineStr"/>
+      <c r="DB189" t="inlineStr"/>
+      <c r="DC189" t="inlineStr"/>
+      <c r="DD189" t="inlineStr"/>
+      <c r="DE189" t="inlineStr"/>
+      <c r="DF189" t="inlineStr"/>
+      <c r="DG189" t="inlineStr"/>
+      <c r="DH189" t="inlineStr"/>
+      <c r="DI189" t="inlineStr">
+        <is>
+          <t>DESCARTADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>552</v>
+      </c>
+      <c r="B190" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C190" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>DESOSPITALIZAÇÃO AMIL - TIME ERIC</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
+      <c r="O190" t="inlineStr"/>
+      <c r="P190" t="inlineStr"/>
+      <c r="Q190" t="inlineStr"/>
+      <c r="R190" t="inlineStr"/>
+      <c r="S190" t="inlineStr"/>
+      <c r="T190" t="inlineStr"/>
+      <c r="U190" t="inlineStr"/>
+      <c r="V190" t="inlineStr"/>
+      <c r="W190" t="inlineStr"/>
+      <c r="X190" t="inlineStr"/>
+      <c r="Y190" t="inlineStr"/>
+      <c r="Z190" t="inlineStr"/>
+      <c r="AA190" t="inlineStr"/>
+      <c r="AB190" t="inlineStr"/>
+      <c r="AC190" t="inlineStr"/>
+      <c r="AD190" t="inlineStr"/>
+      <c r="AE190" t="inlineStr"/>
+      <c r="AF190" t="inlineStr"/>
+      <c r="AG190" t="inlineStr"/>
+      <c r="AH190" t="inlineStr"/>
+      <c r="AI190" t="inlineStr"/>
+      <c r="AJ190" t="inlineStr"/>
+      <c r="AK190" t="n">
+        <v>95437385</v>
+      </c>
+      <c r="AL190" t="inlineStr">
+        <is>
+          <t>NOELSON BARROS DA SILVA</t>
+        </is>
+      </c>
+      <c r="AM190" t="inlineStr">
+        <is>
+          <t>366.322.708-16</t>
+        </is>
+      </c>
+      <c r="AN190" s="1" t="n">
+        <v>31862</v>
+      </c>
+      <c r="AO190" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="AP190" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="AQ190" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="AR190" t="inlineStr">
+        <is>
+          <t>BRONZE SP</t>
+        </is>
+      </c>
+      <c r="AS190" t="n">
+        <v>11984465224</v>
+      </c>
+      <c r="AT190" t="inlineStr">
+        <is>
+          <t>Bem Cuidado</t>
+        </is>
+      </c>
+      <c r="AU190" t="inlineStr"/>
+      <c r="AV190" t="inlineStr"/>
+      <c r="AW190" t="inlineStr"/>
+      <c r="AX190" t="inlineStr"/>
+      <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr"/>
+      <c r="BA190" t="inlineStr"/>
+      <c r="BB190" t="inlineStr"/>
+      <c r="BC190" t="inlineStr"/>
+      <c r="BD190" t="inlineStr"/>
+      <c r="BE190" t="inlineStr"/>
+      <c r="BF190" t="inlineStr"/>
+      <c r="BG190" t="inlineStr"/>
+      <c r="BH190" t="inlineStr"/>
+      <c r="BI190" t="inlineStr"/>
+      <c r="BJ190" t="inlineStr"/>
+      <c r="BK190" t="inlineStr"/>
+      <c r="BL190" t="inlineStr"/>
+      <c r="BM190" t="inlineStr"/>
+      <c r="BN190" t="inlineStr"/>
+      <c r="BO190" t="inlineStr"/>
+      <c r="BP190" t="inlineStr"/>
+      <c r="BQ190" t="inlineStr"/>
+      <c r="BR190" t="inlineStr"/>
+      <c r="BS190" t="inlineStr"/>
+      <c r="BT190" t="inlineStr"/>
+      <c r="BU190" t="inlineStr"/>
+      <c r="BV190" t="inlineStr"/>
+      <c r="BW190" t="inlineStr"/>
+      <c r="BX190" t="inlineStr"/>
+      <c r="BY190" t="inlineStr"/>
+      <c r="BZ190" t="inlineStr"/>
+      <c r="CA190" t="inlineStr"/>
+      <c r="CB190" t="inlineStr"/>
+      <c r="CC190" t="inlineStr"/>
+      <c r="CD190" t="inlineStr"/>
+      <c r="CE190" t="inlineStr"/>
+      <c r="CF190" t="inlineStr"/>
+      <c r="CG190" t="inlineStr"/>
+      <c r="CH190" t="inlineStr"/>
+      <c r="CI190" t="inlineStr"/>
+      <c r="CJ190" t="inlineStr"/>
+      <c r="CK190" t="inlineStr"/>
+      <c r="CL190" t="inlineStr"/>
+      <c r="CM190" t="inlineStr"/>
+      <c r="CN190" t="inlineStr"/>
+      <c r="CO190" t="inlineStr"/>
+      <c r="CP190" t="inlineStr"/>
+      <c r="CQ190" t="inlineStr"/>
+      <c r="CR190" t="inlineStr"/>
+      <c r="CS190" t="inlineStr"/>
+      <c r="CT190" t="inlineStr"/>
+      <c r="CU190" t="inlineStr"/>
+      <c r="CV190" t="inlineStr"/>
+      <c r="CW190" t="inlineStr"/>
+      <c r="CX190" t="inlineStr"/>
+      <c r="CY190" t="inlineStr"/>
+      <c r="CZ190" t="inlineStr"/>
+      <c r="DA190" t="inlineStr"/>
+      <c r="DB190" t="inlineStr"/>
+      <c r="DC190" t="inlineStr"/>
+      <c r="DD190" t="inlineStr"/>
+      <c r="DE190" t="inlineStr"/>
+      <c r="DF190" t="inlineStr"/>
+      <c r="DG190" t="inlineStr"/>
+      <c r="DH190" t="inlineStr"/>
+      <c r="DI190" t="inlineStr">
+        <is>
+          <t>DESCARTADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>553</v>
+      </c>
+      <c r="B191" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C191" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>DESOSPITALIZAÇÃO AMIL - TIME ERIC</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr"/>
+      <c r="P191" t="inlineStr"/>
+      <c r="Q191" t="inlineStr"/>
+      <c r="R191" t="inlineStr"/>
+      <c r="S191" t="inlineStr"/>
+      <c r="T191" t="inlineStr"/>
+      <c r="U191" t="inlineStr"/>
+      <c r="V191" t="inlineStr"/>
+      <c r="W191" t="inlineStr"/>
+      <c r="X191" t="inlineStr"/>
+      <c r="Y191" t="inlineStr"/>
+      <c r="Z191" t="inlineStr"/>
+      <c r="AA191" t="inlineStr"/>
+      <c r="AB191" t="inlineStr"/>
+      <c r="AC191" t="inlineStr"/>
+      <c r="AD191" t="inlineStr"/>
+      <c r="AE191" t="inlineStr"/>
+      <c r="AF191" t="inlineStr"/>
+      <c r="AG191" t="inlineStr"/>
+      <c r="AH191" t="inlineStr"/>
+      <c r="AI191" t="inlineStr"/>
+      <c r="AJ191" t="inlineStr"/>
+      <c r="AK191" t="n">
+        <v>82078176</v>
+      </c>
+      <c r="AL191" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO DANTAS DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="AM191" t="inlineStr">
+        <is>
+          <t>120.290.227-80</t>
+        </is>
+      </c>
+      <c r="AN191" s="1" t="n">
+        <v>32151</v>
+      </c>
+      <c r="AO191" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="AP191" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="AQ191" t="inlineStr">
+        <is>
+          <t>DUQUE DE CAXIAS</t>
+        </is>
+      </c>
+      <c r="AR191" t="inlineStr">
+        <is>
+          <t>6 AMIL FÁCIL S60 QC RJ GM PJ</t>
+        </is>
+      </c>
+      <c r="AS191" t="inlineStr">
+        <is>
+          <t>21-996560478</t>
+        </is>
+      </c>
+      <c r="AT191" t="inlineStr">
+        <is>
+          <t>Saúde Mental</t>
+        </is>
+      </c>
+      <c r="AU191" t="inlineStr">
+        <is>
+          <t>Busca preventiva por bem-estar</t>
+        </is>
+      </c>
+      <c r="AV191" t="inlineStr"/>
+      <c r="AW191" t="inlineStr"/>
+      <c r="AX191" t="inlineStr"/>
+      <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr"/>
+      <c r="BA191" t="inlineStr"/>
+      <c r="BB191" t="inlineStr"/>
+      <c r="BC191" t="inlineStr"/>
+      <c r="BD191" t="inlineStr"/>
+      <c r="BE191" t="inlineStr"/>
+      <c r="BF191" t="inlineStr"/>
+      <c r="BG191" t="inlineStr"/>
+      <c r="BH191" t="inlineStr"/>
+      <c r="BI191" t="inlineStr"/>
+      <c r="BJ191" t="inlineStr"/>
+      <c r="BK191" t="inlineStr"/>
+      <c r="BL191" t="inlineStr"/>
+      <c r="BM191" t="inlineStr"/>
+      <c r="BN191" t="inlineStr"/>
+      <c r="BO191" t="inlineStr"/>
+      <c r="BP191" t="inlineStr"/>
+      <c r="BQ191" t="inlineStr"/>
+      <c r="BR191" t="inlineStr"/>
+      <c r="BS191" t="inlineStr"/>
+      <c r="BT191" t="inlineStr"/>
+      <c r="BU191" t="inlineStr"/>
+      <c r="BV191" t="inlineStr"/>
+      <c r="BW191" t="inlineStr"/>
+      <c r="BX191" t="inlineStr"/>
+      <c r="BY191" t="inlineStr"/>
+      <c r="BZ191" t="inlineStr"/>
+      <c r="CA191" t="inlineStr"/>
+      <c r="CB191" t="inlineStr"/>
+      <c r="CC191" t="inlineStr"/>
+      <c r="CD191" t="inlineStr"/>
+      <c r="CE191" t="inlineStr"/>
+      <c r="CF191" t="inlineStr"/>
+      <c r="CG191" t="inlineStr"/>
+      <c r="CH191" t="inlineStr"/>
+      <c r="CI191" t="inlineStr"/>
+      <c r="CJ191" t="inlineStr"/>
+      <c r="CK191" t="inlineStr"/>
+      <c r="CL191" t="inlineStr"/>
+      <c r="CM191" t="inlineStr"/>
+      <c r="CN191" t="inlineStr"/>
+      <c r="CO191" t="inlineStr"/>
+      <c r="CP191" t="inlineStr"/>
+      <c r="CQ191" t="inlineStr"/>
+      <c r="CR191" t="inlineStr"/>
+      <c r="CS191" t="inlineStr"/>
+      <c r="CT191" t="inlineStr"/>
+      <c r="CU191" t="inlineStr"/>
+      <c r="CV191" t="inlineStr"/>
+      <c r="CW191" t="inlineStr"/>
+      <c r="CX191" t="inlineStr"/>
+      <c r="CY191" t="inlineStr"/>
+      <c r="CZ191" t="inlineStr"/>
+      <c r="DA191" t="inlineStr"/>
+      <c r="DB191" t="inlineStr"/>
+      <c r="DC191" t="inlineStr"/>
+      <c r="DD191" t="inlineStr"/>
+      <c r="DE191" t="inlineStr"/>
+      <c r="DF191" t="inlineStr"/>
+      <c r="DG191" t="inlineStr"/>
+      <c r="DH191" t="inlineStr"/>
+      <c r="DI191" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>554</v>
+      </c>
+      <c r="B192" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C192" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>DESOSPITALIZAÇÃO AMIL - TIME ERIC</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr"/>
+      <c r="P192" t="inlineStr"/>
+      <c r="Q192" t="inlineStr"/>
+      <c r="R192" t="inlineStr"/>
+      <c r="S192" t="inlineStr"/>
+      <c r="T192" t="inlineStr"/>
+      <c r="U192" t="inlineStr"/>
+      <c r="V192" t="inlineStr"/>
+      <c r="W192" t="inlineStr"/>
+      <c r="X192" t="inlineStr"/>
+      <c r="Y192" t="inlineStr"/>
+      <c r="Z192" t="inlineStr"/>
+      <c r="AA192" t="inlineStr"/>
+      <c r="AB192" t="inlineStr"/>
+      <c r="AC192" t="inlineStr"/>
+      <c r="AD192" t="inlineStr"/>
+      <c r="AE192" t="inlineStr"/>
+      <c r="AF192" t="inlineStr"/>
+      <c r="AG192" t="inlineStr"/>
+      <c r="AH192" t="inlineStr"/>
+      <c r="AI192" t="inlineStr"/>
+      <c r="AJ192" t="inlineStr"/>
+      <c r="AK192" t="n">
+        <v>96788568</v>
+      </c>
+      <c r="AL192" t="inlineStr">
+        <is>
+          <t>GENILSON DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="AM192" t="inlineStr">
+        <is>
+          <t>034.138.897-10</t>
+        </is>
+      </c>
+      <c r="AN192" s="1" t="n">
+        <v>27278</v>
+      </c>
+      <c r="AO192" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="AP192" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="AQ192" t="inlineStr">
+        <is>
+          <t>DUQUE DE CAXIAS</t>
+        </is>
+      </c>
+      <c r="AR192" t="inlineStr">
+        <is>
+          <t>PRATA QC COPART</t>
+        </is>
+      </c>
+      <c r="AS192" t="inlineStr">
+        <is>
+          <t>21-994253609</t>
+        </is>
+      </c>
+      <c r="AT192" t="inlineStr">
+        <is>
+          <t>Saúde Mental</t>
+        </is>
+      </c>
+      <c r="AU192" t="inlineStr">
+        <is>
+          <t>Busca preventiva por bem-estar</t>
+        </is>
+      </c>
+      <c r="AV192" t="inlineStr"/>
+      <c r="AW192" t="inlineStr"/>
+      <c r="AX192" t="inlineStr"/>
+      <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr"/>
+      <c r="BA192" t="inlineStr"/>
+      <c r="BB192" t="inlineStr"/>
+      <c r="BC192" t="inlineStr"/>
+      <c r="BD192" t="inlineStr"/>
+      <c r="BE192" t="inlineStr"/>
+      <c r="BF192" t="inlineStr"/>
+      <c r="BG192" t="inlineStr"/>
+      <c r="BH192" t="inlineStr"/>
+      <c r="BI192" t="inlineStr"/>
+      <c r="BJ192" t="inlineStr"/>
+      <c r="BK192" t="inlineStr"/>
+      <c r="BL192" t="inlineStr"/>
+      <c r="BM192" t="inlineStr"/>
+      <c r="BN192" t="inlineStr"/>
+      <c r="BO192" t="inlineStr"/>
+      <c r="BP192" t="inlineStr"/>
+      <c r="BQ192" t="inlineStr"/>
+      <c r="BR192" t="inlineStr"/>
+      <c r="BS192" t="inlineStr"/>
+      <c r="BT192" t="inlineStr"/>
+      <c r="BU192" t="inlineStr"/>
+      <c r="BV192" t="inlineStr"/>
+      <c r="BW192" t="inlineStr"/>
+      <c r="BX192" t="inlineStr"/>
+      <c r="BY192" t="inlineStr"/>
+      <c r="BZ192" t="inlineStr"/>
+      <c r="CA192" t="inlineStr"/>
+      <c r="CB192" t="inlineStr"/>
+      <c r="CC192" t="inlineStr"/>
+      <c r="CD192" t="inlineStr"/>
+      <c r="CE192" t="inlineStr"/>
+      <c r="CF192" t="inlineStr"/>
+      <c r="CG192" t="inlineStr"/>
+      <c r="CH192" t="inlineStr"/>
+      <c r="CI192" t="inlineStr"/>
+      <c r="CJ192" t="inlineStr"/>
+      <c r="CK192" t="inlineStr"/>
+      <c r="CL192" t="inlineStr"/>
+      <c r="CM192" t="inlineStr"/>
+      <c r="CN192" t="inlineStr"/>
+      <c r="CO192" t="inlineStr"/>
+      <c r="CP192" t="inlineStr"/>
+      <c r="CQ192" t="inlineStr"/>
+      <c r="CR192" t="inlineStr"/>
+      <c r="CS192" t="inlineStr"/>
+      <c r="CT192" t="inlineStr"/>
+      <c r="CU192" t="inlineStr"/>
+      <c r="CV192" t="inlineStr"/>
+      <c r="CW192" t="inlineStr"/>
+      <c r="CX192" t="inlineStr"/>
+      <c r="CY192" t="inlineStr"/>
+      <c r="CZ192" t="inlineStr"/>
+      <c r="DA192" t="inlineStr"/>
+      <c r="DB192" t="inlineStr"/>
+      <c r="DC192" t="inlineStr"/>
+      <c r="DD192" t="inlineStr"/>
+      <c r="DE192" t="inlineStr"/>
+      <c r="DF192" t="inlineStr"/>
+      <c r="DG192" t="inlineStr"/>
+      <c r="DH192" t="inlineStr"/>
+      <c r="DI192" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>555</v>
+      </c>
+      <c r="B193" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C193" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>DESOSPITALIZAÇÃO AMIL - TIME ERIC</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
+      <c r="O193" t="inlineStr"/>
+      <c r="P193" t="inlineStr"/>
+      <c r="Q193" t="inlineStr"/>
+      <c r="R193" t="inlineStr"/>
+      <c r="S193" t="inlineStr"/>
+      <c r="T193" t="inlineStr"/>
+      <c r="U193" t="inlineStr"/>
+      <c r="V193" t="inlineStr"/>
+      <c r="W193" t="inlineStr"/>
+      <c r="X193" t="inlineStr"/>
+      <c r="Y193" t="inlineStr"/>
+      <c r="Z193" t="inlineStr"/>
+      <c r="AA193" t="inlineStr"/>
+      <c r="AB193" t="inlineStr"/>
+      <c r="AC193" t="inlineStr"/>
+      <c r="AD193" t="inlineStr"/>
+      <c r="AE193" t="inlineStr"/>
+      <c r="AF193" t="inlineStr"/>
+      <c r="AG193" t="inlineStr"/>
+      <c r="AH193" t="inlineStr"/>
+      <c r="AI193" t="inlineStr"/>
+      <c r="AJ193" t="inlineStr"/>
+      <c r="AK193" t="n">
+        <v>78348042</v>
+      </c>
+      <c r="AL193" t="inlineStr">
+        <is>
+          <t>ODELIA FARIA DE OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="AM193" t="inlineStr">
+        <is>
+          <t>754.824.367-72</t>
+        </is>
+      </c>
+      <c r="AN193" s="1" t="n">
+        <v>22650</v>
+      </c>
+      <c r="AO193" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="AP193" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="AQ193" t="inlineStr">
+        <is>
+          <t>RIO DE JANEIRO</t>
+        </is>
+      </c>
+      <c r="AR193" t="inlineStr">
+        <is>
+          <t>AMIL COLABORADOR QC NAC COPART PJ ADM</t>
+        </is>
+      </c>
+      <c r="AS193" t="n">
+        <v>2194529564</v>
+      </c>
+      <c r="AT193" t="inlineStr">
+        <is>
+          <t>Insuficiência Cardíaca Controlada</t>
+        </is>
+      </c>
+      <c r="AU193" t="inlineStr"/>
+      <c r="AV193" t="inlineStr"/>
+      <c r="AW193" t="inlineStr"/>
+      <c r="AX193" t="inlineStr"/>
+      <c r="AY193" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="AZ193" t="inlineStr"/>
+      <c r="BA193" t="inlineStr"/>
+      <c r="BB193" t="inlineStr"/>
+      <c r="BC193" t="inlineStr"/>
+      <c r="BD193" t="inlineStr"/>
+      <c r="BE193" t="inlineStr"/>
+      <c r="BF193" t="inlineStr"/>
+      <c r="BG193" t="inlineStr"/>
+      <c r="BH193" t="inlineStr"/>
+      <c r="BI193" t="inlineStr"/>
+      <c r="BJ193" t="inlineStr"/>
+      <c r="BK193" t="inlineStr"/>
+      <c r="BL193" t="inlineStr"/>
+      <c r="BM193" t="inlineStr"/>
+      <c r="BN193" t="inlineStr"/>
+      <c r="BO193" t="inlineStr"/>
+      <c r="BP193" t="inlineStr"/>
+      <c r="BQ193" t="inlineStr"/>
+      <c r="BR193" t="inlineStr"/>
+      <c r="BS193" t="inlineStr"/>
+      <c r="BT193" t="inlineStr"/>
+      <c r="BU193" t="inlineStr"/>
+      <c r="BV193" t="inlineStr"/>
+      <c r="BW193" t="inlineStr"/>
+      <c r="BX193" t="inlineStr"/>
+      <c r="BY193" t="inlineStr"/>
+      <c r="BZ193" t="inlineStr"/>
+      <c r="CA193" t="inlineStr"/>
+      <c r="CB193" t="inlineStr"/>
+      <c r="CC193" t="inlineStr"/>
+      <c r="CD193" t="inlineStr"/>
+      <c r="CE193" t="inlineStr"/>
+      <c r="CF193" t="inlineStr"/>
+      <c r="CG193" t="inlineStr"/>
+      <c r="CH193" t="inlineStr"/>
+      <c r="CI193" t="inlineStr"/>
+      <c r="CJ193" t="inlineStr"/>
+      <c r="CK193" t="inlineStr"/>
+      <c r="CL193" t="inlineStr"/>
+      <c r="CM193" t="inlineStr"/>
+      <c r="CN193" t="inlineStr"/>
+      <c r="CO193" t="inlineStr"/>
+      <c r="CP193" t="inlineStr"/>
+      <c r="CQ193" t="inlineStr"/>
+      <c r="CR193" t="inlineStr"/>
+      <c r="CS193" t="inlineStr"/>
+      <c r="CT193" t="inlineStr"/>
+      <c r="CU193" t="inlineStr"/>
+      <c r="CV193" t="inlineStr"/>
+      <c r="CW193" t="inlineStr"/>
+      <c r="CX193" t="inlineStr"/>
+      <c r="CY193" t="inlineStr"/>
+      <c r="CZ193" t="inlineStr"/>
+      <c r="DA193" t="inlineStr"/>
+      <c r="DB193" t="inlineStr"/>
+      <c r="DC193" t="inlineStr"/>
+      <c r="DD193" t="inlineStr"/>
+      <c r="DE193" t="inlineStr"/>
+      <c r="DF193" t="inlineStr"/>
+      <c r="DG193" t="inlineStr"/>
+      <c r="DH193" t="inlineStr"/>
+      <c r="DI193" t="inlineStr">
+        <is>
+          <t>ENVIADO NAVEGAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>556</v>
+      </c>
+      <c r="B194" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C194" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>DESOSPITALIZAÇÃO AMIL - TIME ERIC</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
+      <c r="O194" t="inlineStr"/>
+      <c r="P194" t="inlineStr"/>
+      <c r="Q194" t="inlineStr"/>
+      <c r="R194" t="inlineStr"/>
+      <c r="S194" t="inlineStr"/>
+      <c r="T194" t="inlineStr"/>
+      <c r="U194" t="inlineStr"/>
+      <c r="V194" t="inlineStr"/>
+      <c r="W194" t="inlineStr"/>
+      <c r="X194" t="inlineStr"/>
+      <c r="Y194" t="inlineStr"/>
+      <c r="Z194" t="inlineStr"/>
+      <c r="AA194" t="inlineStr"/>
+      <c r="AB194" t="inlineStr"/>
+      <c r="AC194" t="inlineStr"/>
+      <c r="AD194" t="inlineStr"/>
+      <c r="AE194" t="inlineStr"/>
+      <c r="AF194" t="inlineStr"/>
+      <c r="AG194" t="inlineStr"/>
+      <c r="AH194" t="inlineStr"/>
+      <c r="AI194" t="inlineStr"/>
+      <c r="AJ194" t="inlineStr"/>
+      <c r="AK194" t="n">
+        <v>95628334</v>
+      </c>
+      <c r="AL194" t="inlineStr">
+        <is>
+          <t>DANIELLY CRISTINY DA SILVA ASSUMPCAO</t>
+        </is>
+      </c>
+      <c r="AM194" t="inlineStr">
+        <is>
+          <t>172.741.297-40</t>
+        </is>
+      </c>
+      <c r="AN194" s="1" t="n">
+        <v>38304</v>
+      </c>
+      <c r="AO194" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="AP194" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="AQ194" t="inlineStr">
+        <is>
+          <t>DUQUE DE CAXIAS</t>
+        </is>
+      </c>
+      <c r="AR194" t="inlineStr">
+        <is>
+          <t>BRONZE RJ</t>
+        </is>
+      </c>
+      <c r="AS194" t="inlineStr">
+        <is>
+          <t>21-980910360</t>
+        </is>
+      </c>
+      <c r="AT194" t="inlineStr">
+        <is>
+          <t>Saúde Mental</t>
+        </is>
+      </c>
+      <c r="AU194" t="inlineStr">
+        <is>
+          <t>Busca preventiva por bem-estar</t>
+        </is>
+      </c>
+      <c r="AV194" t="inlineStr"/>
+      <c r="AW194" t="inlineStr"/>
+      <c r="AX194" t="inlineStr"/>
+      <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr"/>
+      <c r="BA194" t="inlineStr"/>
+      <c r="BB194" t="inlineStr"/>
+      <c r="BC194" t="inlineStr"/>
+      <c r="BD194" t="inlineStr"/>
+      <c r="BE194" t="inlineStr"/>
+      <c r="BF194" t="inlineStr"/>
+      <c r="BG194" t="inlineStr"/>
+      <c r="BH194" t="inlineStr"/>
+      <c r="BI194" t="inlineStr"/>
+      <c r="BJ194" t="inlineStr"/>
+      <c r="BK194" t="inlineStr"/>
+      <c r="BL194" t="inlineStr"/>
+      <c r="BM194" t="inlineStr"/>
+      <c r="BN194" t="inlineStr"/>
+      <c r="BO194" t="inlineStr"/>
+      <c r="BP194" t="inlineStr"/>
+      <c r="BQ194" t="inlineStr"/>
+      <c r="BR194" t="inlineStr"/>
+      <c r="BS194" t="inlineStr"/>
+      <c r="BT194" t="inlineStr"/>
+      <c r="BU194" t="inlineStr"/>
+      <c r="BV194" t="inlineStr"/>
+      <c r="BW194" t="inlineStr"/>
+      <c r="BX194" t="inlineStr"/>
+      <c r="BY194" t="inlineStr"/>
+      <c r="BZ194" t="inlineStr"/>
+      <c r="CA194" t="inlineStr"/>
+      <c r="CB194" t="inlineStr"/>
+      <c r="CC194" t="inlineStr"/>
+      <c r="CD194" t="inlineStr"/>
+      <c r="CE194" t="inlineStr"/>
+      <c r="CF194" t="inlineStr"/>
+      <c r="CG194" t="inlineStr"/>
+      <c r="CH194" t="inlineStr"/>
+      <c r="CI194" t="inlineStr"/>
+      <c r="CJ194" t="inlineStr"/>
+      <c r="CK194" t="inlineStr"/>
+      <c r="CL194" t="inlineStr"/>
+      <c r="CM194" t="inlineStr"/>
+      <c r="CN194" t="inlineStr"/>
+      <c r="CO194" t="inlineStr"/>
+      <c r="CP194" t="inlineStr"/>
+      <c r="CQ194" t="inlineStr"/>
+      <c r="CR194" t="inlineStr"/>
+      <c r="CS194" t="inlineStr"/>
+      <c r="CT194" t="inlineStr"/>
+      <c r="CU194" t="inlineStr"/>
+      <c r="CV194" t="inlineStr"/>
+      <c r="CW194" t="inlineStr"/>
+      <c r="CX194" t="inlineStr"/>
+      <c r="CY194" t="inlineStr"/>
+      <c r="CZ194" t="inlineStr"/>
+      <c r="DA194" t="inlineStr"/>
+      <c r="DB194" t="inlineStr"/>
+      <c r="DC194" t="inlineStr"/>
+      <c r="DD194" t="inlineStr"/>
+      <c r="DE194" t="inlineStr"/>
+      <c r="DF194" t="inlineStr"/>
+      <c r="DG194" t="inlineStr"/>
+      <c r="DH194" t="inlineStr"/>
+      <c r="DI194" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>557</v>
+      </c>
+      <c r="B195" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C195" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>DESOSPITALIZAÇÃO AMIL - TIME ERIC</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
+      <c r="O195" t="inlineStr"/>
+      <c r="P195" t="inlineStr"/>
+      <c r="Q195" t="inlineStr"/>
+      <c r="R195" t="inlineStr"/>
+      <c r="S195" t="inlineStr"/>
+      <c r="T195" t="inlineStr"/>
+      <c r="U195" t="inlineStr"/>
+      <c r="V195" t="inlineStr"/>
+      <c r="W195" t="inlineStr"/>
+      <c r="X195" t="inlineStr"/>
+      <c r="Y195" t="inlineStr"/>
+      <c r="Z195" t="inlineStr"/>
+      <c r="AA195" t="inlineStr"/>
+      <c r="AB195" t="inlineStr"/>
+      <c r="AC195" t="inlineStr"/>
+      <c r="AD195" t="inlineStr"/>
+      <c r="AE195" t="inlineStr"/>
+      <c r="AF195" t="inlineStr"/>
+      <c r="AG195" t="inlineStr"/>
+      <c r="AH195" t="inlineStr"/>
+      <c r="AI195" t="inlineStr"/>
+      <c r="AJ195" t="inlineStr"/>
+      <c r="AK195" t="n">
+        <v>485879778</v>
+      </c>
+      <c r="AL195" t="inlineStr">
+        <is>
+          <t>ANA SANTOS DA SILVA</t>
+        </is>
+      </c>
+      <c r="AM195" t="inlineStr">
+        <is>
+          <t>018.505.337-84</t>
+        </is>
+      </c>
+      <c r="AN195" s="1" t="n">
+        <v>12260</v>
+      </c>
+      <c r="AO195" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="AP195" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="AQ195" t="inlineStr">
+        <is>
+          <t>RIO DE JANEIRO</t>
+        </is>
+      </c>
+      <c r="AR195" t="inlineStr">
+        <is>
+          <t>MEDIAL 500 NAC QP PF COP RC5</t>
+        </is>
+      </c>
+      <c r="AS195" t="n">
+        <v>21999118832</v>
+      </c>
+      <c r="AT195" t="inlineStr">
+        <is>
+          <t>Viva Bem</t>
+        </is>
+      </c>
+      <c r="AU195" t="inlineStr"/>
+      <c r="AV195" t="inlineStr"/>
+      <c r="AW195" t="inlineStr"/>
+      <c r="AX195" t="inlineStr"/>
+      <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr"/>
+      <c r="BA195" t="inlineStr"/>
+      <c r="BB195" t="inlineStr"/>
+      <c r="BC195" t="inlineStr"/>
+      <c r="BD195" t="inlineStr"/>
+      <c r="BE195" t="inlineStr"/>
+      <c r="BF195" t="inlineStr"/>
+      <c r="BG195" t="inlineStr"/>
+      <c r="BH195" t="inlineStr"/>
+      <c r="BI195" t="inlineStr"/>
+      <c r="BJ195" t="inlineStr"/>
+      <c r="BK195" t="inlineStr"/>
+      <c r="BL195" t="inlineStr"/>
+      <c r="BM195" t="inlineStr"/>
+      <c r="BN195" t="inlineStr"/>
+      <c r="BO195" t="inlineStr"/>
+      <c r="BP195" t="inlineStr"/>
+      <c r="BQ195" t="inlineStr"/>
+      <c r="BR195" t="inlineStr"/>
+      <c r="BS195" t="inlineStr"/>
+      <c r="BT195" t="inlineStr"/>
+      <c r="BU195" t="inlineStr"/>
+      <c r="BV195" t="inlineStr"/>
+      <c r="BW195" t="inlineStr"/>
+      <c r="BX195" t="inlineStr"/>
+      <c r="BY195" t="inlineStr"/>
+      <c r="BZ195" t="inlineStr"/>
+      <c r="CA195" t="inlineStr"/>
+      <c r="CB195" t="inlineStr"/>
+      <c r="CC195" t="inlineStr"/>
+      <c r="CD195" t="inlineStr"/>
+      <c r="CE195" t="inlineStr"/>
+      <c r="CF195" t="inlineStr"/>
+      <c r="CG195" t="inlineStr"/>
+      <c r="CH195" t="inlineStr"/>
+      <c r="CI195" t="inlineStr"/>
+      <c r="CJ195" t="inlineStr"/>
+      <c r="CK195" t="inlineStr"/>
+      <c r="CL195" t="inlineStr"/>
+      <c r="CM195" t="inlineStr"/>
+      <c r="CN195" t="inlineStr"/>
+      <c r="CO195" t="inlineStr"/>
+      <c r="CP195" t="inlineStr"/>
+      <c r="CQ195" t="inlineStr"/>
+      <c r="CR195" t="inlineStr"/>
+      <c r="CS195" t="inlineStr"/>
+      <c r="CT195" t="inlineStr"/>
+      <c r="CU195" t="inlineStr"/>
+      <c r="CV195" t="inlineStr"/>
+      <c r="CW195" t="inlineStr"/>
+      <c r="CX195" t="inlineStr"/>
+      <c r="CY195" t="inlineStr"/>
+      <c r="CZ195" t="inlineStr"/>
+      <c r="DA195" t="inlineStr"/>
+      <c r="DB195" t="inlineStr"/>
+      <c r="DC195" t="inlineStr"/>
+      <c r="DD195" t="inlineStr"/>
+      <c r="DE195" t="inlineStr"/>
+      <c r="DF195" t="inlineStr"/>
+      <c r="DG195" t="inlineStr"/>
+      <c r="DH195" t="inlineStr"/>
+      <c r="DI195" t="inlineStr">
+        <is>
+          <t>DESCARTADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>558</v>
+      </c>
+      <c r="B196" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C196" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>DESOSPITALIZAÇÃO AMIL - TIME ERIC</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
+      <c r="O196" t="inlineStr"/>
+      <c r="P196" t="inlineStr"/>
+      <c r="Q196" t="inlineStr"/>
+      <c r="R196" t="inlineStr"/>
+      <c r="S196" t="inlineStr"/>
+      <c r="T196" t="inlineStr"/>
+      <c r="U196" t="inlineStr"/>
+      <c r="V196" t="inlineStr"/>
+      <c r="W196" t="inlineStr"/>
+      <c r="X196" t="inlineStr"/>
+      <c r="Y196" t="inlineStr"/>
+      <c r="Z196" t="inlineStr"/>
+      <c r="AA196" t="inlineStr"/>
+      <c r="AB196" t="inlineStr"/>
+      <c r="AC196" t="inlineStr"/>
+      <c r="AD196" t="inlineStr"/>
+      <c r="AE196" t="inlineStr"/>
+      <c r="AF196" t="inlineStr"/>
+      <c r="AG196" t="inlineStr"/>
+      <c r="AH196" t="inlineStr"/>
+      <c r="AI196" t="inlineStr"/>
+      <c r="AJ196" t="inlineStr"/>
+      <c r="AK196" t="n">
+        <v>997064309</v>
+      </c>
+      <c r="AL196" t="inlineStr">
+        <is>
+          <t>ALINE FRANCO MARQUES</t>
+        </is>
+      </c>
+      <c r="AM196" t="inlineStr">
+        <is>
+          <t>485.248.428-73</t>
+        </is>
+      </c>
+      <c r="AN196" s="1" t="n">
+        <v>35985</v>
+      </c>
+      <c r="AO196" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="AP196" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="AQ196" t="inlineStr">
+        <is>
+          <t>SAO PAULO</t>
+        </is>
+      </c>
+      <c r="AR196" t="inlineStr">
+        <is>
+          <t>AMIL FACIL</t>
+        </is>
+      </c>
+      <c r="AS196" t="n">
+        <v>11997064309</v>
+      </c>
+      <c r="AT196" t="inlineStr">
+        <is>
+          <t>Gestação Segura</t>
+        </is>
+      </c>
+      <c r="AU196" t="inlineStr"/>
+      <c r="AV196" t="inlineStr"/>
+      <c r="AW196" t="inlineStr"/>
+      <c r="AX196" t="inlineStr"/>
+      <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr"/>
+      <c r="BA196" t="inlineStr"/>
+      <c r="BB196" t="inlineStr"/>
+      <c r="BC196" t="inlineStr"/>
+      <c r="BD196" t="inlineStr"/>
+      <c r="BE196" t="inlineStr"/>
+      <c r="BF196" t="inlineStr"/>
+      <c r="BG196" t="inlineStr"/>
+      <c r="BH196" t="inlineStr"/>
+      <c r="BI196" t="inlineStr"/>
+      <c r="BJ196" t="inlineStr"/>
+      <c r="BK196" t="inlineStr"/>
+      <c r="BL196" t="inlineStr"/>
+      <c r="BM196" t="inlineStr"/>
+      <c r="BN196" t="inlineStr"/>
+      <c r="BO196" t="inlineStr"/>
+      <c r="BP196" t="inlineStr"/>
+      <c r="BQ196" t="inlineStr"/>
+      <c r="BR196" t="inlineStr"/>
+      <c r="BS196" t="inlineStr"/>
+      <c r="BT196" t="inlineStr"/>
+      <c r="BU196" t="inlineStr"/>
+      <c r="BV196" t="inlineStr"/>
+      <c r="BW196" t="inlineStr"/>
+      <c r="BX196" t="inlineStr"/>
+      <c r="BY196" t="inlineStr"/>
+      <c r="BZ196" t="inlineStr"/>
+      <c r="CA196" t="inlineStr"/>
+      <c r="CB196" t="inlineStr"/>
+      <c r="CC196" t="inlineStr"/>
+      <c r="CD196" t="inlineStr"/>
+      <c r="CE196" t="inlineStr"/>
+      <c r="CF196" t="inlineStr"/>
+      <c r="CG196" t="inlineStr"/>
+      <c r="CH196" t="inlineStr"/>
+      <c r="CI196" t="inlineStr"/>
+      <c r="CJ196" t="inlineStr"/>
+      <c r="CK196" t="inlineStr"/>
+      <c r="CL196" t="inlineStr"/>
+      <c r="CM196" t="inlineStr"/>
+      <c r="CN196" t="inlineStr"/>
+      <c r="CO196" t="inlineStr"/>
+      <c r="CP196" t="inlineStr"/>
+      <c r="CQ196" t="inlineStr"/>
+      <c r="CR196" t="inlineStr"/>
+      <c r="CS196" t="inlineStr"/>
+      <c r="CT196" t="inlineStr"/>
+      <c r="CU196" t="inlineStr"/>
+      <c r="CV196" t="inlineStr"/>
+      <c r="CW196" t="inlineStr"/>
+      <c r="CX196" t="inlineStr"/>
+      <c r="CY196" t="inlineStr"/>
+      <c r="CZ196" t="inlineStr"/>
+      <c r="DA196" t="inlineStr"/>
+      <c r="DB196" t="inlineStr"/>
+      <c r="DC196" t="inlineStr"/>
+      <c r="DD196" t="inlineStr"/>
+      <c r="DE196" t="inlineStr"/>
+      <c r="DF196" t="inlineStr"/>
+      <c r="DG196" t="inlineStr"/>
+      <c r="DH196" t="inlineStr"/>
+      <c r="DI196" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>559</v>
+      </c>
+      <c r="B197" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C197" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>DESOSPITALIZAÇÃO AMIL - TIME ERIC</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr"/>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
+      <c r="O197" t="inlineStr"/>
+      <c r="P197" t="inlineStr"/>
+      <c r="Q197" t="inlineStr"/>
+      <c r="R197" t="inlineStr"/>
+      <c r="S197" t="inlineStr"/>
+      <c r="T197" t="inlineStr"/>
+      <c r="U197" t="inlineStr"/>
+      <c r="V197" t="inlineStr"/>
+      <c r="W197" t="inlineStr"/>
+      <c r="X197" t="inlineStr"/>
+      <c r="Y197" t="inlineStr"/>
+      <c r="Z197" t="inlineStr"/>
+      <c r="AA197" t="inlineStr"/>
+      <c r="AB197" t="inlineStr"/>
+      <c r="AC197" t="inlineStr"/>
+      <c r="AD197" t="inlineStr"/>
+      <c r="AE197" t="inlineStr"/>
+      <c r="AF197" t="inlineStr"/>
+      <c r="AG197" t="inlineStr"/>
+      <c r="AH197" t="inlineStr"/>
+      <c r="AI197" t="inlineStr"/>
+      <c r="AJ197" t="inlineStr"/>
+      <c r="AK197" t="n">
+        <v>96260903</v>
+      </c>
+      <c r="AL197" t="inlineStr">
+        <is>
+          <t>BHIANCA DOS SANTOS CAMPOS</t>
+        </is>
+      </c>
+      <c r="AM197" t="inlineStr">
+        <is>
+          <t>133.317.837-90</t>
+        </is>
+      </c>
+      <c r="AN197" s="1" t="n">
+        <v>33716</v>
+      </c>
+      <c r="AO197" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="AP197" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="AQ197" t="inlineStr">
+        <is>
+          <t>rio de janeiro</t>
+        </is>
+      </c>
+      <c r="AR197" t="inlineStr">
+        <is>
+          <t>AMIL COLABORADOR QC NAC COPART PJ ADM</t>
+        </is>
+      </c>
+      <c r="AS197" t="n">
+        <v>21976516379</v>
+      </c>
+      <c r="AT197" t="inlineStr">
+        <is>
+          <t>Saúde Mental</t>
+        </is>
+      </c>
+      <c r="AU197" t="inlineStr">
+        <is>
+          <t>Sofrimento situacional (Ex: trabalho, família)</t>
+        </is>
+      </c>
+      <c r="AV197" t="inlineStr"/>
+      <c r="AW197" t="inlineStr"/>
+      <c r="AX197" t="inlineStr"/>
+      <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr"/>
+      <c r="BA197" t="inlineStr"/>
+      <c r="BB197" t="inlineStr"/>
+      <c r="BC197" t="inlineStr"/>
+      <c r="BD197" t="inlineStr"/>
+      <c r="BE197" t="inlineStr"/>
+      <c r="BF197" t="inlineStr"/>
+      <c r="BG197" t="inlineStr"/>
+      <c r="BH197" t="inlineStr"/>
+      <c r="BI197" t="inlineStr"/>
+      <c r="BJ197" t="inlineStr"/>
+      <c r="BK197" t="inlineStr"/>
+      <c r="BL197" t="inlineStr"/>
+      <c r="BM197" t="inlineStr"/>
+      <c r="BN197" t="inlineStr"/>
+      <c r="BO197" t="inlineStr"/>
+      <c r="BP197" t="inlineStr"/>
+      <c r="BQ197" t="inlineStr"/>
+      <c r="BR197" t="inlineStr"/>
+      <c r="BS197" t="inlineStr"/>
+      <c r="BT197" t="inlineStr"/>
+      <c r="BU197" t="inlineStr"/>
+      <c r="BV197" t="inlineStr"/>
+      <c r="BW197" t="inlineStr"/>
+      <c r="BX197" t="inlineStr"/>
+      <c r="BY197" t="inlineStr"/>
+      <c r="BZ197" t="inlineStr"/>
+      <c r="CA197" t="inlineStr"/>
+      <c r="CB197" t="inlineStr"/>
+      <c r="CC197" t="inlineStr"/>
+      <c r="CD197" t="inlineStr"/>
+      <c r="CE197" t="inlineStr"/>
+      <c r="CF197" t="inlineStr"/>
+      <c r="CG197" t="inlineStr"/>
+      <c r="CH197" t="inlineStr"/>
+      <c r="CI197" t="inlineStr"/>
+      <c r="CJ197" t="inlineStr"/>
+      <c r="CK197" t="inlineStr"/>
+      <c r="CL197" t="inlineStr"/>
+      <c r="CM197" t="inlineStr"/>
+      <c r="CN197" t="inlineStr"/>
+      <c r="CO197" t="inlineStr"/>
+      <c r="CP197" t="inlineStr"/>
+      <c r="CQ197" t="inlineStr"/>
+      <c r="CR197" t="inlineStr"/>
+      <c r="CS197" t="inlineStr"/>
+      <c r="CT197" t="inlineStr"/>
+      <c r="CU197" t="inlineStr"/>
+      <c r="CV197" t="inlineStr"/>
+      <c r="CW197" t="inlineStr"/>
+      <c r="CX197" t="inlineStr"/>
+      <c r="CY197" t="inlineStr"/>
+      <c r="CZ197" t="inlineStr"/>
+      <c r="DA197" t="inlineStr"/>
+      <c r="DB197" t="inlineStr"/>
+      <c r="DC197" t="inlineStr"/>
+      <c r="DD197" t="inlineStr"/>
+      <c r="DE197" t="inlineStr"/>
+      <c r="DF197" t="inlineStr"/>
+      <c r="DG197" t="inlineStr"/>
+      <c r="DH197" t="inlineStr"/>
+      <c r="DI197" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>560</v>
+      </c>
+      <c r="B198" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C198" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>DESOSPITALIZAÇÃO AMIL - TIME ERIC</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
+      <c r="O198" t="inlineStr"/>
+      <c r="P198" t="inlineStr"/>
+      <c r="Q198" t="inlineStr"/>
+      <c r="R198" t="inlineStr"/>
+      <c r="S198" t="inlineStr"/>
+      <c r="T198" t="inlineStr"/>
+      <c r="U198" t="inlineStr"/>
+      <c r="V198" t="inlineStr"/>
+      <c r="W198" t="inlineStr"/>
+      <c r="X198" t="inlineStr"/>
+      <c r="Y198" t="inlineStr"/>
+      <c r="Z198" t="inlineStr"/>
+      <c r="AA198" t="inlineStr"/>
+      <c r="AB198" t="inlineStr"/>
+      <c r="AC198" t="inlineStr"/>
+      <c r="AD198" t="inlineStr"/>
+      <c r="AE198" t="inlineStr"/>
+      <c r="AF198" t="inlineStr"/>
+      <c r="AG198" t="inlineStr"/>
+      <c r="AH198" t="inlineStr"/>
+      <c r="AI198" t="inlineStr"/>
+      <c r="AJ198" t="inlineStr"/>
+      <c r="AK198" t="n">
+        <v>97649804</v>
+      </c>
+      <c r="AL198" t="inlineStr">
+        <is>
+          <t>JHESSICA MARIA MELO BARROZO</t>
+        </is>
+      </c>
+      <c r="AM198" t="inlineStr">
+        <is>
+          <t>032.074.883-90</t>
+        </is>
+      </c>
+      <c r="AN198" s="1" t="n">
+        <v>33284</v>
+      </c>
+      <c r="AO198" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="AP198" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="AQ198" t="inlineStr">
+        <is>
+          <t>SAO PAULO</t>
+        </is>
+      </c>
+      <c r="AR198" t="inlineStr">
+        <is>
+          <t>AMIL</t>
+        </is>
+      </c>
+      <c r="AS198" t="n">
+        <v>11983342999</v>
+      </c>
+      <c r="AT198" t="inlineStr">
+        <is>
+          <t>Gestação Segura</t>
+        </is>
+      </c>
+      <c r="AU198" t="inlineStr"/>
+      <c r="AV198" t="inlineStr"/>
+      <c r="AW198" t="inlineStr"/>
+      <c r="AX198" t="inlineStr"/>
+      <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr"/>
+      <c r="BA198" t="inlineStr"/>
+      <c r="BB198" t="inlineStr"/>
+      <c r="BC198" t="inlineStr"/>
+      <c r="BD198" t="inlineStr"/>
+      <c r="BE198" t="inlineStr"/>
+      <c r="BF198" t="inlineStr"/>
+      <c r="BG198" t="inlineStr"/>
+      <c r="BH198" t="inlineStr"/>
+      <c r="BI198" t="inlineStr"/>
+      <c r="BJ198" t="inlineStr"/>
+      <c r="BK198" t="inlineStr"/>
+      <c r="BL198" t="inlineStr"/>
+      <c r="BM198" t="inlineStr"/>
+      <c r="BN198" t="inlineStr"/>
+      <c r="BO198" t="inlineStr"/>
+      <c r="BP198" t="inlineStr"/>
+      <c r="BQ198" t="inlineStr"/>
+      <c r="BR198" t="inlineStr"/>
+      <c r="BS198" t="inlineStr"/>
+      <c r="BT198" t="inlineStr"/>
+      <c r="BU198" t="inlineStr"/>
+      <c r="BV198" t="inlineStr"/>
+      <c r="BW198" t="inlineStr"/>
+      <c r="BX198" t="inlineStr"/>
+      <c r="BY198" t="inlineStr"/>
+      <c r="BZ198" t="inlineStr"/>
+      <c r="CA198" t="inlineStr"/>
+      <c r="CB198" t="inlineStr"/>
+      <c r="CC198" t="inlineStr"/>
+      <c r="CD198" t="inlineStr"/>
+      <c r="CE198" t="inlineStr"/>
+      <c r="CF198" t="inlineStr"/>
+      <c r="CG198" t="inlineStr"/>
+      <c r="CH198" t="inlineStr"/>
+      <c r="CI198" t="inlineStr"/>
+      <c r="CJ198" t="inlineStr"/>
+      <c r="CK198" t="inlineStr"/>
+      <c r="CL198" t="inlineStr"/>
+      <c r="CM198" t="inlineStr"/>
+      <c r="CN198" t="inlineStr"/>
+      <c r="CO198" t="inlineStr"/>
+      <c r="CP198" t="inlineStr"/>
+      <c r="CQ198" t="inlineStr"/>
+      <c r="CR198" t="inlineStr"/>
+      <c r="CS198" t="inlineStr"/>
+      <c r="CT198" t="inlineStr"/>
+      <c r="CU198" t="inlineStr"/>
+      <c r="CV198" t="inlineStr"/>
+      <c r="CW198" t="inlineStr"/>
+      <c r="CX198" t="inlineStr"/>
+      <c r="CY198" t="inlineStr"/>
+      <c r="CZ198" t="inlineStr"/>
+      <c r="DA198" t="inlineStr"/>
+      <c r="DB198" t="inlineStr"/>
+      <c r="DC198" t="inlineStr"/>
+      <c r="DD198" t="inlineStr"/>
+      <c r="DE198" t="inlineStr"/>
+      <c r="DF198" t="inlineStr"/>
+      <c r="DG198" t="inlineStr"/>
+      <c r="DH198" t="inlineStr"/>
+      <c r="DI198" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>561</v>
+      </c>
+      <c r="B199" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C199" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>DESOSPITALIZAÇÃO AMIL - TIME ERIC</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr"/>
+      <c r="N199" t="inlineStr"/>
+      <c r="O199" t="inlineStr"/>
+      <c r="P199" t="inlineStr"/>
+      <c r="Q199" t="inlineStr"/>
+      <c r="R199" t="inlineStr"/>
+      <c r="S199" t="inlineStr"/>
+      <c r="T199" t="inlineStr"/>
+      <c r="U199" t="inlineStr"/>
+      <c r="V199" t="inlineStr"/>
+      <c r="W199" t="inlineStr"/>
+      <c r="X199" t="inlineStr"/>
+      <c r="Y199" t="inlineStr"/>
+      <c r="Z199" t="inlineStr"/>
+      <c r="AA199" t="inlineStr"/>
+      <c r="AB199" t="inlineStr"/>
+      <c r="AC199" t="inlineStr"/>
+      <c r="AD199" t="inlineStr"/>
+      <c r="AE199" t="inlineStr"/>
+      <c r="AF199" t="inlineStr"/>
+      <c r="AG199" t="inlineStr"/>
+      <c r="AH199" t="inlineStr"/>
+      <c r="AI199" t="inlineStr"/>
+      <c r="AJ199" t="inlineStr"/>
+      <c r="AK199" t="n">
+        <v>86429049</v>
+      </c>
+      <c r="AL199" t="inlineStr">
+        <is>
+          <t>TAYLLA BARBOSA MANTUANO</t>
+        </is>
+      </c>
+      <c r="AM199" t="inlineStr">
+        <is>
+          <t>132.538.337-63</t>
+        </is>
+      </c>
+      <c r="AN199" s="1" t="n">
+        <v>32983</v>
+      </c>
+      <c r="AO199" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="AP199" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="AQ199" t="inlineStr">
+        <is>
+          <t>RIO DE JANEIRO</t>
+        </is>
+      </c>
+      <c r="AR199" t="inlineStr">
+        <is>
+          <t>AMIL FÁCIL S40 QC RJ GM COPART PJ</t>
+        </is>
+      </c>
+      <c r="AS199" t="n">
+        <v>21989177455</v>
+      </c>
+      <c r="AT199" t="inlineStr">
+        <is>
+          <t>Saúde Mental</t>
+        </is>
+      </c>
+      <c r="AU199" t="inlineStr">
+        <is>
+          <t>Sofrimento situacional (Ex: trabalho, família)</t>
+        </is>
+      </c>
+      <c r="AV199" t="inlineStr"/>
+      <c r="AW199" t="inlineStr"/>
+      <c r="AX199" t="inlineStr"/>
+      <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr"/>
+      <c r="BA199" t="inlineStr"/>
+      <c r="BB199" t="inlineStr"/>
+      <c r="BC199" t="inlineStr"/>
+      <c r="BD199" t="inlineStr"/>
+      <c r="BE199" t="inlineStr"/>
+      <c r="BF199" t="inlineStr"/>
+      <c r="BG199" t="inlineStr"/>
+      <c r="BH199" t="inlineStr"/>
+      <c r="BI199" t="inlineStr"/>
+      <c r="BJ199" t="inlineStr"/>
+      <c r="BK199" t="inlineStr"/>
+      <c r="BL199" t="inlineStr"/>
+      <c r="BM199" t="inlineStr"/>
+      <c r="BN199" t="inlineStr"/>
+      <c r="BO199" t="inlineStr"/>
+      <c r="BP199" t="inlineStr"/>
+      <c r="BQ199" t="inlineStr"/>
+      <c r="BR199" t="inlineStr"/>
+      <c r="BS199" t="inlineStr"/>
+      <c r="BT199" t="inlineStr"/>
+      <c r="BU199" t="inlineStr"/>
+      <c r="BV199" t="inlineStr"/>
+      <c r="BW199" t="inlineStr"/>
+      <c r="BX199" t="inlineStr"/>
+      <c r="BY199" t="inlineStr"/>
+      <c r="BZ199" t="inlineStr"/>
+      <c r="CA199" t="inlineStr"/>
+      <c r="CB199" t="inlineStr"/>
+      <c r="CC199" t="inlineStr"/>
+      <c r="CD199" t="inlineStr"/>
+      <c r="CE199" t="inlineStr"/>
+      <c r="CF199" t="inlineStr"/>
+      <c r="CG199" t="inlineStr"/>
+      <c r="CH199" t="inlineStr"/>
+      <c r="CI199" t="inlineStr"/>
+      <c r="CJ199" t="inlineStr"/>
+      <c r="CK199" t="inlineStr"/>
+      <c r="CL199" t="inlineStr"/>
+      <c r="CM199" t="inlineStr"/>
+      <c r="CN199" t="inlineStr"/>
+      <c r="CO199" t="inlineStr"/>
+      <c r="CP199" t="inlineStr"/>
+      <c r="CQ199" t="inlineStr"/>
+      <c r="CR199" t="inlineStr"/>
+      <c r="CS199" t="inlineStr"/>
+      <c r="CT199" t="inlineStr"/>
+      <c r="CU199" t="inlineStr"/>
+      <c r="CV199" t="inlineStr"/>
+      <c r="CW199" t="inlineStr"/>
+      <c r="CX199" t="inlineStr"/>
+      <c r="CY199" t="inlineStr"/>
+      <c r="CZ199" t="inlineStr"/>
+      <c r="DA199" t="inlineStr"/>
+      <c r="DB199" t="inlineStr"/>
+      <c r="DC199" t="inlineStr"/>
+      <c r="DD199" t="inlineStr"/>
+      <c r="DE199" t="inlineStr"/>
+      <c r="DF199" t="inlineStr"/>
+      <c r="DG199" t="inlineStr"/>
+      <c r="DH199" t="inlineStr"/>
+      <c r="DI199" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>562</v>
+      </c>
+      <c r="B200" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C200" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>DESOSPITALIZAÇÃO AMIL - TIME ERIC</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr"/>
+      <c r="N200" t="inlineStr"/>
+      <c r="O200" t="inlineStr"/>
+      <c r="P200" t="inlineStr"/>
+      <c r="Q200" t="inlineStr"/>
+      <c r="R200" t="inlineStr"/>
+      <c r="S200" t="inlineStr"/>
+      <c r="T200" t="inlineStr"/>
+      <c r="U200" t="inlineStr"/>
+      <c r="V200" t="inlineStr"/>
+      <c r="W200" t="inlineStr"/>
+      <c r="X200" t="inlineStr"/>
+      <c r="Y200" t="inlineStr"/>
+      <c r="Z200" t="inlineStr"/>
+      <c r="AA200" t="inlineStr"/>
+      <c r="AB200" t="inlineStr"/>
+      <c r="AC200" t="inlineStr"/>
+      <c r="AD200" t="inlineStr"/>
+      <c r="AE200" t="inlineStr"/>
+      <c r="AF200" t="inlineStr"/>
+      <c r="AG200" t="inlineStr"/>
+      <c r="AH200" t="inlineStr"/>
+      <c r="AI200" t="inlineStr"/>
+      <c r="AJ200" t="inlineStr"/>
+      <c r="AK200" t="n">
+        <v>450180980</v>
+      </c>
+      <c r="AL200" t="inlineStr">
+        <is>
+          <t>NILZA LIGUORI CESAR</t>
+        </is>
+      </c>
+      <c r="AM200" t="inlineStr">
+        <is>
+          <t>882.275.708-44</t>
+        </is>
+      </c>
+      <c r="AN200" s="1" t="n">
+        <v>19042</v>
+      </c>
+      <c r="AO200" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="AP200" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="AQ200" t="inlineStr">
+        <is>
+          <t>sp</t>
+        </is>
+      </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>AMESP ESPECIAL IIC</t>
+        </is>
+      </c>
+      <c r="AS200" t="n">
+        <v>11971137337</v>
+      </c>
+      <c r="AT200" t="inlineStr">
+        <is>
+          <t>Bem Cuidado</t>
+        </is>
+      </c>
+      <c r="AU200" t="inlineStr"/>
+      <c r="AV200" t="inlineStr"/>
+      <c r="AW200" t="inlineStr"/>
+      <c r="AX200" t="inlineStr"/>
+      <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr"/>
+      <c r="BA200" t="inlineStr"/>
+      <c r="BB200" t="inlineStr"/>
+      <c r="BC200" t="inlineStr"/>
+      <c r="BD200" t="inlineStr"/>
+      <c r="BE200" t="inlineStr"/>
+      <c r="BF200" t="inlineStr"/>
+      <c r="BG200" t="inlineStr"/>
+      <c r="BH200" t="inlineStr"/>
+      <c r="BI200" t="inlineStr"/>
+      <c r="BJ200" t="inlineStr"/>
+      <c r="BK200" t="inlineStr"/>
+      <c r="BL200" t="inlineStr"/>
+      <c r="BM200" t="inlineStr"/>
+      <c r="BN200" t="inlineStr"/>
+      <c r="BO200" t="inlineStr"/>
+      <c r="BP200" t="inlineStr"/>
+      <c r="BQ200" t="inlineStr"/>
+      <c r="BR200" t="inlineStr"/>
+      <c r="BS200" t="inlineStr"/>
+      <c r="BT200" t="inlineStr"/>
+      <c r="BU200" t="inlineStr"/>
+      <c r="BV200" t="inlineStr"/>
+      <c r="BW200" t="inlineStr"/>
+      <c r="BX200" t="inlineStr"/>
+      <c r="BY200" t="inlineStr"/>
+      <c r="BZ200" t="inlineStr"/>
+      <c r="CA200" t="inlineStr"/>
+      <c r="CB200" t="inlineStr"/>
+      <c r="CC200" t="inlineStr"/>
+      <c r="CD200" t="inlineStr"/>
+      <c r="CE200" t="inlineStr"/>
+      <c r="CF200" t="inlineStr"/>
+      <c r="CG200" t="inlineStr"/>
+      <c r="CH200" t="inlineStr"/>
+      <c r="CI200" t="inlineStr"/>
+      <c r="CJ200" t="inlineStr"/>
+      <c r="CK200" t="inlineStr"/>
+      <c r="CL200" t="inlineStr"/>
+      <c r="CM200" t="inlineStr"/>
+      <c r="CN200" t="inlineStr"/>
+      <c r="CO200" t="inlineStr"/>
+      <c r="CP200" t="inlineStr"/>
+      <c r="CQ200" t="inlineStr"/>
+      <c r="CR200" t="inlineStr"/>
+      <c r="CS200" t="inlineStr"/>
+      <c r="CT200" t="inlineStr"/>
+      <c r="CU200" t="inlineStr"/>
+      <c r="CV200" t="inlineStr"/>
+      <c r="CW200" t="inlineStr"/>
+      <c r="CX200" t="inlineStr"/>
+      <c r="CY200" t="inlineStr"/>
+      <c r="CZ200" t="inlineStr"/>
+      <c r="DA200" t="inlineStr"/>
+      <c r="DB200" t="inlineStr"/>
+      <c r="DC200" t="inlineStr"/>
+      <c r="DD200" t="inlineStr"/>
+      <c r="DE200" t="inlineStr"/>
+      <c r="DF200" t="inlineStr"/>
+      <c r="DG200" t="inlineStr"/>
+      <c r="DH200" t="inlineStr"/>
+      <c r="DI200" t="inlineStr">
+        <is>
+          <t>DESCARTADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>563</v>
+      </c>
+      <c r="B201" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C201" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>DESOSPITALIZAÇÃO AMIL - TIME ERIC</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr"/>
+      <c r="O201" t="inlineStr"/>
+      <c r="P201" t="inlineStr"/>
+      <c r="Q201" t="inlineStr"/>
+      <c r="R201" t="inlineStr"/>
+      <c r="S201" t="inlineStr"/>
+      <c r="T201" t="inlineStr"/>
+      <c r="U201" t="inlineStr"/>
+      <c r="V201" t="inlineStr"/>
+      <c r="W201" t="inlineStr"/>
+      <c r="X201" t="inlineStr"/>
+      <c r="Y201" t="inlineStr"/>
+      <c r="Z201" t="inlineStr"/>
+      <c r="AA201" t="inlineStr"/>
+      <c r="AB201" t="inlineStr"/>
+      <c r="AC201" t="inlineStr"/>
+      <c r="AD201" t="inlineStr"/>
+      <c r="AE201" t="inlineStr"/>
+      <c r="AF201" t="inlineStr"/>
+      <c r="AG201" t="inlineStr"/>
+      <c r="AH201" t="inlineStr"/>
+      <c r="AI201" t="inlineStr"/>
+      <c r="AJ201" t="inlineStr"/>
+      <c r="AK201" t="n">
+        <v>88169352</v>
+      </c>
+      <c r="AL201" t="inlineStr">
+        <is>
+          <t>NEUZA RAMOS</t>
+        </is>
+      </c>
+      <c r="AM201" t="inlineStr">
+        <is>
+          <t>111.889.638-64</t>
+        </is>
+      </c>
+      <c r="AN201" s="1" t="n">
+        <v>19979</v>
+      </c>
+      <c r="AO201" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="AP201" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="AQ201" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="AR201" t="inlineStr">
+        <is>
+          <t>AMIL FÁCIL F110 QC SP GM COPART TP PJ_PME</t>
+        </is>
+      </c>
+      <c r="AS201" t="n">
+        <v>11978700325</v>
+      </c>
+      <c r="AT201" t="inlineStr">
+        <is>
+          <t>Bem Cuidado</t>
+        </is>
+      </c>
+      <c r="AU201" t="inlineStr"/>
+      <c r="AV201" t="inlineStr"/>
+      <c r="AW201" t="inlineStr"/>
+      <c r="AX201" t="inlineStr"/>
+      <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr"/>
+      <c r="BA201" t="inlineStr"/>
+      <c r="BB201" t="inlineStr"/>
+      <c r="BC201" t="inlineStr"/>
+      <c r="BD201" t="inlineStr"/>
+      <c r="BE201" t="inlineStr"/>
+      <c r="BF201" t="inlineStr"/>
+      <c r="BG201" t="inlineStr"/>
+      <c r="BH201" t="inlineStr"/>
+      <c r="BI201" t="inlineStr"/>
+      <c r="BJ201" t="inlineStr"/>
+      <c r="BK201" t="inlineStr"/>
+      <c r="BL201" t="inlineStr"/>
+      <c r="BM201" t="inlineStr"/>
+      <c r="BN201" t="inlineStr"/>
+      <c r="BO201" t="inlineStr"/>
+      <c r="BP201" t="inlineStr"/>
+      <c r="BQ201" t="inlineStr"/>
+      <c r="BR201" t="inlineStr"/>
+      <c r="BS201" t="inlineStr"/>
+      <c r="BT201" t="inlineStr"/>
+      <c r="BU201" t="inlineStr"/>
+      <c r="BV201" t="inlineStr"/>
+      <c r="BW201" t="inlineStr"/>
+      <c r="BX201" t="inlineStr"/>
+      <c r="BY201" t="inlineStr"/>
+      <c r="BZ201" t="inlineStr"/>
+      <c r="CA201" t="inlineStr"/>
+      <c r="CB201" t="inlineStr"/>
+      <c r="CC201" t="inlineStr"/>
+      <c r="CD201" t="inlineStr"/>
+      <c r="CE201" t="inlineStr"/>
+      <c r="CF201" t="inlineStr"/>
+      <c r="CG201" t="inlineStr"/>
+      <c r="CH201" t="inlineStr"/>
+      <c r="CI201" t="inlineStr"/>
+      <c r="CJ201" t="inlineStr"/>
+      <c r="CK201" t="inlineStr"/>
+      <c r="CL201" t="inlineStr"/>
+      <c r="CM201" t="inlineStr"/>
+      <c r="CN201" t="inlineStr"/>
+      <c r="CO201" t="inlineStr"/>
+      <c r="CP201" t="inlineStr"/>
+      <c r="CQ201" t="inlineStr"/>
+      <c r="CR201" t="inlineStr"/>
+      <c r="CS201" t="inlineStr"/>
+      <c r="CT201" t="inlineStr"/>
+      <c r="CU201" t="inlineStr"/>
+      <c r="CV201" t="inlineStr"/>
+      <c r="CW201" t="inlineStr"/>
+      <c r="CX201" t="inlineStr"/>
+      <c r="CY201" t="inlineStr"/>
+      <c r="CZ201" t="inlineStr"/>
+      <c r="DA201" t="inlineStr"/>
+      <c r="DB201" t="inlineStr"/>
+      <c r="DC201" t="inlineStr"/>
+      <c r="DD201" t="inlineStr"/>
+      <c r="DE201" t="inlineStr"/>
+      <c r="DF201" t="inlineStr"/>
+      <c r="DG201" t="inlineStr"/>
+      <c r="DH201" t="inlineStr"/>
+      <c r="DI201" t="inlineStr">
+        <is>
+          <t>DESCARTADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>564</v>
+      </c>
+      <c r="B202" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C202" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>DESOSPITALIZAÇÃO AMIL - TIME ERIC</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
+      <c r="O202" t="inlineStr"/>
+      <c r="P202" t="inlineStr"/>
+      <c r="Q202" t="inlineStr"/>
+      <c r="R202" t="inlineStr"/>
+      <c r="S202" t="inlineStr"/>
+      <c r="T202" t="inlineStr"/>
+      <c r="U202" t="inlineStr"/>
+      <c r="V202" t="inlineStr"/>
+      <c r="W202" t="inlineStr"/>
+      <c r="X202" t="inlineStr"/>
+      <c r="Y202" t="inlineStr"/>
+      <c r="Z202" t="inlineStr"/>
+      <c r="AA202" t="inlineStr"/>
+      <c r="AB202" t="inlineStr"/>
+      <c r="AC202" t="inlineStr"/>
+      <c r="AD202" t="inlineStr"/>
+      <c r="AE202" t="inlineStr"/>
+      <c r="AF202" t="inlineStr"/>
+      <c r="AG202" t="inlineStr"/>
+      <c r="AH202" t="inlineStr"/>
+      <c r="AI202" t="inlineStr"/>
+      <c r="AJ202" t="inlineStr"/>
+      <c r="AK202" t="n">
+        <v>94079577</v>
+      </c>
+      <c r="AL202" t="inlineStr">
+        <is>
+          <t>AMAURI BELO DE SOUZA</t>
+        </is>
+      </c>
+      <c r="AM202" t="inlineStr">
+        <is>
+          <t>090.417.308-93</t>
+        </is>
+      </c>
+      <c r="AN202" s="1" t="n">
+        <v>23565</v>
+      </c>
+      <c r="AO202" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="AP202" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="AQ202" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="AR202" t="inlineStr">
+        <is>
+          <t>BRONZE SP COPART</t>
+        </is>
+      </c>
+      <c r="AS202" t="inlineStr">
+        <is>
+          <t>11959614995/11967374773</t>
+        </is>
+      </c>
+      <c r="AT202" t="inlineStr">
+        <is>
+          <t>Viva Bem</t>
+        </is>
+      </c>
+      <c r="AU202" t="inlineStr"/>
+      <c r="AV202" t="inlineStr"/>
+      <c r="AW202" t="inlineStr"/>
+      <c r="AX202" t="inlineStr"/>
+      <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr"/>
+      <c r="BA202" t="inlineStr"/>
+      <c r="BB202" t="inlineStr"/>
+      <c r="BC202" t="inlineStr"/>
+      <c r="BD202" t="inlineStr"/>
+      <c r="BE202" t="inlineStr"/>
+      <c r="BF202" t="inlineStr"/>
+      <c r="BG202" t="inlineStr"/>
+      <c r="BH202" t="inlineStr"/>
+      <c r="BI202" t="inlineStr"/>
+      <c r="BJ202" t="inlineStr"/>
+      <c r="BK202" t="inlineStr"/>
+      <c r="BL202" t="inlineStr"/>
+      <c r="BM202" t="inlineStr"/>
+      <c r="BN202" t="inlineStr"/>
+      <c r="BO202" t="inlineStr"/>
+      <c r="BP202" t="inlineStr"/>
+      <c r="BQ202" t="inlineStr"/>
+      <c r="BR202" t="inlineStr"/>
+      <c r="BS202" t="inlineStr"/>
+      <c r="BT202" t="inlineStr"/>
+      <c r="BU202" t="inlineStr"/>
+      <c r="BV202" t="inlineStr"/>
+      <c r="BW202" t="inlineStr"/>
+      <c r="BX202" t="inlineStr"/>
+      <c r="BY202" t="inlineStr"/>
+      <c r="BZ202" t="inlineStr"/>
+      <c r="CA202" t="inlineStr"/>
+      <c r="CB202" t="inlineStr"/>
+      <c r="CC202" t="inlineStr"/>
+      <c r="CD202" t="inlineStr"/>
+      <c r="CE202" t="inlineStr"/>
+      <c r="CF202" t="inlineStr"/>
+      <c r="CG202" t="inlineStr"/>
+      <c r="CH202" t="inlineStr"/>
+      <c r="CI202" t="inlineStr"/>
+      <c r="CJ202" t="inlineStr"/>
+      <c r="CK202" t="inlineStr"/>
+      <c r="CL202" t="inlineStr"/>
+      <c r="CM202" t="inlineStr"/>
+      <c r="CN202" t="inlineStr"/>
+      <c r="CO202" t="inlineStr"/>
+      <c r="CP202" t="inlineStr"/>
+      <c r="CQ202" t="inlineStr"/>
+      <c r="CR202" t="inlineStr"/>
+      <c r="CS202" t="inlineStr"/>
+      <c r="CT202" t="inlineStr"/>
+      <c r="CU202" t="inlineStr"/>
+      <c r="CV202" t="inlineStr"/>
+      <c r="CW202" t="inlineStr"/>
+      <c r="CX202" t="inlineStr"/>
+      <c r="CY202" t="inlineStr"/>
+      <c r="CZ202" t="inlineStr"/>
+      <c r="DA202" t="inlineStr"/>
+      <c r="DB202" t="inlineStr"/>
+      <c r="DC202" t="inlineStr"/>
+      <c r="DD202" t="inlineStr"/>
+      <c r="DE202" t="inlineStr"/>
+      <c r="DF202" t="inlineStr"/>
+      <c r="DG202" t="inlineStr"/>
+      <c r="DH202" t="inlineStr"/>
+      <c r="DI202" t="inlineStr">
+        <is>
+          <t>DESCARTADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>565</v>
+      </c>
+      <c r="B203" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C203" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>DESOSPITALIZAÇÃO AMIL - TIME ERIC</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
+      <c r="O203" t="inlineStr"/>
+      <c r="P203" t="inlineStr"/>
+      <c r="Q203" t="inlineStr"/>
+      <c r="R203" t="inlineStr"/>
+      <c r="S203" t="inlineStr"/>
+      <c r="T203" t="inlineStr"/>
+      <c r="U203" t="inlineStr"/>
+      <c r="V203" t="inlineStr"/>
+      <c r="W203" t="inlineStr"/>
+      <c r="X203" t="inlineStr"/>
+      <c r="Y203" t="inlineStr"/>
+      <c r="Z203" t="inlineStr"/>
+      <c r="AA203" t="inlineStr"/>
+      <c r="AB203" t="inlineStr"/>
+      <c r="AC203" t="inlineStr"/>
+      <c r="AD203" t="inlineStr"/>
+      <c r="AE203" t="inlineStr"/>
+      <c r="AF203" t="inlineStr"/>
+      <c r="AG203" t="inlineStr"/>
+      <c r="AH203" t="inlineStr"/>
+      <c r="AI203" t="inlineStr"/>
+      <c r="AJ203" t="inlineStr"/>
+      <c r="AK203" t="n">
+        <v>95709997</v>
+      </c>
+      <c r="AL203" t="inlineStr">
+        <is>
+          <t>WELLINGTON VIEIRA DE PAULA</t>
+        </is>
+      </c>
+      <c r="AM203" t="inlineStr">
+        <is>
+          <t>352.271.728-70</t>
+        </is>
+      </c>
+      <c r="AN203" s="1" t="n">
+        <v>32611</v>
+      </c>
+      <c r="AO203" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="AP203" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="AQ203" t="inlineStr">
+        <is>
+          <t>sp</t>
+        </is>
+      </c>
+      <c r="AR203" t="inlineStr">
+        <is>
+          <t>BRONZE SP</t>
+        </is>
+      </c>
+      <c r="AS203" t="n">
+        <v>11940188063</v>
+      </c>
+      <c r="AT203" t="inlineStr">
+        <is>
+          <t>Emagrecimento</t>
+        </is>
+      </c>
+      <c r="AU203" t="inlineStr"/>
+      <c r="AV203" t="inlineStr"/>
+      <c r="AW203" t="inlineStr"/>
+      <c r="AX203" t="inlineStr"/>
+      <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr"/>
+      <c r="BA203" t="inlineStr"/>
+      <c r="BB203" t="inlineStr"/>
+      <c r="BC203" t="inlineStr"/>
+      <c r="BD203" t="inlineStr"/>
+      <c r="BE203" t="inlineStr"/>
+      <c r="BF203" t="inlineStr"/>
+      <c r="BG203" t="inlineStr"/>
+      <c r="BH203" t="inlineStr"/>
+      <c r="BI203" t="inlineStr"/>
+      <c r="BJ203" t="inlineStr"/>
+      <c r="BK203" t="inlineStr"/>
+      <c r="BL203" t="inlineStr"/>
+      <c r="BM203" t="inlineStr"/>
+      <c r="BN203" t="inlineStr"/>
+      <c r="BO203" t="inlineStr"/>
+      <c r="BP203" t="inlineStr"/>
+      <c r="BQ203" t="inlineStr"/>
+      <c r="BR203" t="inlineStr"/>
+      <c r="BS203" t="inlineStr"/>
+      <c r="BT203" t="inlineStr"/>
+      <c r="BU203" t="inlineStr"/>
+      <c r="BV203" t="inlineStr"/>
+      <c r="BW203" t="inlineStr"/>
+      <c r="BX203" t="inlineStr"/>
+      <c r="BY203" t="inlineStr"/>
+      <c r="BZ203" t="inlineStr"/>
+      <c r="CA203" t="inlineStr"/>
+      <c r="CB203" t="inlineStr"/>
+      <c r="CC203" t="inlineStr"/>
+      <c r="CD203" t="inlineStr"/>
+      <c r="CE203" t="inlineStr"/>
+      <c r="CF203" t="inlineStr"/>
+      <c r="CG203" t="inlineStr"/>
+      <c r="CH203" t="inlineStr"/>
+      <c r="CI203" t="inlineStr"/>
+      <c r="CJ203" t="inlineStr"/>
+      <c r="CK203" t="inlineStr"/>
+      <c r="CL203" t="inlineStr"/>
+      <c r="CM203" t="inlineStr"/>
+      <c r="CN203" t="inlineStr"/>
+      <c r="CO203" t="inlineStr"/>
+      <c r="CP203" t="inlineStr"/>
+      <c r="CQ203" t="inlineStr"/>
+      <c r="CR203" t="inlineStr"/>
+      <c r="CS203" t="inlineStr"/>
+      <c r="CT203" t="inlineStr"/>
+      <c r="CU203" t="inlineStr"/>
+      <c r="CV203" t="inlineStr"/>
+      <c r="CW203" t="inlineStr"/>
+      <c r="CX203" t="inlineStr"/>
+      <c r="CY203" t="inlineStr"/>
+      <c r="CZ203" t="inlineStr"/>
+      <c r="DA203" t="inlineStr"/>
+      <c r="DB203" t="inlineStr"/>
+      <c r="DC203" t="inlineStr"/>
+      <c r="DD203" t="inlineStr"/>
+      <c r="DE203" t="inlineStr"/>
+      <c r="DF203" t="inlineStr"/>
+      <c r="DG203" t="inlineStr"/>
+      <c r="DH203" t="inlineStr"/>
+      <c r="DI203" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>566</v>
+      </c>
+      <c r="B204" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C204" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>DESOSPITALIZAÇÃO AMIL - TIME ERIC</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr"/>
+      <c r="N204" t="inlineStr"/>
+      <c r="O204" t="inlineStr"/>
+      <c r="P204" t="inlineStr"/>
+      <c r="Q204" t="inlineStr"/>
+      <c r="R204" t="inlineStr"/>
+      <c r="S204" t="inlineStr"/>
+      <c r="T204" t="inlineStr"/>
+      <c r="U204" t="inlineStr"/>
+      <c r="V204" t="inlineStr"/>
+      <c r="W204" t="inlineStr"/>
+      <c r="X204" t="inlineStr"/>
+      <c r="Y204" t="inlineStr"/>
+      <c r="Z204" t="inlineStr"/>
+      <c r="AA204" t="inlineStr"/>
+      <c r="AB204" t="inlineStr"/>
+      <c r="AC204" t="inlineStr"/>
+      <c r="AD204" t="inlineStr"/>
+      <c r="AE204" t="inlineStr"/>
+      <c r="AF204" t="inlineStr"/>
+      <c r="AG204" t="inlineStr"/>
+      <c r="AH204" t="inlineStr"/>
+      <c r="AI204" t="inlineStr"/>
+      <c r="AJ204" t="inlineStr"/>
+      <c r="AK204" t="n">
+        <v>757353134</v>
+      </c>
+      <c r="AL204" t="inlineStr">
+        <is>
+          <t>CEZARINA TELES DIAS</t>
+        </is>
+      </c>
+      <c r="AM204" t="inlineStr">
+        <is>
+          <t>028.150.727-93</t>
+        </is>
+      </c>
+      <c r="AN204" s="1" t="n">
+        <v>14301</v>
+      </c>
+      <c r="AO204" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="AP204" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="AQ204" t="inlineStr">
+        <is>
+          <t>RIO DE JANEIRO</t>
+        </is>
+      </c>
+      <c r="AR204" t="inlineStr">
+        <is>
+          <t>DIX CLASSIC ESSENCIAL REGIONAL RJ QC</t>
+        </is>
+      </c>
+      <c r="AS204" t="n">
+        <v>21980185445</v>
+      </c>
+      <c r="AT204" t="inlineStr">
+        <is>
+          <t>Insuficiência Cardíaca Controlada</t>
+        </is>
+      </c>
+      <c r="AU204" t="inlineStr"/>
+      <c r="AV204" t="inlineStr"/>
+      <c r="AW204" t="inlineStr"/>
+      <c r="AX204" t="inlineStr"/>
+      <c r="AY204" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="AZ204" t="inlineStr"/>
+      <c r="BA204" t="inlineStr"/>
+      <c r="BB204" t="inlineStr"/>
+      <c r="BC204" t="inlineStr"/>
+      <c r="BD204" t="inlineStr"/>
+      <c r="BE204" t="inlineStr"/>
+      <c r="BF204" t="inlineStr"/>
+      <c r="BG204" t="inlineStr"/>
+      <c r="BH204" t="inlineStr"/>
+      <c r="BI204" t="inlineStr"/>
+      <c r="BJ204" t="inlineStr"/>
+      <c r="BK204" t="inlineStr"/>
+      <c r="BL204" t="inlineStr"/>
+      <c r="BM204" t="inlineStr"/>
+      <c r="BN204" t="inlineStr"/>
+      <c r="BO204" t="inlineStr"/>
+      <c r="BP204" t="inlineStr"/>
+      <c r="BQ204" t="inlineStr"/>
+      <c r="BR204" t="inlineStr"/>
+      <c r="BS204" t="inlineStr"/>
+      <c r="BT204" t="inlineStr"/>
+      <c r="BU204" t="inlineStr"/>
+      <c r="BV204" t="inlineStr"/>
+      <c r="BW204" t="inlineStr"/>
+      <c r="BX204" t="inlineStr"/>
+      <c r="BY204" t="inlineStr"/>
+      <c r="BZ204" t="inlineStr"/>
+      <c r="CA204" t="inlineStr"/>
+      <c r="CB204" t="inlineStr"/>
+      <c r="CC204" t="inlineStr"/>
+      <c r="CD204" t="inlineStr"/>
+      <c r="CE204" t="inlineStr"/>
+      <c r="CF204" t="inlineStr"/>
+      <c r="CG204" t="inlineStr"/>
+      <c r="CH204" t="inlineStr"/>
+      <c r="CI204" t="inlineStr"/>
+      <c r="CJ204" t="inlineStr"/>
+      <c r="CK204" t="inlineStr"/>
+      <c r="CL204" t="inlineStr"/>
+      <c r="CM204" t="inlineStr"/>
+      <c r="CN204" t="inlineStr"/>
+      <c r="CO204" t="inlineStr"/>
+      <c r="CP204" t="inlineStr"/>
+      <c r="CQ204" t="inlineStr"/>
+      <c r="CR204" t="inlineStr"/>
+      <c r="CS204" t="inlineStr"/>
+      <c r="CT204" t="inlineStr"/>
+      <c r="CU204" t="inlineStr"/>
+      <c r="CV204" t="inlineStr"/>
+      <c r="CW204" t="inlineStr"/>
+      <c r="CX204" t="inlineStr"/>
+      <c r="CY204" t="inlineStr"/>
+      <c r="CZ204" t="inlineStr"/>
+      <c r="DA204" t="inlineStr"/>
+      <c r="DB204" t="inlineStr"/>
+      <c r="DC204" t="inlineStr"/>
+      <c r="DD204" t="inlineStr"/>
+      <c r="DE204" t="inlineStr"/>
+      <c r="DF204" t="inlineStr"/>
+      <c r="DG204" t="inlineStr"/>
+      <c r="DH204" t="inlineStr"/>
+      <c r="DI204" t="inlineStr">
+        <is>
+          <t>ENVIADO NAVEGAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>567</v>
+      </c>
+      <c r="B205" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C205" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>DESOSPITALIZAÇÃO AMIL - TIME ERIC</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
+      <c r="O205" t="inlineStr"/>
+      <c r="P205" t="inlineStr"/>
+      <c r="Q205" t="inlineStr"/>
+      <c r="R205" t="inlineStr"/>
+      <c r="S205" t="inlineStr"/>
+      <c r="T205" t="inlineStr"/>
+      <c r="U205" t="inlineStr"/>
+      <c r="V205" t="inlineStr"/>
+      <c r="W205" t="inlineStr"/>
+      <c r="X205" t="inlineStr"/>
+      <c r="Y205" t="inlineStr"/>
+      <c r="Z205" t="inlineStr"/>
+      <c r="AA205" t="inlineStr"/>
+      <c r="AB205" t="inlineStr"/>
+      <c r="AC205" t="inlineStr"/>
+      <c r="AD205" t="inlineStr"/>
+      <c r="AE205" t="inlineStr"/>
+      <c r="AF205" t="inlineStr"/>
+      <c r="AG205" t="inlineStr"/>
+      <c r="AH205" t="inlineStr"/>
+      <c r="AI205" t="inlineStr"/>
+      <c r="AJ205" t="inlineStr"/>
+      <c r="AK205" t="n">
+        <v>745839487</v>
+      </c>
+      <c r="AL205" t="inlineStr">
+        <is>
+          <t>MARIA DO CARMO ROCHA</t>
+        </is>
+      </c>
+      <c r="AM205" t="inlineStr">
+        <is>
+          <t>929.113.587-91</t>
+        </is>
+      </c>
+      <c r="AN205" s="1" t="n">
+        <v>17913</v>
+      </c>
+      <c r="AO205" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="AP205" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="AQ205" t="inlineStr">
+        <is>
+          <t>RIO DE JANEIRO</t>
+        </is>
+      </c>
+      <c r="AR205" t="inlineStr">
+        <is>
+          <t>DIX RJ R5 QC</t>
+        </is>
+      </c>
+      <c r="AS205" t="n">
+        <v>21980064071</v>
+      </c>
+      <c r="AT205" t="inlineStr">
+        <is>
+          <t>Insuficiência Cardíaca Controlada</t>
+        </is>
+      </c>
+      <c r="AU205" t="inlineStr"/>
+      <c r="AV205" t="inlineStr"/>
+      <c r="AW205" t="inlineStr"/>
+      <c r="AX205" t="inlineStr"/>
+      <c r="AY205" s="1" t="n">
+        <v>46206</v>
+      </c>
+      <c r="AZ205" t="inlineStr"/>
+      <c r="BA205" t="inlineStr"/>
+      <c r="BB205" t="inlineStr"/>
+      <c r="BC205" t="inlineStr"/>
+      <c r="BD205" t="inlineStr"/>
+      <c r="BE205" t="inlineStr"/>
+      <c r="BF205" t="inlineStr"/>
+      <c r="BG205" t="inlineStr"/>
+      <c r="BH205" t="inlineStr"/>
+      <c r="BI205" t="inlineStr"/>
+      <c r="BJ205" t="inlineStr"/>
+      <c r="BK205" t="inlineStr"/>
+      <c r="BL205" t="inlineStr"/>
+      <c r="BM205" t="inlineStr"/>
+      <c r="BN205" t="inlineStr"/>
+      <c r="BO205" t="inlineStr"/>
+      <c r="BP205" t="inlineStr"/>
+      <c r="BQ205" t="inlineStr"/>
+      <c r="BR205" t="inlineStr"/>
+      <c r="BS205" t="inlineStr"/>
+      <c r="BT205" t="inlineStr"/>
+      <c r="BU205" t="inlineStr"/>
+      <c r="BV205" t="inlineStr"/>
+      <c r="BW205" t="inlineStr"/>
+      <c r="BX205" t="inlineStr"/>
+      <c r="BY205" t="inlineStr"/>
+      <c r="BZ205" t="inlineStr"/>
+      <c r="CA205" t="inlineStr"/>
+      <c r="CB205" t="inlineStr"/>
+      <c r="CC205" t="inlineStr"/>
+      <c r="CD205" t="inlineStr"/>
+      <c r="CE205" t="inlineStr"/>
+      <c r="CF205" t="inlineStr"/>
+      <c r="CG205" t="inlineStr"/>
+      <c r="CH205" t="inlineStr"/>
+      <c r="CI205" t="inlineStr"/>
+      <c r="CJ205" t="inlineStr"/>
+      <c r="CK205" t="inlineStr"/>
+      <c r="CL205" t="inlineStr"/>
+      <c r="CM205" t="inlineStr"/>
+      <c r="CN205" t="inlineStr"/>
+      <c r="CO205" t="inlineStr"/>
+      <c r="CP205" t="inlineStr"/>
+      <c r="CQ205" t="inlineStr"/>
+      <c r="CR205" t="inlineStr"/>
+      <c r="CS205" t="inlineStr"/>
+      <c r="CT205" t="inlineStr"/>
+      <c r="CU205" t="inlineStr"/>
+      <c r="CV205" t="inlineStr"/>
+      <c r="CW205" t="inlineStr"/>
+      <c r="CX205" t="inlineStr"/>
+      <c r="CY205" t="inlineStr"/>
+      <c r="CZ205" t="inlineStr"/>
+      <c r="DA205" t="inlineStr"/>
+      <c r="DB205" t="inlineStr"/>
+      <c r="DC205" t="inlineStr"/>
+      <c r="DD205" t="inlineStr"/>
+      <c r="DE205" t="inlineStr"/>
+      <c r="DF205" t="inlineStr"/>
+      <c r="DG205" t="inlineStr"/>
+      <c r="DH205" t="inlineStr"/>
+      <c r="DI205" t="inlineStr">
+        <is>
+          <t>ENVIADO NAVEGAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>568</v>
+      </c>
+      <c r="B206" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C206" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>DESOSPITALIZAÇÃO AMIL - TIME ERIC</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr"/>
+      <c r="O206" t="inlineStr"/>
+      <c r="P206" t="inlineStr"/>
+      <c r="Q206" t="inlineStr"/>
+      <c r="R206" t="inlineStr"/>
+      <c r="S206" t="inlineStr"/>
+      <c r="T206" t="inlineStr"/>
+      <c r="U206" t="inlineStr"/>
+      <c r="V206" t="inlineStr"/>
+      <c r="W206" t="inlineStr"/>
+      <c r="X206" t="inlineStr"/>
+      <c r="Y206" t="inlineStr"/>
+      <c r="Z206" t="inlineStr"/>
+      <c r="AA206" t="inlineStr"/>
+      <c r="AB206" t="inlineStr"/>
+      <c r="AC206" t="inlineStr"/>
+      <c r="AD206" t="inlineStr"/>
+      <c r="AE206" t="inlineStr"/>
+      <c r="AF206" t="inlineStr"/>
+      <c r="AG206" t="inlineStr"/>
+      <c r="AH206" t="inlineStr"/>
+      <c r="AI206" t="inlineStr"/>
+      <c r="AJ206" t="inlineStr"/>
+      <c r="AK206" t="n">
+        <v>755577310</v>
+      </c>
+      <c r="AL206" t="inlineStr">
+        <is>
+          <t>RUTE LIMA SANTOS</t>
+        </is>
+      </c>
+      <c r="AM206" t="inlineStr">
+        <is>
+          <t>102.252.437-25</t>
+        </is>
+      </c>
+      <c r="AN206" s="1" t="n">
+        <v>16155</v>
+      </c>
+      <c r="AO206" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="AP206" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="AQ206" t="inlineStr">
+        <is>
+          <t>DUQUE DE CAXIAS</t>
+        </is>
+      </c>
+      <c r="AR206" t="inlineStr">
+        <is>
+          <t>DIX CLASSIC QC</t>
+        </is>
+      </c>
+      <c r="AS206" t="n">
+        <v>21996042832</v>
+      </c>
+      <c r="AT206" t="inlineStr">
+        <is>
+          <t>Saúde Mental</t>
+        </is>
+      </c>
+      <c r="AU206" t="inlineStr">
+        <is>
+          <t>Demanda por orientação/prevenção</t>
+        </is>
+      </c>
+      <c r="AV206" t="inlineStr"/>
+      <c r="AW206" t="inlineStr"/>
+      <c r="AX206" t="inlineStr"/>
+      <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr"/>
+      <c r="BA206" t="inlineStr"/>
+      <c r="BB206" t="inlineStr"/>
+      <c r="BC206" t="inlineStr"/>
+      <c r="BD206" t="inlineStr"/>
+      <c r="BE206" t="inlineStr"/>
+      <c r="BF206" t="inlineStr"/>
+      <c r="BG206" t="inlineStr"/>
+      <c r="BH206" t="inlineStr"/>
+      <c r="BI206" t="inlineStr"/>
+      <c r="BJ206" t="inlineStr"/>
+      <c r="BK206" t="inlineStr"/>
+      <c r="BL206" t="inlineStr"/>
+      <c r="BM206" t="inlineStr"/>
+      <c r="BN206" t="inlineStr"/>
+      <c r="BO206" t="inlineStr"/>
+      <c r="BP206" t="inlineStr"/>
+      <c r="BQ206" t="inlineStr"/>
+      <c r="BR206" t="inlineStr"/>
+      <c r="BS206" t="inlineStr"/>
+      <c r="BT206" t="inlineStr"/>
+      <c r="BU206" t="inlineStr"/>
+      <c r="BV206" t="inlineStr"/>
+      <c r="BW206" t="inlineStr"/>
+      <c r="BX206" t="inlineStr"/>
+      <c r="BY206" t="inlineStr"/>
+      <c r="BZ206" t="inlineStr"/>
+      <c r="CA206" t="inlineStr"/>
+      <c r="CB206" t="inlineStr"/>
+      <c r="CC206" t="inlineStr"/>
+      <c r="CD206" t="inlineStr"/>
+      <c r="CE206" t="inlineStr"/>
+      <c r="CF206" t="inlineStr"/>
+      <c r="CG206" t="inlineStr"/>
+      <c r="CH206" t="inlineStr"/>
+      <c r="CI206" t="inlineStr"/>
+      <c r="CJ206" t="inlineStr"/>
+      <c r="CK206" t="inlineStr"/>
+      <c r="CL206" t="inlineStr"/>
+      <c r="CM206" t="inlineStr"/>
+      <c r="CN206" t="inlineStr"/>
+      <c r="CO206" t="inlineStr"/>
+      <c r="CP206" t="inlineStr"/>
+      <c r="CQ206" t="inlineStr"/>
+      <c r="CR206" t="inlineStr"/>
+      <c r="CS206" t="inlineStr"/>
+      <c r="CT206" t="inlineStr"/>
+      <c r="CU206" t="inlineStr"/>
+      <c r="CV206" t="inlineStr"/>
+      <c r="CW206" t="inlineStr"/>
+      <c r="CX206" t="inlineStr"/>
+      <c r="CY206" t="inlineStr"/>
+      <c r="CZ206" t="inlineStr"/>
+      <c r="DA206" t="inlineStr"/>
+      <c r="DB206" t="inlineStr"/>
+      <c r="DC206" t="inlineStr"/>
+      <c r="DD206" t="inlineStr"/>
+      <c r="DE206" t="inlineStr"/>
+      <c r="DF206" t="inlineStr"/>
+      <c r="DG206" t="inlineStr"/>
+      <c r="DH206" t="inlineStr"/>
+      <c r="DI206" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>569</v>
+      </c>
+      <c r="B207" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C207" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>DESOSPITALIZAÇÃO AMIL - TIME ERIC</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr"/>
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr"/>
+      <c r="N207" t="inlineStr"/>
+      <c r="O207" t="inlineStr"/>
+      <c r="P207" t="inlineStr"/>
+      <c r="Q207" t="inlineStr"/>
+      <c r="R207" t="inlineStr"/>
+      <c r="S207" t="inlineStr"/>
+      <c r="T207" t="inlineStr"/>
+      <c r="U207" t="inlineStr"/>
+      <c r="V207" t="inlineStr"/>
+      <c r="W207" t="inlineStr"/>
+      <c r="X207" t="inlineStr"/>
+      <c r="Y207" t="inlineStr"/>
+      <c r="Z207" t="inlineStr"/>
+      <c r="AA207" t="inlineStr"/>
+      <c r="AB207" t="inlineStr"/>
+      <c r="AC207" t="inlineStr"/>
+      <c r="AD207" t="inlineStr"/>
+      <c r="AE207" t="inlineStr"/>
+      <c r="AF207" t="inlineStr"/>
+      <c r="AG207" t="inlineStr"/>
+      <c r="AH207" t="inlineStr"/>
+      <c r="AI207" t="inlineStr"/>
+      <c r="AJ207" t="inlineStr"/>
+      <c r="AK207" t="n">
+        <v>755577310</v>
+      </c>
+      <c r="AL207" t="inlineStr">
+        <is>
+          <t>RUTE LIMA SANTOS</t>
+        </is>
+      </c>
+      <c r="AM207" t="inlineStr">
+        <is>
+          <t>102.252.437-25</t>
+        </is>
+      </c>
+      <c r="AN207" s="1" t="n">
+        <v>16155</v>
+      </c>
+      <c r="AO207" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="AP207" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="AQ207" t="inlineStr">
+        <is>
+          <t>DUQUE DE CAXIAS</t>
+        </is>
+      </c>
+      <c r="AR207" t="inlineStr">
+        <is>
+          <t>DIX CLASSIC QC</t>
+        </is>
+      </c>
+      <c r="AS207" t="n">
+        <v>21996042832</v>
+      </c>
+      <c r="AT207" t="inlineStr">
+        <is>
+          <t>Viva Bem</t>
+        </is>
+      </c>
+      <c r="AU207" t="inlineStr"/>
+      <c r="AV207" t="inlineStr"/>
+      <c r="AW207" t="inlineStr"/>
+      <c r="AX207" t="inlineStr"/>
+      <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr"/>
+      <c r="BA207" t="inlineStr"/>
+      <c r="BB207" t="inlineStr"/>
+      <c r="BC207" t="inlineStr"/>
+      <c r="BD207" t="inlineStr"/>
+      <c r="BE207" t="inlineStr"/>
+      <c r="BF207" t="inlineStr"/>
+      <c r="BG207" t="inlineStr"/>
+      <c r="BH207" t="inlineStr"/>
+      <c r="BI207" t="inlineStr"/>
+      <c r="BJ207" t="inlineStr"/>
+      <c r="BK207" t="inlineStr"/>
+      <c r="BL207" t="inlineStr"/>
+      <c r="BM207" t="inlineStr"/>
+      <c r="BN207" t="inlineStr"/>
+      <c r="BO207" t="inlineStr"/>
+      <c r="BP207" t="inlineStr"/>
+      <c r="BQ207" t="inlineStr"/>
+      <c r="BR207" t="inlineStr"/>
+      <c r="BS207" t="inlineStr"/>
+      <c r="BT207" t="inlineStr"/>
+      <c r="BU207" t="inlineStr"/>
+      <c r="BV207" t="inlineStr"/>
+      <c r="BW207" t="inlineStr"/>
+      <c r="BX207" t="inlineStr"/>
+      <c r="BY207" t="inlineStr"/>
+      <c r="BZ207" t="inlineStr"/>
+      <c r="CA207" t="inlineStr"/>
+      <c r="CB207" t="inlineStr"/>
+      <c r="CC207" t="inlineStr"/>
+      <c r="CD207" t="inlineStr"/>
+      <c r="CE207" t="inlineStr"/>
+      <c r="CF207" t="inlineStr"/>
+      <c r="CG207" t="inlineStr"/>
+      <c r="CH207" t="inlineStr"/>
+      <c r="CI207" t="inlineStr"/>
+      <c r="CJ207" t="inlineStr"/>
+      <c r="CK207" t="inlineStr"/>
+      <c r="CL207" t="inlineStr"/>
+      <c r="CM207" t="inlineStr"/>
+      <c r="CN207" t="inlineStr"/>
+      <c r="CO207" t="inlineStr"/>
+      <c r="CP207" t="inlineStr"/>
+      <c r="CQ207" t="inlineStr"/>
+      <c r="CR207" t="inlineStr"/>
+      <c r="CS207" t="inlineStr"/>
+      <c r="CT207" t="inlineStr"/>
+      <c r="CU207" t="inlineStr"/>
+      <c r="CV207" t="inlineStr"/>
+      <c r="CW207" t="inlineStr"/>
+      <c r="CX207" t="inlineStr"/>
+      <c r="CY207" t="inlineStr"/>
+      <c r="CZ207" t="inlineStr"/>
+      <c r="DA207" t="inlineStr"/>
+      <c r="DB207" t="inlineStr"/>
+      <c r="DC207" t="inlineStr"/>
+      <c r="DD207" t="inlineStr"/>
+      <c r="DE207" t="inlineStr"/>
+      <c r="DF207" t="inlineStr"/>
+      <c r="DG207" t="inlineStr"/>
+      <c r="DH207" t="inlineStr"/>
+      <c r="DI207" t="inlineStr">
+        <is>
+          <t>DESCARTADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>570</v>
+      </c>
+      <c r="B208" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C208" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>DESOSPITALIZAÇÃO AMIL - TIME ERIC</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr"/>
+      <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr"/>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
+      <c r="O208" t="inlineStr"/>
+      <c r="P208" t="inlineStr"/>
+      <c r="Q208" t="inlineStr"/>
+      <c r="R208" t="inlineStr"/>
+      <c r="S208" t="inlineStr"/>
+      <c r="T208" t="inlineStr"/>
+      <c r="U208" t="inlineStr"/>
+      <c r="V208" t="inlineStr"/>
+      <c r="W208" t="inlineStr"/>
+      <c r="X208" t="inlineStr"/>
+      <c r="Y208" t="inlineStr"/>
+      <c r="Z208" t="inlineStr"/>
+      <c r="AA208" t="inlineStr"/>
+      <c r="AB208" t="inlineStr"/>
+      <c r="AC208" t="inlineStr"/>
+      <c r="AD208" t="inlineStr"/>
+      <c r="AE208" t="inlineStr"/>
+      <c r="AF208" t="inlineStr"/>
+      <c r="AG208" t="inlineStr"/>
+      <c r="AH208" t="inlineStr"/>
+      <c r="AI208" t="inlineStr"/>
+      <c r="AJ208" t="inlineStr"/>
+      <c r="AK208" t="n">
+        <v>94589919</v>
+      </c>
+      <c r="AL208" t="inlineStr">
+        <is>
+          <t>ALINE BRAGA TERRA</t>
+        </is>
+      </c>
+      <c r="AM208" t="inlineStr">
+        <is>
+          <t>084.831.517-07</t>
+        </is>
+      </c>
+      <c r="AN208" s="1" t="n">
+        <v>29195</v>
+      </c>
+      <c r="AO208" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="AP208" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="AQ208" t="inlineStr">
+        <is>
+          <t>RIO DE JANEIRO</t>
+        </is>
+      </c>
+      <c r="AR208" t="inlineStr">
+        <is>
+          <t>AMIL BLUE III COLAB QP NAC COPART PJ ADM</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr">
+        <is>
+          <t>21-994160133</t>
+        </is>
+      </c>
+      <c r="AT208" t="inlineStr">
+        <is>
+          <t>Saúde Mental</t>
+        </is>
+      </c>
+      <c r="AU208" t="inlineStr">
+        <is>
+          <t>Busca preventiva por bem-estar</t>
+        </is>
+      </c>
+      <c r="AV208" t="inlineStr"/>
+      <c r="AW208" t="inlineStr"/>
+      <c r="AX208" t="inlineStr"/>
+      <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr"/>
+      <c r="BA208" t="inlineStr"/>
+      <c r="BB208" t="inlineStr"/>
+      <c r="BC208" t="inlineStr"/>
+      <c r="BD208" t="inlineStr"/>
+      <c r="BE208" t="inlineStr"/>
+      <c r="BF208" t="inlineStr"/>
+      <c r="BG208" t="inlineStr"/>
+      <c r="BH208" t="inlineStr"/>
+      <c r="BI208" t="inlineStr"/>
+      <c r="BJ208" t="inlineStr"/>
+      <c r="BK208" t="inlineStr"/>
+      <c r="BL208" t="inlineStr"/>
+      <c r="BM208" t="inlineStr"/>
+      <c r="BN208" t="inlineStr"/>
+      <c r="BO208" t="inlineStr"/>
+      <c r="BP208" t="inlineStr"/>
+      <c r="BQ208" t="inlineStr"/>
+      <c r="BR208" t="inlineStr"/>
+      <c r="BS208" t="inlineStr"/>
+      <c r="BT208" t="inlineStr"/>
+      <c r="BU208" t="inlineStr"/>
+      <c r="BV208" t="inlineStr"/>
+      <c r="BW208" t="inlineStr"/>
+      <c r="BX208" t="inlineStr"/>
+      <c r="BY208" t="inlineStr"/>
+      <c r="BZ208" t="inlineStr"/>
+      <c r="CA208" t="inlineStr"/>
+      <c r="CB208" t="inlineStr"/>
+      <c r="CC208" t="inlineStr"/>
+      <c r="CD208" t="inlineStr"/>
+      <c r="CE208" t="inlineStr"/>
+      <c r="CF208" t="inlineStr"/>
+      <c r="CG208" t="inlineStr"/>
+      <c r="CH208" t="inlineStr"/>
+      <c r="CI208" t="inlineStr"/>
+      <c r="CJ208" t="inlineStr"/>
+      <c r="CK208" t="inlineStr"/>
+      <c r="CL208" t="inlineStr"/>
+      <c r="CM208" t="inlineStr"/>
+      <c r="CN208" t="inlineStr"/>
+      <c r="CO208" t="inlineStr"/>
+      <c r="CP208" t="inlineStr"/>
+      <c r="CQ208" t="inlineStr"/>
+      <c r="CR208" t="inlineStr"/>
+      <c r="CS208" t="inlineStr"/>
+      <c r="CT208" t="inlineStr"/>
+      <c r="CU208" t="inlineStr"/>
+      <c r="CV208" t="inlineStr"/>
+      <c r="CW208" t="inlineStr"/>
+      <c r="CX208" t="inlineStr"/>
+      <c r="CY208" t="inlineStr"/>
+      <c r="CZ208" t="inlineStr"/>
+      <c r="DA208" t="inlineStr"/>
+      <c r="DB208" t="inlineStr"/>
+      <c r="DC208" t="inlineStr"/>
+      <c r="DD208" t="inlineStr"/>
+      <c r="DE208" t="inlineStr"/>
+      <c r="DF208" t="inlineStr"/>
+      <c r="DG208" t="inlineStr"/>
+      <c r="DH208" t="inlineStr"/>
+      <c r="DI208" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>571</v>
+      </c>
+      <c r="B209" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C209" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>DESOSPITALIZAÇÃO AMIL - TIME ERIC</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr"/>
+      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr"/>
+      <c r="M209" t="inlineStr"/>
+      <c r="N209" t="inlineStr"/>
+      <c r="O209" t="inlineStr"/>
+      <c r="P209" t="inlineStr"/>
+      <c r="Q209" t="inlineStr"/>
+      <c r="R209" t="inlineStr"/>
+      <c r="S209" t="inlineStr"/>
+      <c r="T209" t="inlineStr"/>
+      <c r="U209" t="inlineStr"/>
+      <c r="V209" t="inlineStr"/>
+      <c r="W209" t="inlineStr"/>
+      <c r="X209" t="inlineStr"/>
+      <c r="Y209" t="inlineStr"/>
+      <c r="Z209" t="inlineStr"/>
+      <c r="AA209" t="inlineStr"/>
+      <c r="AB209" t="inlineStr"/>
+      <c r="AC209" t="inlineStr"/>
+      <c r="AD209" t="inlineStr"/>
+      <c r="AE209" t="inlineStr"/>
+      <c r="AF209" t="inlineStr"/>
+      <c r="AG209" t="inlineStr"/>
+      <c r="AH209" t="inlineStr"/>
+      <c r="AI209" t="inlineStr"/>
+      <c r="AJ209" t="inlineStr"/>
+      <c r="AK209" t="n">
+        <v>87557292</v>
+      </c>
+      <c r="AL209" t="inlineStr">
+        <is>
+          <t>MARIZA FRANCISCO</t>
+        </is>
+      </c>
+      <c r="AM209" t="inlineStr">
+        <is>
+          <t>882.855.707-97</t>
+        </is>
+      </c>
+      <c r="AN209" s="1" t="n">
+        <v>17293</v>
+      </c>
+      <c r="AO209" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="AP209" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="AQ209" t="inlineStr">
+        <is>
+          <t>DUQUE DE CAXIAS</t>
+        </is>
+      </c>
+      <c r="AR209" t="inlineStr">
+        <is>
+          <t>AMIL S380 QC NAC R COPART PJ</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr">
+        <is>
+          <t>21-975193877/993881946</t>
+        </is>
+      </c>
+      <c r="AT209" t="inlineStr">
+        <is>
+          <t>Bem Cuidado</t>
+        </is>
+      </c>
+      <c r="AU209" t="inlineStr"/>
+      <c r="AV209" t="inlineStr"/>
+      <c r="AW209" t="inlineStr"/>
+      <c r="AX209" t="inlineStr"/>
+      <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr"/>
+      <c r="BA209" t="inlineStr"/>
+      <c r="BB209" t="inlineStr"/>
+      <c r="BC209" t="inlineStr"/>
+      <c r="BD209" t="inlineStr"/>
+      <c r="BE209" t="inlineStr"/>
+      <c r="BF209" t="inlineStr"/>
+      <c r="BG209" t="inlineStr"/>
+      <c r="BH209" t="inlineStr"/>
+      <c r="BI209" t="inlineStr"/>
+      <c r="BJ209" t="inlineStr"/>
+      <c r="BK209" t="inlineStr"/>
+      <c r="BL209" t="inlineStr"/>
+      <c r="BM209" t="inlineStr"/>
+      <c r="BN209" t="inlineStr"/>
+      <c r="BO209" t="inlineStr"/>
+      <c r="BP209" t="inlineStr"/>
+      <c r="BQ209" t="inlineStr"/>
+      <c r="BR209" t="inlineStr"/>
+      <c r="BS209" t="inlineStr"/>
+      <c r="BT209" t="inlineStr"/>
+      <c r="BU209" t="inlineStr"/>
+      <c r="BV209" t="inlineStr"/>
+      <c r="BW209" t="inlineStr"/>
+      <c r="BX209" t="inlineStr"/>
+      <c r="BY209" t="inlineStr"/>
+      <c r="BZ209" t="inlineStr"/>
+      <c r="CA209" t="inlineStr"/>
+      <c r="CB209" t="inlineStr"/>
+      <c r="CC209" t="inlineStr"/>
+      <c r="CD209" t="inlineStr"/>
+      <c r="CE209" t="inlineStr"/>
+      <c r="CF209" t="inlineStr"/>
+      <c r="CG209" t="inlineStr"/>
+      <c r="CH209" t="inlineStr"/>
+      <c r="CI209" t="inlineStr"/>
+      <c r="CJ209" t="inlineStr"/>
+      <c r="CK209" t="inlineStr"/>
+      <c r="CL209" t="inlineStr"/>
+      <c r="CM209" t="inlineStr"/>
+      <c r="CN209" t="inlineStr"/>
+      <c r="CO209" t="inlineStr"/>
+      <c r="CP209" t="inlineStr"/>
+      <c r="CQ209" t="inlineStr"/>
+      <c r="CR209" t="inlineStr"/>
+      <c r="CS209" t="inlineStr"/>
+      <c r="CT209" t="inlineStr"/>
+      <c r="CU209" t="inlineStr"/>
+      <c r="CV209" t="inlineStr"/>
+      <c r="CW209" t="inlineStr"/>
+      <c r="CX209" t="inlineStr"/>
+      <c r="CY209" t="inlineStr"/>
+      <c r="CZ209" t="inlineStr"/>
+      <c r="DA209" t="inlineStr"/>
+      <c r="DB209" t="inlineStr"/>
+      <c r="DC209" t="inlineStr"/>
+      <c r="DD209" t="inlineStr"/>
+      <c r="DE209" t="inlineStr"/>
+      <c r="DF209" t="inlineStr"/>
+      <c r="DG209" t="inlineStr"/>
+      <c r="DH209" t="inlineStr"/>
+      <c r="DI209" t="inlineStr">
+        <is>
+          <t>DESCARTADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>572</v>
+      </c>
+      <c r="B210" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C210" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>GSC</t>
+        </is>
+      </c>
+      <c r="G210" t="n">
+        <v>93493141</v>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>MICHELE GALAN DE JESUS JANDUZZO</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>319.226.758-57</t>
+        </is>
+      </c>
+      <c r="J210" s="1" t="n">
+        <v>31182</v>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>SAO PAULO</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>963887 AMIL S750 R2 QP NAC COPART PJ</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>(19) 998002501</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>2237572000 HARALD</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>Adriana Aparecida da Rosa Souza</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>Endometriose</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr"/>
+      <c r="T210" t="inlineStr"/>
+      <c r="U210" t="inlineStr"/>
+      <c r="V210" t="inlineStr"/>
+      <c r="W210" t="inlineStr"/>
+      <c r="X210" t="inlineStr"/>
+      <c r="Y210" t="inlineStr"/>
+      <c r="Z210" t="inlineStr"/>
+      <c r="AA210" t="inlineStr"/>
+      <c r="AB210" t="inlineStr"/>
+      <c r="AC210" t="inlineStr"/>
+      <c r="AD210" t="inlineStr"/>
+      <c r="AE210" t="inlineStr"/>
+      <c r="AF210" t="inlineStr"/>
+      <c r="AG210" t="inlineStr"/>
+      <c r="AH210" t="inlineStr"/>
+      <c r="AI210" t="inlineStr"/>
+      <c r="AJ210" t="inlineStr"/>
+      <c r="AK210" t="inlineStr"/>
+      <c r="AL210" t="inlineStr"/>
+      <c r="AM210" t="inlineStr"/>
+      <c r="AN210" t="inlineStr"/>
+      <c r="AO210" t="inlineStr"/>
+      <c r="AP210" t="inlineStr"/>
+      <c r="AQ210" t="inlineStr"/>
+      <c r="AR210" t="inlineStr"/>
+      <c r="AS210" t="inlineStr"/>
+      <c r="AT210" t="inlineStr"/>
+      <c r="AU210" t="inlineStr"/>
+      <c r="AV210" t="inlineStr"/>
+      <c r="AW210" t="inlineStr"/>
+      <c r="AX210" t="inlineStr"/>
+      <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr"/>
+      <c r="BA210" t="inlineStr"/>
+      <c r="BB210" t="inlineStr"/>
+      <c r="BC210" t="inlineStr"/>
+      <c r="BD210" t="inlineStr"/>
+      <c r="BE210" t="inlineStr"/>
+      <c r="BF210" t="inlineStr"/>
+      <c r="BG210" t="inlineStr"/>
+      <c r="BH210" t="inlineStr"/>
+      <c r="BI210" t="inlineStr"/>
+      <c r="BJ210" t="inlineStr"/>
+      <c r="BK210" t="inlineStr"/>
+      <c r="BL210" t="inlineStr"/>
+      <c r="BM210" t="inlineStr"/>
+      <c r="BN210" t="inlineStr"/>
+      <c r="BO210" t="inlineStr"/>
+      <c r="BP210" t="inlineStr"/>
+      <c r="BQ210" t="inlineStr"/>
+      <c r="BR210" t="inlineStr"/>
+      <c r="BS210" t="inlineStr"/>
+      <c r="BT210" t="inlineStr"/>
+      <c r="BU210" t="inlineStr"/>
+      <c r="BV210" t="inlineStr"/>
+      <c r="BW210" t="inlineStr"/>
+      <c r="BX210" t="inlineStr"/>
+      <c r="BY210" t="inlineStr"/>
+      <c r="BZ210" t="inlineStr"/>
+      <c r="CA210" t="inlineStr"/>
+      <c r="CB210" t="inlineStr"/>
+      <c r="CC210" t="inlineStr"/>
+      <c r="CD210" t="inlineStr"/>
+      <c r="CE210" t="inlineStr"/>
+      <c r="CF210" t="inlineStr"/>
+      <c r="CG210" t="inlineStr"/>
+      <c r="CH210" t="inlineStr"/>
+      <c r="CI210" t="inlineStr"/>
+      <c r="CJ210" t="inlineStr"/>
+      <c r="CK210" t="inlineStr"/>
+      <c r="CL210" t="inlineStr"/>
+      <c r="CM210" t="inlineStr"/>
+      <c r="CN210" t="inlineStr"/>
+      <c r="CO210" t="inlineStr"/>
+      <c r="CP210" t="inlineStr"/>
+      <c r="CQ210" t="inlineStr"/>
+      <c r="CR210" t="inlineStr"/>
+      <c r="CS210" t="inlineStr"/>
+      <c r="CT210" t="inlineStr"/>
+      <c r="CU210" t="inlineStr"/>
+      <c r="CV210" t="inlineStr"/>
+      <c r="CW210" t="inlineStr"/>
+      <c r="CX210" t="inlineStr"/>
+      <c r="CY210" t="inlineStr"/>
+      <c r="CZ210" t="inlineStr"/>
+      <c r="DA210" t="inlineStr"/>
+      <c r="DB210" t="inlineStr"/>
+      <c r="DC210" t="inlineStr"/>
+      <c r="DD210" t="inlineStr"/>
+      <c r="DE210" t="inlineStr"/>
+      <c r="DF210" t="inlineStr"/>
+      <c r="DG210" t="inlineStr"/>
+      <c r="DH210" t="inlineStr"/>
+      <c r="DI210" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>573</v>
+      </c>
+      <c r="B211" s="1" t="n">
+        <v>46186</v>
+      </c>
+      <c r="C211" s="1" t="n">
+        <v>46186</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>GSC</t>
+        </is>
+      </c>
+      <c r="G211" t="n">
+        <v>93906090</v>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>BRUNA PESSOA DA SILVA</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>406.828.668-06</t>
+        </is>
+      </c>
+      <c r="J211" s="1" t="n">
+        <v>33549</v>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>TABOAO DA SERRA</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>967071 PRATA QC COPART</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>(11)  994283335</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>2391647000 VMT TELECOMUNICACOES</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>Adriana Aparecida da Rosa Souza</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>Saúde Renal</t>
+        </is>
+      </c>
+      <c r="S211" t="inlineStr"/>
+      <c r="T211" t="inlineStr"/>
+      <c r="U211" t="inlineStr"/>
+      <c r="V211" t="inlineStr"/>
+      <c r="W211" t="inlineStr"/>
+      <c r="X211" t="inlineStr"/>
+      <c r="Y211" t="inlineStr"/>
+      <c r="Z211" t="inlineStr"/>
+      <c r="AA211" t="inlineStr"/>
+      <c r="AB211" t="inlineStr"/>
+      <c r="AC211" t="inlineStr"/>
+      <c r="AD211" t="inlineStr"/>
+      <c r="AE211" t="inlineStr"/>
+      <c r="AF211" t="inlineStr"/>
+      <c r="AG211" t="inlineStr"/>
+      <c r="AH211" t="inlineStr"/>
+      <c r="AI211" t="inlineStr"/>
+      <c r="AJ211" t="inlineStr"/>
+      <c r="AK211" t="inlineStr"/>
+      <c r="AL211" t="inlineStr"/>
+      <c r="AM211" t="inlineStr"/>
+      <c r="AN211" t="inlineStr"/>
+      <c r="AO211" t="inlineStr"/>
+      <c r="AP211" t="inlineStr"/>
+      <c r="AQ211" t="inlineStr"/>
+      <c r="AR211" t="inlineStr"/>
+      <c r="AS211" t="inlineStr"/>
+      <c r="AT211" t="inlineStr"/>
+      <c r="AU211" t="inlineStr"/>
+      <c r="AV211" t="inlineStr"/>
+      <c r="AW211" t="inlineStr"/>
+      <c r="AX211" t="inlineStr"/>
+      <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr"/>
+      <c r="BA211" t="inlineStr"/>
+      <c r="BB211" t="inlineStr"/>
+      <c r="BC211" t="inlineStr"/>
+      <c r="BD211" t="inlineStr"/>
+      <c r="BE211" t="inlineStr"/>
+      <c r="BF211" t="inlineStr"/>
+      <c r="BG211" t="inlineStr"/>
+      <c r="BH211" t="inlineStr"/>
+      <c r="BI211" t="inlineStr"/>
+      <c r="BJ211" t="inlineStr"/>
+      <c r="BK211" t="inlineStr"/>
+      <c r="BL211" t="inlineStr"/>
+      <c r="BM211" t="inlineStr"/>
+      <c r="BN211" t="inlineStr"/>
+      <c r="BO211" t="inlineStr"/>
+      <c r="BP211" t="inlineStr"/>
+      <c r="BQ211" t="inlineStr"/>
+      <c r="BR211" t="inlineStr"/>
+      <c r="BS211" t="inlineStr"/>
+      <c r="BT211" t="inlineStr"/>
+      <c r="BU211" t="inlineStr"/>
+      <c r="BV211" t="inlineStr"/>
+      <c r="BW211" t="inlineStr"/>
+      <c r="BX211" t="inlineStr"/>
+      <c r="BY211" t="inlineStr"/>
+      <c r="BZ211" t="inlineStr"/>
+      <c r="CA211" t="inlineStr"/>
+      <c r="CB211" t="inlineStr"/>
+      <c r="CC211" t="inlineStr"/>
+      <c r="CD211" t="inlineStr"/>
+      <c r="CE211" t="inlineStr"/>
+      <c r="CF211" t="inlineStr"/>
+      <c r="CG211" t="inlineStr"/>
+      <c r="CH211" t="inlineStr"/>
+      <c r="CI211" t="inlineStr"/>
+      <c r="CJ211" t="inlineStr"/>
+      <c r="CK211" t="inlineStr"/>
+      <c r="CL211" t="inlineStr"/>
+      <c r="CM211" t="inlineStr"/>
+      <c r="CN211" t="inlineStr"/>
+      <c r="CO211" t="inlineStr"/>
+      <c r="CP211" t="inlineStr"/>
+      <c r="CQ211" t="inlineStr"/>
+      <c r="CR211" t="inlineStr"/>
+      <c r="CS211" t="inlineStr"/>
+      <c r="CT211" t="inlineStr"/>
+      <c r="CU211" t="inlineStr"/>
+      <c r="CV211" t="inlineStr"/>
+      <c r="CW211" t="inlineStr"/>
+      <c r="CX211" t="inlineStr"/>
+      <c r="CY211" t="inlineStr"/>
+      <c r="CZ211" t="inlineStr"/>
+      <c r="DA211" t="inlineStr"/>
+      <c r="DB211" t="inlineStr"/>
+      <c r="DC211" t="inlineStr"/>
+      <c r="DD211" t="inlineStr"/>
+      <c r="DE211" t="inlineStr"/>
+      <c r="DF211" t="inlineStr"/>
+      <c r="DG211" t="inlineStr"/>
+      <c r="DH211" t="inlineStr"/>
+      <c r="DI211" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>574</v>
+      </c>
+      <c r="B212" s="1" t="n">
+        <v>46186</v>
+      </c>
+      <c r="C212" s="1" t="n">
+        <v>46186</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>GSC</t>
+        </is>
+      </c>
+      <c r="G212" t="n">
+        <v>93906191</v>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>JOAO EMANUEL DOS SANTOS SOUZA</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>246.166.328-98</t>
+        </is>
+      </c>
+      <c r="J212" s="1" t="n">
+        <v>28064</v>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>SAO PAULO</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>967177 OURO QP R COPART</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(19)  993042935  </t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>2391647000 VMT TELECOMUNICACOES</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>Adriana Aparecida da Rosa Souza</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>Cuidados Pós Infarto</t>
+        </is>
+      </c>
+      <c r="S212" t="inlineStr"/>
+      <c r="T212" t="inlineStr"/>
+      <c r="U212" t="inlineStr"/>
+      <c r="V212" t="inlineStr"/>
+      <c r="W212" t="inlineStr"/>
+      <c r="X212" t="inlineStr"/>
+      <c r="Y212" t="inlineStr"/>
+      <c r="Z212" t="inlineStr"/>
+      <c r="AA212" t="inlineStr"/>
+      <c r="AB212" t="inlineStr"/>
+      <c r="AC212" t="inlineStr"/>
+      <c r="AD212" t="inlineStr"/>
+      <c r="AE212" t="inlineStr"/>
+      <c r="AF212" t="inlineStr"/>
+      <c r="AG212" t="inlineStr"/>
+      <c r="AH212" t="inlineStr"/>
+      <c r="AI212" t="inlineStr"/>
+      <c r="AJ212" t="inlineStr"/>
+      <c r="AK212" t="inlineStr"/>
+      <c r="AL212" t="inlineStr"/>
+      <c r="AM212" t="inlineStr"/>
+      <c r="AN212" t="inlineStr"/>
+      <c r="AO212" t="inlineStr"/>
+      <c r="AP212" t="inlineStr"/>
+      <c r="AQ212" t="inlineStr"/>
+      <c r="AR212" t="inlineStr"/>
+      <c r="AS212" t="inlineStr"/>
+      <c r="AT212" t="inlineStr"/>
+      <c r="AU212" t="inlineStr"/>
+      <c r="AV212" t="inlineStr"/>
+      <c r="AW212" t="inlineStr"/>
+      <c r="AX212" t="inlineStr"/>
+      <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr"/>
+      <c r="BA212" t="inlineStr"/>
+      <c r="BB212" t="inlineStr"/>
+      <c r="BC212" t="inlineStr"/>
+      <c r="BD212" t="inlineStr"/>
+      <c r="BE212" t="inlineStr"/>
+      <c r="BF212" t="inlineStr"/>
+      <c r="BG212" t="inlineStr"/>
+      <c r="BH212" t="inlineStr"/>
+      <c r="BI212" t="inlineStr"/>
+      <c r="BJ212" t="inlineStr"/>
+      <c r="BK212" t="inlineStr"/>
+      <c r="BL212" t="inlineStr"/>
+      <c r="BM212" t="inlineStr"/>
+      <c r="BN212" t="inlineStr"/>
+      <c r="BO212" t="inlineStr"/>
+      <c r="BP212" t="inlineStr"/>
+      <c r="BQ212" t="inlineStr"/>
+      <c r="BR212" t="inlineStr"/>
+      <c r="BS212" t="inlineStr"/>
+      <c r="BT212" t="inlineStr"/>
+      <c r="BU212" t="inlineStr"/>
+      <c r="BV212" t="inlineStr"/>
+      <c r="BW212" t="inlineStr"/>
+      <c r="BX212" t="inlineStr"/>
+      <c r="BY212" t="inlineStr"/>
+      <c r="BZ212" t="inlineStr"/>
+      <c r="CA212" t="inlineStr"/>
+      <c r="CB212" t="inlineStr"/>
+      <c r="CC212" t="inlineStr"/>
+      <c r="CD212" t="inlineStr"/>
+      <c r="CE212" t="inlineStr"/>
+      <c r="CF212" t="inlineStr"/>
+      <c r="CG212" t="inlineStr"/>
+      <c r="CH212" t="inlineStr"/>
+      <c r="CI212" t="inlineStr"/>
+      <c r="CJ212" t="inlineStr"/>
+      <c r="CK212" t="inlineStr"/>
+      <c r="CL212" t="inlineStr"/>
+      <c r="CM212" t="inlineStr"/>
+      <c r="CN212" t="inlineStr"/>
+      <c r="CO212" t="inlineStr"/>
+      <c r="CP212" t="inlineStr"/>
+      <c r="CQ212" t="inlineStr"/>
+      <c r="CR212" t="inlineStr"/>
+      <c r="CS212" t="inlineStr"/>
+      <c r="CT212" t="inlineStr"/>
+      <c r="CU212" t="inlineStr"/>
+      <c r="CV212" t="inlineStr"/>
+      <c r="CW212" t="inlineStr"/>
+      <c r="CX212" t="inlineStr"/>
+      <c r="CY212" t="inlineStr"/>
+      <c r="CZ212" t="inlineStr"/>
+      <c r="DA212" t="inlineStr"/>
+      <c r="DB212" t="inlineStr"/>
+      <c r="DC212" t="inlineStr"/>
+      <c r="DD212" t="inlineStr"/>
+      <c r="DE212" t="inlineStr"/>
+      <c r="DF212" t="inlineStr"/>
+      <c r="DG212" t="inlineStr"/>
+      <c r="DH212" t="inlineStr"/>
+      <c r="DI212" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>575</v>
+      </c>
+      <c r="B213" s="1" t="n">
+        <v>46186</v>
+      </c>
+      <c r="C213" s="1" t="n">
+        <v>46186</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>GSC</t>
+        </is>
+      </c>
+      <c r="G213" t="n">
+        <v>93905776</v>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>JOAO VICTOR BISCAIA DE OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>430.761.548-42</t>
+        </is>
+      </c>
+      <c r="J213" s="1" t="n">
+        <v>34041</v>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>GUARULHOS</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>967071 PRATA QC COPART</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>(11)  962221220</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>2391647000 VMT TELECOMUNICACOES</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>Adriana Aparecida da Rosa Souza</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>Saúde Mental</t>
+        </is>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>Demanda por orientação/prevenção</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr"/>
+      <c r="U213" t="inlineStr"/>
+      <c r="V213" t="inlineStr"/>
+      <c r="W213" t="inlineStr"/>
+      <c r="X213" t="inlineStr"/>
+      <c r="Y213" t="inlineStr"/>
+      <c r="Z213" t="inlineStr"/>
+      <c r="AA213" t="inlineStr"/>
+      <c r="AB213" t="inlineStr"/>
+      <c r="AC213" t="inlineStr"/>
+      <c r="AD213" t="inlineStr"/>
+      <c r="AE213" t="inlineStr"/>
+      <c r="AF213" t="inlineStr"/>
+      <c r="AG213" t="inlineStr"/>
+      <c r="AH213" t="inlineStr"/>
+      <c r="AI213" t="inlineStr"/>
+      <c r="AJ213" t="inlineStr"/>
+      <c r="AK213" t="inlineStr"/>
+      <c r="AL213" t="inlineStr"/>
+      <c r="AM213" t="inlineStr"/>
+      <c r="AN213" t="inlineStr"/>
+      <c r="AO213" t="inlineStr"/>
+      <c r="AP213" t="inlineStr"/>
+      <c r="AQ213" t="inlineStr"/>
+      <c r="AR213" t="inlineStr"/>
+      <c r="AS213" t="inlineStr"/>
+      <c r="AT213" t="inlineStr"/>
+      <c r="AU213" t="inlineStr"/>
+      <c r="AV213" t="inlineStr"/>
+      <c r="AW213" t="inlineStr"/>
+      <c r="AX213" t="inlineStr"/>
+      <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr"/>
+      <c r="BA213" t="inlineStr"/>
+      <c r="BB213" t="inlineStr"/>
+      <c r="BC213" t="inlineStr"/>
+      <c r="BD213" t="inlineStr"/>
+      <c r="BE213" t="inlineStr"/>
+      <c r="BF213" t="inlineStr"/>
+      <c r="BG213" t="inlineStr"/>
+      <c r="BH213" t="inlineStr"/>
+      <c r="BI213" t="inlineStr"/>
+      <c r="BJ213" t="inlineStr"/>
+      <c r="BK213" t="inlineStr"/>
+      <c r="BL213" t="inlineStr"/>
+      <c r="BM213" t="inlineStr"/>
+      <c r="BN213" t="inlineStr"/>
+      <c r="BO213" t="inlineStr"/>
+      <c r="BP213" t="inlineStr"/>
+      <c r="BQ213" t="inlineStr"/>
+      <c r="BR213" t="inlineStr"/>
+      <c r="BS213" t="inlineStr"/>
+      <c r="BT213" t="inlineStr"/>
+      <c r="BU213" t="inlineStr"/>
+      <c r="BV213" t="inlineStr"/>
+      <c r="BW213" t="inlineStr"/>
+      <c r="BX213" t="inlineStr"/>
+      <c r="BY213" t="inlineStr"/>
+      <c r="BZ213" t="inlineStr"/>
+      <c r="CA213" t="inlineStr"/>
+      <c r="CB213" t="inlineStr"/>
+      <c r="CC213" t="inlineStr"/>
+      <c r="CD213" t="inlineStr"/>
+      <c r="CE213" t="inlineStr"/>
+      <c r="CF213" t="inlineStr"/>
+      <c r="CG213" t="inlineStr"/>
+      <c r="CH213" t="inlineStr"/>
+      <c r="CI213" t="inlineStr"/>
+      <c r="CJ213" t="inlineStr"/>
+      <c r="CK213" t="inlineStr"/>
+      <c r="CL213" t="inlineStr"/>
+      <c r="CM213" t="inlineStr"/>
+      <c r="CN213" t="inlineStr"/>
+      <c r="CO213" t="inlineStr"/>
+      <c r="CP213" t="inlineStr"/>
+      <c r="CQ213" t="inlineStr"/>
+      <c r="CR213" t="inlineStr"/>
+      <c r="CS213" t="inlineStr"/>
+      <c r="CT213" t="inlineStr"/>
+      <c r="CU213" t="inlineStr"/>
+      <c r="CV213" t="inlineStr"/>
+      <c r="CW213" t="inlineStr"/>
+      <c r="CX213" t="inlineStr"/>
+      <c r="CY213" t="inlineStr"/>
+      <c r="CZ213" t="inlineStr"/>
+      <c r="DA213" t="inlineStr"/>
+      <c r="DB213" t="inlineStr"/>
+      <c r="DC213" t="inlineStr"/>
+      <c r="DD213" t="inlineStr"/>
+      <c r="DE213" t="inlineStr"/>
+      <c r="DF213" t="inlineStr"/>
+      <c r="DG213" t="inlineStr"/>
+      <c r="DH213" t="inlineStr"/>
+      <c r="DI213" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>576</v>
+      </c>
+      <c r="B214" s="1" t="n">
+        <v>46186</v>
+      </c>
+      <c r="C214" s="1" t="n">
+        <v>46186</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>GSC</t>
+        </is>
+      </c>
+      <c r="G214" t="n">
+        <v>93906361</v>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>EVELYN DA SILVA MARINONE</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>181.565.777-44</t>
+        </is>
+      </c>
+      <c r="J214" s="1" t="n">
+        <v>37379</v>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>TANGUA</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>967071 PRATA QC COPART</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>(21) 971836719</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>2391647000 VMT TELECOMUNICACOES</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>Adriana Aparecida da Rosa Souza</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>Saúde Mental</t>
+        </is>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>Demanda por orientação/prevenção</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr"/>
+      <c r="U214" t="inlineStr"/>
+      <c r="V214" t="inlineStr"/>
+      <c r="W214" t="inlineStr"/>
+      <c r="X214" t="inlineStr"/>
+      <c r="Y214" t="inlineStr"/>
+      <c r="Z214" t="inlineStr"/>
+      <c r="AA214" t="inlineStr"/>
+      <c r="AB214" t="inlineStr"/>
+      <c r="AC214" t="inlineStr"/>
+      <c r="AD214" t="inlineStr"/>
+      <c r="AE214" t="inlineStr"/>
+      <c r="AF214" t="inlineStr"/>
+      <c r="AG214" t="inlineStr"/>
+      <c r="AH214" t="inlineStr"/>
+      <c r="AI214" t="inlineStr"/>
+      <c r="AJ214" t="inlineStr"/>
+      <c r="AK214" t="inlineStr"/>
+      <c r="AL214" t="inlineStr"/>
+      <c r="AM214" t="inlineStr"/>
+      <c r="AN214" t="inlineStr"/>
+      <c r="AO214" t="inlineStr"/>
+      <c r="AP214" t="inlineStr"/>
+      <c r="AQ214" t="inlineStr"/>
+      <c r="AR214" t="inlineStr"/>
+      <c r="AS214" t="inlineStr"/>
+      <c r="AT214" t="inlineStr"/>
+      <c r="AU214" t="inlineStr"/>
+      <c r="AV214" t="inlineStr"/>
+      <c r="AW214" t="inlineStr"/>
+      <c r="AX214" t="inlineStr"/>
+      <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr"/>
+      <c r="BA214" t="inlineStr"/>
+      <c r="BB214" t="inlineStr"/>
+      <c r="BC214" t="inlineStr"/>
+      <c r="BD214" t="inlineStr"/>
+      <c r="BE214" t="inlineStr"/>
+      <c r="BF214" t="inlineStr"/>
+      <c r="BG214" t="inlineStr"/>
+      <c r="BH214" t="inlineStr"/>
+      <c r="BI214" t="inlineStr"/>
+      <c r="BJ214" t="inlineStr"/>
+      <c r="BK214" t="inlineStr"/>
+      <c r="BL214" t="inlineStr"/>
+      <c r="BM214" t="inlineStr"/>
+      <c r="BN214" t="inlineStr"/>
+      <c r="BO214" t="inlineStr"/>
+      <c r="BP214" t="inlineStr"/>
+      <c r="BQ214" t="inlineStr"/>
+      <c r="BR214" t="inlineStr"/>
+      <c r="BS214" t="inlineStr"/>
+      <c r="BT214" t="inlineStr"/>
+      <c r="BU214" t="inlineStr"/>
+      <c r="BV214" t="inlineStr"/>
+      <c r="BW214" t="inlineStr"/>
+      <c r="BX214" t="inlineStr"/>
+      <c r="BY214" t="inlineStr"/>
+      <c r="BZ214" t="inlineStr"/>
+      <c r="CA214" t="inlineStr"/>
+      <c r="CB214" t="inlineStr"/>
+      <c r="CC214" t="inlineStr"/>
+      <c r="CD214" t="inlineStr"/>
+      <c r="CE214" t="inlineStr"/>
+      <c r="CF214" t="inlineStr"/>
+      <c r="CG214" t="inlineStr"/>
+      <c r="CH214" t="inlineStr"/>
+      <c r="CI214" t="inlineStr"/>
+      <c r="CJ214" t="inlineStr"/>
+      <c r="CK214" t="inlineStr"/>
+      <c r="CL214" t="inlineStr"/>
+      <c r="CM214" t="inlineStr"/>
+      <c r="CN214" t="inlineStr"/>
+      <c r="CO214" t="inlineStr"/>
+      <c r="CP214" t="inlineStr"/>
+      <c r="CQ214" t="inlineStr"/>
+      <c r="CR214" t="inlineStr"/>
+      <c r="CS214" t="inlineStr"/>
+      <c r="CT214" t="inlineStr"/>
+      <c r="CU214" t="inlineStr"/>
+      <c r="CV214" t="inlineStr"/>
+      <c r="CW214" t="inlineStr"/>
+      <c r="CX214" t="inlineStr"/>
+      <c r="CY214" t="inlineStr"/>
+      <c r="CZ214" t="inlineStr"/>
+      <c r="DA214" t="inlineStr"/>
+      <c r="DB214" t="inlineStr"/>
+      <c r="DC214" t="inlineStr"/>
+      <c r="DD214" t="inlineStr"/>
+      <c r="DE214" t="inlineStr"/>
+      <c r="DF214" t="inlineStr"/>
+      <c r="DG214" t="inlineStr"/>
+      <c r="DH214" t="inlineStr"/>
+      <c r="DI214" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>577</v>
+      </c>
+      <c r="B215" s="1" t="n">
+        <v>46186</v>
+      </c>
+      <c r="C215" s="1" t="n">
+        <v>46186</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>GSC</t>
+        </is>
+      </c>
+      <c r="G215" t="n">
+        <v>93905776</v>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>JOAO VICTOR BISCAIA DE OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>430.761.548-42</t>
+        </is>
+      </c>
+      <c r="J215" s="1" t="n">
+        <v>34040</v>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>GUARULHOS</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>967071 PRATA QC COPART</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>(11)  962221220</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>2391647000 VMT TELECOMUNICACOES</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>Adriana Aparecida da Rosa Souza</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>Saúde Mental</t>
+        </is>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>Demanda por orientação/prevenção</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr"/>
+      <c r="U215" t="inlineStr"/>
+      <c r="V215" t="inlineStr"/>
+      <c r="W215" t="inlineStr"/>
+      <c r="X215" t="inlineStr"/>
+      <c r="Y215" t="inlineStr"/>
+      <c r="Z215" t="inlineStr"/>
+      <c r="AA215" t="inlineStr"/>
+      <c r="AB215" t="inlineStr"/>
+      <c r="AC215" t="inlineStr"/>
+      <c r="AD215" t="inlineStr"/>
+      <c r="AE215" t="inlineStr"/>
+      <c r="AF215" t="inlineStr"/>
+      <c r="AG215" t="inlineStr"/>
+      <c r="AH215" t="inlineStr"/>
+      <c r="AI215" t="inlineStr"/>
+      <c r="AJ215" t="inlineStr"/>
+      <c r="AK215" t="inlineStr"/>
+      <c r="AL215" t="inlineStr"/>
+      <c r="AM215" t="inlineStr"/>
+      <c r="AN215" t="inlineStr"/>
+      <c r="AO215" t="inlineStr"/>
+      <c r="AP215" t="inlineStr"/>
+      <c r="AQ215" t="inlineStr"/>
+      <c r="AR215" t="inlineStr"/>
+      <c r="AS215" t="inlineStr"/>
+      <c r="AT215" t="inlineStr"/>
+      <c r="AU215" t="inlineStr"/>
+      <c r="AV215" t="inlineStr"/>
+      <c r="AW215" t="inlineStr"/>
+      <c r="AX215" t="inlineStr"/>
+      <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr"/>
+      <c r="BA215" t="inlineStr"/>
+      <c r="BB215" t="inlineStr"/>
+      <c r="BC215" t="inlineStr"/>
+      <c r="BD215" t="inlineStr"/>
+      <c r="BE215" t="inlineStr"/>
+      <c r="BF215" t="inlineStr"/>
+      <c r="BG215" t="inlineStr"/>
+      <c r="BH215" t="inlineStr"/>
+      <c r="BI215" t="inlineStr"/>
+      <c r="BJ215" t="inlineStr"/>
+      <c r="BK215" t="inlineStr"/>
+      <c r="BL215" t="inlineStr"/>
+      <c r="BM215" t="inlineStr"/>
+      <c r="BN215" t="inlineStr"/>
+      <c r="BO215" t="inlineStr"/>
+      <c r="BP215" t="inlineStr"/>
+      <c r="BQ215" t="inlineStr"/>
+      <c r="BR215" t="inlineStr"/>
+      <c r="BS215" t="inlineStr"/>
+      <c r="BT215" t="inlineStr"/>
+      <c r="BU215" t="inlineStr"/>
+      <c r="BV215" t="inlineStr"/>
+      <c r="BW215" t="inlineStr"/>
+      <c r="BX215" t="inlineStr"/>
+      <c r="BY215" t="inlineStr"/>
+      <c r="BZ215" t="inlineStr"/>
+      <c r="CA215" t="inlineStr"/>
+      <c r="CB215" t="inlineStr"/>
+      <c r="CC215" t="inlineStr"/>
+      <c r="CD215" t="inlineStr"/>
+      <c r="CE215" t="inlineStr"/>
+      <c r="CF215" t="inlineStr"/>
+      <c r="CG215" t="inlineStr"/>
+      <c r="CH215" t="inlineStr"/>
+      <c r="CI215" t="inlineStr"/>
+      <c r="CJ215" t="inlineStr"/>
+      <c r="CK215" t="inlineStr"/>
+      <c r="CL215" t="inlineStr"/>
+      <c r="CM215" t="inlineStr"/>
+      <c r="CN215" t="inlineStr"/>
+      <c r="CO215" t="inlineStr"/>
+      <c r="CP215" t="inlineStr"/>
+      <c r="CQ215" t="inlineStr"/>
+      <c r="CR215" t="inlineStr"/>
+      <c r="CS215" t="inlineStr"/>
+      <c r="CT215" t="inlineStr"/>
+      <c r="CU215" t="inlineStr"/>
+      <c r="CV215" t="inlineStr"/>
+      <c r="CW215" t="inlineStr"/>
+      <c r="CX215" t="inlineStr"/>
+      <c r="CY215" t="inlineStr"/>
+      <c r="CZ215" t="inlineStr"/>
+      <c r="DA215" t="inlineStr"/>
+      <c r="DB215" t="inlineStr"/>
+      <c r="DC215" t="inlineStr"/>
+      <c r="DD215" t="inlineStr"/>
+      <c r="DE215" t="inlineStr"/>
+      <c r="DF215" t="inlineStr"/>
+      <c r="DG215" t="inlineStr"/>
+      <c r="DH215" t="inlineStr"/>
+      <c r="DI215" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>578</v>
+      </c>
+      <c r="B216" s="1" t="n">
+        <v>46186</v>
+      </c>
+      <c r="C216" s="1" t="n">
+        <v>46186</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>GSC</t>
+        </is>
+      </c>
+      <c r="G216" t="n">
+        <v>93905866</v>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>BRUNO ROCHA DA SILVA</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>231.025.738-94</t>
+        </is>
+      </c>
+      <c r="J216" s="1" t="n">
+        <v>32213</v>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>SUZANO</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>967071 PRATA QC COPART</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>(11)  962856104</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>2391647000 VMT TELECOMUNICACOES</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>Adriana Aparecida da Rosa Souza</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>Saúde da Coluna</t>
+        </is>
+      </c>
+      <c r="S216" t="inlineStr"/>
+      <c r="T216" t="inlineStr"/>
+      <c r="U216" t="inlineStr"/>
+      <c r="V216" t="inlineStr"/>
+      <c r="W216" t="inlineStr"/>
+      <c r="X216" t="inlineStr"/>
+      <c r="Y216" t="inlineStr"/>
+      <c r="Z216" t="inlineStr"/>
+      <c r="AA216" t="inlineStr"/>
+      <c r="AB216" t="inlineStr"/>
+      <c r="AC216" t="inlineStr"/>
+      <c r="AD216" t="inlineStr"/>
+      <c r="AE216" t="inlineStr"/>
+      <c r="AF216" t="inlineStr"/>
+      <c r="AG216" t="inlineStr"/>
+      <c r="AH216" t="inlineStr"/>
+      <c r="AI216" t="inlineStr"/>
+      <c r="AJ216" t="inlineStr"/>
+      <c r="AK216" t="inlineStr"/>
+      <c r="AL216" t="inlineStr"/>
+      <c r="AM216" t="inlineStr"/>
+      <c r="AN216" t="inlineStr"/>
+      <c r="AO216" t="inlineStr"/>
+      <c r="AP216" t="inlineStr"/>
+      <c r="AQ216" t="inlineStr"/>
+      <c r="AR216" t="inlineStr"/>
+      <c r="AS216" t="inlineStr"/>
+      <c r="AT216" t="inlineStr"/>
+      <c r="AU216" t="inlineStr"/>
+      <c r="AV216" t="inlineStr"/>
+      <c r="AW216" t="inlineStr"/>
+      <c r="AX216" t="inlineStr"/>
+      <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr"/>
+      <c r="BA216" t="inlineStr"/>
+      <c r="BB216" t="inlineStr"/>
+      <c r="BC216" t="inlineStr"/>
+      <c r="BD216" t="inlineStr"/>
+      <c r="BE216" t="inlineStr"/>
+      <c r="BF216" t="inlineStr"/>
+      <c r="BG216" t="inlineStr"/>
+      <c r="BH216" t="inlineStr"/>
+      <c r="BI216" t="inlineStr"/>
+      <c r="BJ216" t="inlineStr"/>
+      <c r="BK216" t="inlineStr"/>
+      <c r="BL216" t="inlineStr"/>
+      <c r="BM216" t="inlineStr"/>
+      <c r="BN216" t="inlineStr"/>
+      <c r="BO216" t="inlineStr"/>
+      <c r="BP216" t="inlineStr"/>
+      <c r="BQ216" t="inlineStr"/>
+      <c r="BR216" t="inlineStr"/>
+      <c r="BS216" t="inlineStr"/>
+      <c r="BT216" t="inlineStr"/>
+      <c r="BU216" t="inlineStr"/>
+      <c r="BV216" t="inlineStr"/>
+      <c r="BW216" t="inlineStr"/>
+      <c r="BX216" t="inlineStr"/>
+      <c r="BY216" t="inlineStr"/>
+      <c r="BZ216" t="inlineStr"/>
+      <c r="CA216" t="inlineStr"/>
+      <c r="CB216" t="inlineStr"/>
+      <c r="CC216" t="inlineStr"/>
+      <c r="CD216" t="inlineStr"/>
+      <c r="CE216" t="inlineStr"/>
+      <c r="CF216" t="inlineStr"/>
+      <c r="CG216" t="inlineStr"/>
+      <c r="CH216" t="inlineStr"/>
+      <c r="CI216" t="inlineStr"/>
+      <c r="CJ216" t="inlineStr"/>
+      <c r="CK216" t="inlineStr"/>
+      <c r="CL216" t="inlineStr"/>
+      <c r="CM216" t="inlineStr"/>
+      <c r="CN216" t="inlineStr"/>
+      <c r="CO216" t="inlineStr"/>
+      <c r="CP216" t="inlineStr"/>
+      <c r="CQ216" t="inlineStr"/>
+      <c r="CR216" t="inlineStr"/>
+      <c r="CS216" t="inlineStr"/>
+      <c r="CT216" t="inlineStr"/>
+      <c r="CU216" t="inlineStr"/>
+      <c r="CV216" t="inlineStr"/>
+      <c r="CW216" t="inlineStr"/>
+      <c r="CX216" t="inlineStr"/>
+      <c r="CY216" t="inlineStr"/>
+      <c r="CZ216" t="inlineStr"/>
+      <c r="DA216" t="inlineStr"/>
+      <c r="DB216" t="inlineStr"/>
+      <c r="DC216" t="inlineStr"/>
+      <c r="DD216" t="inlineStr"/>
+      <c r="DE216" t="inlineStr"/>
+      <c r="DF216" t="inlineStr"/>
+      <c r="DG216" t="inlineStr"/>
+      <c r="DH216" t="inlineStr"/>
+      <c r="DI216" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>579</v>
+      </c>
+      <c r="B217" s="1" t="n">
+        <v>46186</v>
+      </c>
+      <c r="C217" s="1" t="n">
+        <v>46186</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>GSC</t>
+        </is>
+      </c>
+      <c r="G217" t="n">
+        <v>93905843</v>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>DORYS BRITO DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>325.499.088-99</t>
+        </is>
+      </c>
+      <c r="J217" s="1" t="n">
+        <v>397112</v>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>DIADEMA</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>967071 PRATA QC COPART</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>(11) 994478218</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>A2391647000 VMT TELECOMUNICACOES</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>Adriana Aparecida da Rosa Souza</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>Cuidado Integral da Mama (oncologia)</t>
+        </is>
+      </c>
+      <c r="S217" t="inlineStr"/>
+      <c r="T217" t="inlineStr"/>
+      <c r="U217" t="inlineStr"/>
+      <c r="V217" t="inlineStr"/>
+      <c r="W217" t="inlineStr"/>
+      <c r="X217" t="inlineStr"/>
+      <c r="Y217" t="inlineStr"/>
+      <c r="Z217" t="inlineStr"/>
+      <c r="AA217" t="inlineStr"/>
+      <c r="AB217" t="inlineStr"/>
+      <c r="AC217" t="inlineStr"/>
+      <c r="AD217" t="inlineStr"/>
+      <c r="AE217" t="inlineStr"/>
+      <c r="AF217" t="inlineStr"/>
+      <c r="AG217" t="inlineStr"/>
+      <c r="AH217" t="inlineStr"/>
+      <c r="AI217" t="inlineStr"/>
+      <c r="AJ217" t="inlineStr"/>
+      <c r="AK217" t="inlineStr"/>
+      <c r="AL217" t="inlineStr"/>
+      <c r="AM217" t="inlineStr"/>
+      <c r="AN217" t="inlineStr"/>
+      <c r="AO217" t="inlineStr"/>
+      <c r="AP217" t="inlineStr"/>
+      <c r="AQ217" t="inlineStr"/>
+      <c r="AR217" t="inlineStr"/>
+      <c r="AS217" t="inlineStr"/>
+      <c r="AT217" t="inlineStr"/>
+      <c r="AU217" t="inlineStr"/>
+      <c r="AV217" t="inlineStr"/>
+      <c r="AW217" t="inlineStr"/>
+      <c r="AX217" t="inlineStr"/>
+      <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr"/>
+      <c r="BA217" t="inlineStr"/>
+      <c r="BB217" t="inlineStr"/>
+      <c r="BC217" t="inlineStr"/>
+      <c r="BD217" t="inlineStr"/>
+      <c r="BE217" t="inlineStr"/>
+      <c r="BF217" t="inlineStr"/>
+      <c r="BG217" t="inlineStr"/>
+      <c r="BH217" t="inlineStr"/>
+      <c r="BI217" t="inlineStr"/>
+      <c r="BJ217" t="inlineStr"/>
+      <c r="BK217" t="inlineStr"/>
+      <c r="BL217" t="inlineStr"/>
+      <c r="BM217" t="inlineStr"/>
+      <c r="BN217" t="inlineStr"/>
+      <c r="BO217" t="inlineStr"/>
+      <c r="BP217" t="inlineStr"/>
+      <c r="BQ217" t="inlineStr"/>
+      <c r="BR217" t="inlineStr"/>
+      <c r="BS217" t="inlineStr"/>
+      <c r="BT217" t="inlineStr"/>
+      <c r="BU217" t="inlineStr"/>
+      <c r="BV217" t="inlineStr"/>
+      <c r="BW217" t="inlineStr"/>
+      <c r="BX217" t="inlineStr"/>
+      <c r="BY217" t="inlineStr"/>
+      <c r="BZ217" t="inlineStr"/>
+      <c r="CA217" t="inlineStr"/>
+      <c r="CB217" t="inlineStr"/>
+      <c r="CC217" t="inlineStr"/>
+      <c r="CD217" t="inlineStr"/>
+      <c r="CE217" t="inlineStr"/>
+      <c r="CF217" t="inlineStr"/>
+      <c r="CG217" t="inlineStr"/>
+      <c r="CH217" t="inlineStr"/>
+      <c r="CI217" t="inlineStr"/>
+      <c r="CJ217" t="inlineStr"/>
+      <c r="CK217" t="inlineStr"/>
+      <c r="CL217" t="inlineStr"/>
+      <c r="CM217" t="inlineStr"/>
+      <c r="CN217" t="inlineStr"/>
+      <c r="CO217" t="inlineStr"/>
+      <c r="CP217" t="inlineStr"/>
+      <c r="CQ217" t="inlineStr"/>
+      <c r="CR217" t="inlineStr"/>
+      <c r="CS217" t="inlineStr"/>
+      <c r="CT217" t="inlineStr"/>
+      <c r="CU217" t="inlineStr"/>
+      <c r="CV217" t="inlineStr"/>
+      <c r="CW217" t="inlineStr"/>
+      <c r="CX217" t="inlineStr"/>
+      <c r="CY217" t="inlineStr"/>
+      <c r="CZ217" t="inlineStr"/>
+      <c r="DA217" t="inlineStr"/>
+      <c r="DB217" t="inlineStr"/>
+      <c r="DC217" t="inlineStr"/>
+      <c r="DD217" t="inlineStr"/>
+      <c r="DE217" t="inlineStr"/>
+      <c r="DF217" t="inlineStr"/>
+      <c r="DG217" t="inlineStr"/>
+      <c r="DH217" t="inlineStr"/>
+      <c r="DI217" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>580</v>
+      </c>
+      <c r="B218" s="1" t="n">
+        <v>46187</v>
+      </c>
+      <c r="C218" s="1" t="n">
+        <v>46187</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>GSC</t>
+        </is>
+      </c>
+      <c r="G218" t="n">
+        <v>93906235</v>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>ARIANA AREAS DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>136.640.707-55</t>
+        </is>
+      </c>
+      <c r="J218" s="1" t="n">
+        <v>32445</v>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Feminino</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>SAO GONÇALO</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>967071 PRATA QC COPART</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>(21) 973254246  (21)  996687968</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>2391647000 VMT TELECOMUNICACOES</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>Adriana Aparecida da Rosa Souza</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>Saúde da Coluna</t>
+        </is>
+      </c>
+      <c r="S218" t="inlineStr"/>
+      <c r="T218" t="inlineStr"/>
+      <c r="U218" t="inlineStr"/>
+      <c r="V218" t="inlineStr"/>
+      <c r="W218" t="inlineStr"/>
+      <c r="X218" t="inlineStr"/>
+      <c r="Y218" t="inlineStr"/>
+      <c r="Z218" t="inlineStr"/>
+      <c r="AA218" t="inlineStr"/>
+      <c r="AB218" t="inlineStr"/>
+      <c r="AC218" t="inlineStr"/>
+      <c r="AD218" t="inlineStr"/>
+      <c r="AE218" t="inlineStr"/>
+      <c r="AF218" t="inlineStr"/>
+      <c r="AG218" t="inlineStr"/>
+      <c r="AH218" t="inlineStr"/>
+      <c r="AI218" t="inlineStr"/>
+      <c r="AJ218" t="inlineStr"/>
+      <c r="AK218" t="inlineStr"/>
+      <c r="AL218" t="inlineStr"/>
+      <c r="AM218" t="inlineStr"/>
+      <c r="AN218" t="inlineStr"/>
+      <c r="AO218" t="inlineStr"/>
+      <c r="AP218" t="inlineStr"/>
+      <c r="AQ218" t="inlineStr"/>
+      <c r="AR218" t="inlineStr"/>
+      <c r="AS218" t="inlineStr"/>
+      <c r="AT218" t="inlineStr"/>
+      <c r="AU218" t="inlineStr"/>
+      <c r="AV218" t="inlineStr"/>
+      <c r="AW218" t="inlineStr"/>
+      <c r="AX218" t="inlineStr"/>
+      <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr"/>
+      <c r="BA218" t="inlineStr"/>
+      <c r="BB218" t="inlineStr"/>
+      <c r="BC218" t="inlineStr"/>
+      <c r="BD218" t="inlineStr"/>
+      <c r="BE218" t="inlineStr"/>
+      <c r="BF218" t="inlineStr"/>
+      <c r="BG218" t="inlineStr"/>
+      <c r="BH218" t="inlineStr"/>
+      <c r="BI218" t="inlineStr"/>
+      <c r="BJ218" t="inlineStr"/>
+      <c r="BK218" t="inlineStr"/>
+      <c r="BL218" t="inlineStr"/>
+      <c r="BM218" t="inlineStr"/>
+      <c r="BN218" t="inlineStr"/>
+      <c r="BO218" t="inlineStr"/>
+      <c r="BP218" t="inlineStr"/>
+      <c r="BQ218" t="inlineStr"/>
+      <c r="BR218" t="inlineStr"/>
+      <c r="BS218" t="inlineStr"/>
+      <c r="BT218" t="inlineStr"/>
+      <c r="BU218" t="inlineStr"/>
+      <c r="BV218" t="inlineStr"/>
+      <c r="BW218" t="inlineStr"/>
+      <c r="BX218" t="inlineStr"/>
+      <c r="BY218" t="inlineStr"/>
+      <c r="BZ218" t="inlineStr"/>
+      <c r="CA218" t="inlineStr"/>
+      <c r="CB218" t="inlineStr"/>
+      <c r="CC218" t="inlineStr"/>
+      <c r="CD218" t="inlineStr"/>
+      <c r="CE218" t="inlineStr"/>
+      <c r="CF218" t="inlineStr"/>
+      <c r="CG218" t="inlineStr"/>
+      <c r="CH218" t="inlineStr"/>
+      <c r="CI218" t="inlineStr"/>
+      <c r="CJ218" t="inlineStr"/>
+      <c r="CK218" t="inlineStr"/>
+      <c r="CL218" t="inlineStr"/>
+      <c r="CM218" t="inlineStr"/>
+      <c r="CN218" t="inlineStr"/>
+      <c r="CO218" t="inlineStr"/>
+      <c r="CP218" t="inlineStr"/>
+      <c r="CQ218" t="inlineStr"/>
+      <c r="CR218" t="inlineStr"/>
+      <c r="CS218" t="inlineStr"/>
+      <c r="CT218" t="inlineStr"/>
+      <c r="CU218" t="inlineStr"/>
+      <c r="CV218" t="inlineStr"/>
+      <c r="CW218" t="inlineStr"/>
+      <c r="CX218" t="inlineStr"/>
+      <c r="CY218" t="inlineStr"/>
+      <c r="CZ218" t="inlineStr"/>
+      <c r="DA218" t="inlineStr"/>
+      <c r="DB218" t="inlineStr"/>
+      <c r="DC218" t="inlineStr"/>
+      <c r="DD218" t="inlineStr"/>
+      <c r="DE218" t="inlineStr"/>
+      <c r="DF218" t="inlineStr"/>
+      <c r="DG218" t="inlineStr"/>
+      <c r="DH218" t="inlineStr"/>
+      <c r="DI218" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>581</v>
+      </c>
+      <c r="B219" s="1" t="n">
+        <v>46187</v>
+      </c>
+      <c r="C219" s="1" t="n">
+        <v>46187</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>GSC</t>
+        </is>
+      </c>
+      <c r="G219" t="n">
+        <v>93906388</v>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>AUGUSTO JOSE GUTIERREZ PAGAN ANDRADE</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>370.422.418-94</t>
+        </is>
+      </c>
+      <c r="J219" s="1" t="n">
+        <v>31950</v>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>SAO PAULO</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>967071 PRATA QC COPART</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>(11)  930061767</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>2391647000 VMT TELECOMUNICACOES</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>Adriana Aparecida da Rosa Souza</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>Saúde da Coluna</t>
+        </is>
+      </c>
+      <c r="S219" t="inlineStr"/>
+      <c r="T219" t="inlineStr"/>
+      <c r="U219" t="inlineStr"/>
+      <c r="V219" t="inlineStr"/>
+      <c r="W219" t="inlineStr"/>
+      <c r="X219" t="inlineStr"/>
+      <c r="Y219" t="inlineStr"/>
+      <c r="Z219" t="inlineStr"/>
+      <c r="AA219" t="inlineStr"/>
+      <c r="AB219" t="inlineStr"/>
+      <c r="AC219" t="inlineStr"/>
+      <c r="AD219" t="inlineStr"/>
+      <c r="AE219" t="inlineStr"/>
+      <c r="AF219" t="inlineStr"/>
+      <c r="AG219" t="inlineStr"/>
+      <c r="AH219" t="inlineStr"/>
+      <c r="AI219" t="inlineStr"/>
+      <c r="AJ219" t="inlineStr"/>
+      <c r="AK219" t="inlineStr"/>
+      <c r="AL219" t="inlineStr"/>
+      <c r="AM219" t="inlineStr"/>
+      <c r="AN219" t="inlineStr"/>
+      <c r="AO219" t="inlineStr"/>
+      <c r="AP219" t="inlineStr"/>
+      <c r="AQ219" t="inlineStr"/>
+      <c r="AR219" t="inlineStr"/>
+      <c r="AS219" t="inlineStr"/>
+      <c r="AT219" t="inlineStr"/>
+      <c r="AU219" t="inlineStr"/>
+      <c r="AV219" t="inlineStr"/>
+      <c r="AW219" t="inlineStr"/>
+      <c r="AX219" t="inlineStr"/>
+      <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr"/>
+      <c r="BA219" t="inlineStr"/>
+      <c r="BB219" t="inlineStr"/>
+      <c r="BC219" t="inlineStr"/>
+      <c r="BD219" t="inlineStr"/>
+      <c r="BE219" t="inlineStr"/>
+      <c r="BF219" t="inlineStr"/>
+      <c r="BG219" t="inlineStr"/>
+      <c r="BH219" t="inlineStr"/>
+      <c r="BI219" t="inlineStr"/>
+      <c r="BJ219" t="inlineStr"/>
+      <c r="BK219" t="inlineStr"/>
+      <c r="BL219" t="inlineStr"/>
+      <c r="BM219" t="inlineStr"/>
+      <c r="BN219" t="inlineStr"/>
+      <c r="BO219" t="inlineStr"/>
+      <c r="BP219" t="inlineStr"/>
+      <c r="BQ219" t="inlineStr"/>
+      <c r="BR219" t="inlineStr"/>
+      <c r="BS219" t="inlineStr"/>
+      <c r="BT219" t="inlineStr"/>
+      <c r="BU219" t="inlineStr"/>
+      <c r="BV219" t="inlineStr"/>
+      <c r="BW219" t="inlineStr"/>
+      <c r="BX219" t="inlineStr"/>
+      <c r="BY219" t="inlineStr"/>
+      <c r="BZ219" t="inlineStr"/>
+      <c r="CA219" t="inlineStr"/>
+      <c r="CB219" t="inlineStr"/>
+      <c r="CC219" t="inlineStr"/>
+      <c r="CD219" t="inlineStr"/>
+      <c r="CE219" t="inlineStr"/>
+      <c r="CF219" t="inlineStr"/>
+      <c r="CG219" t="inlineStr"/>
+      <c r="CH219" t="inlineStr"/>
+      <c r="CI219" t="inlineStr"/>
+      <c r="CJ219" t="inlineStr"/>
+      <c r="CK219" t="inlineStr"/>
+      <c r="CL219" t="inlineStr"/>
+      <c r="CM219" t="inlineStr"/>
+      <c r="CN219" t="inlineStr"/>
+      <c r="CO219" t="inlineStr"/>
+      <c r="CP219" t="inlineStr"/>
+      <c r="CQ219" t="inlineStr"/>
+      <c r="CR219" t="inlineStr"/>
+      <c r="CS219" t="inlineStr"/>
+      <c r="CT219" t="inlineStr"/>
+      <c r="CU219" t="inlineStr"/>
+      <c r="CV219" t="inlineStr"/>
+      <c r="CW219" t="inlineStr"/>
+      <c r="CX219" t="inlineStr"/>
+      <c r="CY219" t="inlineStr"/>
+      <c r="CZ219" t="inlineStr"/>
+      <c r="DA219" t="inlineStr"/>
+      <c r="DB219" t="inlineStr"/>
+      <c r="DC219" t="inlineStr"/>
+      <c r="DD219" t="inlineStr"/>
+      <c r="DE219" t="inlineStr"/>
+      <c r="DF219" t="inlineStr"/>
+      <c r="DG219" t="inlineStr"/>
+      <c r="DH219" t="inlineStr"/>
+      <c r="DI219" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
